--- a/output/cta-violent-crime-ytd.xlsx
+++ b/output/cta-violent-crime-ytd.xlsx
@@ -9,17 +9,17 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="West Town" sheetId="3" r:id="rId3"/>
-    <sheet name="Englewood" sheetId="4" r:id="rId4"/>
-    <sheet name="Avondale" sheetId="5" r:id="rId5"/>
-    <sheet name="Douglas" sheetId="6" r:id="rId6"/>
-    <sheet name="Grand Crossing" sheetId="7" r:id="rId7"/>
+    <sheet name="Englewood" sheetId="3" r:id="rId3"/>
+    <sheet name="Avondale" sheetId="4" r:id="rId4"/>
+    <sheet name="Douglas" sheetId="5" r:id="rId5"/>
+    <sheet name="Grand Boulevard" sheetId="6" r:id="rId6"/>
+    <sheet name="West Town" sheetId="7" r:id="rId7"/>
     <sheet name="Austin" sheetId="8" r:id="rId8"/>
-    <sheet name="Grand Boulevard" sheetId="9" r:id="rId9"/>
-    <sheet name="Mount Greenwood" sheetId="10" r:id="rId10"/>
-    <sheet name="Humboldt Park" sheetId="11" r:id="rId11"/>
-    <sheet name="Garfield Park" sheetId="12" r:id="rId12"/>
-    <sheet name="Loop" sheetId="13" r:id="rId13"/>
+    <sheet name="Mount Greenwood" sheetId="9" r:id="rId9"/>
+    <sheet name="Humboldt Park" sheetId="10" r:id="rId10"/>
+    <sheet name="Garfield Park" sheetId="11" r:id="rId11"/>
+    <sheet name="Loop" sheetId="12" r:id="rId12"/>
+    <sheet name="Grand Crossing" sheetId="13" r:id="rId13"/>
     <sheet name="United Center" sheetId="14" r:id="rId14"/>
     <sheet name="Ashburn" sheetId="15" r:id="rId15"/>
     <sheet name="Rush &amp; Division" sheetId="16" r:id="rId16"/>
@@ -34,11 +34,11 @@
     <sheet name="South Chicago" sheetId="25" r:id="rId25"/>
     <sheet name="Roseland" sheetId="26" r:id="rId26"/>
     <sheet name="Fuller Park" sheetId="27" r:id="rId27"/>
-    <sheet name="O'Hare" sheetId="28" r:id="rId28"/>
-    <sheet name="Little Italy, UIC" sheetId="29" r:id="rId29"/>
-    <sheet name="Hyde Park" sheetId="30" r:id="rId30"/>
-    <sheet name="Calumet Heights" sheetId="31" r:id="rId31"/>
-    <sheet name="Kenwood" sheetId="32" r:id="rId32"/>
+    <sheet name="Little Italy, UIC" sheetId="28" r:id="rId28"/>
+    <sheet name="Hyde Park" sheetId="29" r:id="rId29"/>
+    <sheet name="Calumet Heights" sheetId="30" r:id="rId30"/>
+    <sheet name="Kenwood" sheetId="31" r:id="rId31"/>
+    <sheet name="O'Hare" sheetId="32" r:id="rId32"/>
     <sheet name="Chicago Lawn" sheetId="33" r:id="rId33"/>
     <sheet name="Wrigleyville" sheetId="34" r:id="rId34"/>
     <sheet name="Auburn Gresham" sheetId="35" r:id="rId35"/>
@@ -1101,59 +1101,6 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1362,6 +1309,261 @@
       </c>
       <c r="M6">
         <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>7</v>
+      </c>
+      <c r="J3">
+        <v>8</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>28</v>
+      </c>
+      <c r="F6">
+        <v>43</v>
+      </c>
+      <c r="G6">
+        <v>35</v>
+      </c>
+      <c r="H6">
+        <v>30</v>
+      </c>
+      <c r="I6">
+        <v>23</v>
+      </c>
+      <c r="J6">
+        <v>20</v>
+      </c>
+      <c r="K6">
+        <v>19</v>
+      </c>
+      <c r="L6">
+        <v>22</v>
+      </c>
+      <c r="M6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>37</v>
+      </c>
+      <c r="F7">
+        <v>50</v>
+      </c>
+      <c r="G7">
+        <v>43</v>
+      </c>
+      <c r="H7">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>35</v>
+      </c>
+      <c r="J7">
+        <v>29</v>
+      </c>
+      <c r="K7">
+        <v>35</v>
+      </c>
+      <c r="L7">
+        <v>32</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1434,106 +1636,127 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
       <c r="C3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="M3">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I5">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -1542,40 +1765,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F6">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G6">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H6">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I6">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="J6">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="K6">
+        <v>38</v>
+      </c>
+      <c r="L6">
+        <v>32</v>
+      </c>
+      <c r="M6">
         <v>19</v>
-      </c>
-      <c r="L6">
-        <v>22</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1583,40 +1806,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D7">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="F7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G7">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="H7">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="I7">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="J7">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="K7">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="L7">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1690,13 +1913,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -1708,22 +1931,22 @@
         <v>4</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1731,85 +1954,73 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
         <v>10</v>
       </c>
-      <c r="I3">
-        <v>24</v>
-      </c>
-      <c r="J3">
-        <v>24</v>
-      </c>
-      <c r="K3">
-        <v>22</v>
-      </c>
       <c r="L3">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>4</v>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -1818,40 +2029,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H6">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="I6">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="J6">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="K6">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M6">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1859,40 +2070,40 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>27</v>
+      </c>
+      <c r="F7">
         <v>36</v>
       </c>
-      <c r="C7">
-        <v>41</v>
-      </c>
-      <c r="D7">
-        <v>58</v>
-      </c>
-      <c r="E7">
-        <v>56</v>
-      </c>
-      <c r="F7">
-        <v>55</v>
-      </c>
       <c r="G7">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="H7">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="J7">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="K7">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="L7">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="M7">
-        <v>42</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -8166,168 +8377,6 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8558,9 +8607,174 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -8623,29 +8837,32 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="D2">
         <v>3</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
       <c r="H2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2">
         <v>4</v>
@@ -8655,116 +8872,154 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
       <c r="J4">
         <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="L6">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>28</v>
+      </c>
+      <c r="C7">
+        <v>38</v>
+      </c>
+      <c r="D7">
+        <v>34</v>
+      </c>
+      <c r="E7">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>39</v>
+      </c>
+      <c r="G7">
+        <v>31</v>
+      </c>
+      <c r="H7">
+        <v>37</v>
+      </c>
+      <c r="I7">
+        <v>34</v>
+      </c>
+      <c r="J7">
+        <v>21</v>
+      </c>
+      <c r="K7">
+        <v>42</v>
+      </c>
+      <c r="L7">
+        <v>52</v>
+      </c>
+      <c r="M7">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -8773,171 +9028,6 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>5</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9100,7 +9190,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9209,6 +9299,168 @@
       </c>
       <c r="H6">
         <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -10568,7 +10820,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10631,189 +10883,133 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>3</v>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
       <c r="H2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>5</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>13</v>
-      </c>
       <c r="E3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
       <c r="K4">
         <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>28</v>
-      </c>
-      <c r="C7">
-        <v>38</v>
-      </c>
-      <c r="D7">
-        <v>34</v>
-      </c>
-      <c r="E7">
-        <v>23</v>
-      </c>
-      <c r="F7">
-        <v>39</v>
-      </c>
-      <c r="G7">
-        <v>31</v>
-      </c>
-      <c r="H7">
-        <v>37</v>
-      </c>
-      <c r="I7">
-        <v>34</v>
-      </c>
-      <c r="J7">
-        <v>21</v>
-      </c>
-      <c r="K7">
-        <v>42</v>
-      </c>
-      <c r="L7">
-        <v>52</v>
-      </c>
-      <c r="M7">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -12755,7 +12951,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12818,33 +13014,27 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3">
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="F3">
@@ -12853,68 +13043,41 @@
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K4">
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -12923,28 +13086,63 @@
         <v>3</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -14318,10 +14516,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -14382,27 +14580,36 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="I2">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3">
-        <v>1</v>
+      <c r="B3">
+        <v>2</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -14411,10 +14618,13 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -14422,94 +14632,89 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4">
+        <v>4</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>4</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
-        <v>7</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
-      <c r="M7">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -16010,7 +16215,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -16074,197 +16279,147 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
         <v>11</v>
       </c>
-      <c r="H6">
-        <v>13</v>
-      </c>
-      <c r="I6">
-        <v>13</v>
-      </c>
-      <c r="J6">
-        <v>18</v>
-      </c>
-      <c r="K6">
-        <v>31</v>
-      </c>
-      <c r="L6">
-        <v>31</v>
-      </c>
       <c r="M6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>19</v>
-      </c>
-      <c r="C7">
-        <v>29</v>
-      </c>
-      <c r="D7">
-        <v>27</v>
-      </c>
-      <c r="E7">
-        <v>27</v>
-      </c>
-      <c r="F7">
-        <v>36</v>
-      </c>
-      <c r="G7">
-        <v>19</v>
-      </c>
-      <c r="H7">
-        <v>25</v>
-      </c>
-      <c r="I7">
-        <v>29</v>
-      </c>
-      <c r="J7">
-        <v>30</v>
-      </c>
-      <c r="K7">
-        <v>48</v>
-      </c>
-      <c r="L7">
-        <v>44</v>
-      </c>
-      <c r="M7">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -18552,205 +18707,50 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>10</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-ytd.xlsx
+++ b/output/cta-violent-crime-ytd.xlsx
@@ -9,17 +9,17 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Englewood" sheetId="3" r:id="rId3"/>
-    <sheet name="Avondale" sheetId="4" r:id="rId4"/>
-    <sheet name="Douglas" sheetId="5" r:id="rId5"/>
-    <sheet name="Grand Boulevard" sheetId="6" r:id="rId6"/>
-    <sheet name="West Town" sheetId="7" r:id="rId7"/>
+    <sheet name="West Town" sheetId="3" r:id="rId3"/>
+    <sheet name="Englewood" sheetId="4" r:id="rId4"/>
+    <sheet name="Avondale" sheetId="5" r:id="rId5"/>
+    <sheet name="Douglas" sheetId="6" r:id="rId6"/>
+    <sheet name="Grand Crossing" sheetId="7" r:id="rId7"/>
     <sheet name="Austin" sheetId="8" r:id="rId8"/>
-    <sheet name="Mount Greenwood" sheetId="9" r:id="rId9"/>
-    <sheet name="Humboldt Park" sheetId="10" r:id="rId10"/>
-    <sheet name="Garfield Park" sheetId="11" r:id="rId11"/>
-    <sheet name="Loop" sheetId="12" r:id="rId12"/>
-    <sheet name="Grand Crossing" sheetId="13" r:id="rId13"/>
+    <sheet name="Grand Boulevard" sheetId="9" r:id="rId9"/>
+    <sheet name="Mount Greenwood" sheetId="10" r:id="rId10"/>
+    <sheet name="Humboldt Park" sheetId="11" r:id="rId11"/>
+    <sheet name="Garfield Park" sheetId="12" r:id="rId12"/>
+    <sheet name="Loop" sheetId="13" r:id="rId13"/>
     <sheet name="United Center" sheetId="14" r:id="rId14"/>
     <sheet name="Ashburn" sheetId="15" r:id="rId15"/>
     <sheet name="Rush &amp; Division" sheetId="16" r:id="rId16"/>
@@ -34,11 +34,11 @@
     <sheet name="South Chicago" sheetId="25" r:id="rId25"/>
     <sheet name="Roseland" sheetId="26" r:id="rId26"/>
     <sheet name="Fuller Park" sheetId="27" r:id="rId27"/>
-    <sheet name="Little Italy, UIC" sheetId="28" r:id="rId28"/>
-    <sheet name="Hyde Park" sheetId="29" r:id="rId29"/>
-    <sheet name="Calumet Heights" sheetId="30" r:id="rId30"/>
-    <sheet name="Kenwood" sheetId="31" r:id="rId31"/>
-    <sheet name="O'Hare" sheetId="32" r:id="rId32"/>
+    <sheet name="O'Hare" sheetId="28" r:id="rId28"/>
+    <sheet name="Little Italy, UIC" sheetId="29" r:id="rId29"/>
+    <sheet name="Hyde Park" sheetId="30" r:id="rId30"/>
+    <sheet name="Calumet Heights" sheetId="31" r:id="rId31"/>
+    <sheet name="Kenwood" sheetId="32" r:id="rId32"/>
     <sheet name="Chicago Lawn" sheetId="33" r:id="rId33"/>
     <sheet name="Wrigleyville" sheetId="34" r:id="rId34"/>
     <sheet name="Auburn Gresham" sheetId="35" r:id="rId35"/>
@@ -874,16 +874,16 @@
         <v>65</v>
       </c>
       <c r="H2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L2">
         <v>102</v>
@@ -897,10 +897,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C3">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D3">
         <v>96</v>
@@ -915,13 +915,13 @@
         <v>87</v>
       </c>
       <c r="H3">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I3">
         <v>144</v>
       </c>
       <c r="J3">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K3">
         <v>155</v>
@@ -1017,40 +1017,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C6">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D6">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E6">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F6">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G6">
         <v>350</v>
       </c>
       <c r="H6">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I6">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J6">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K6">
         <v>357</v>
       </c>
       <c r="L6">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M6">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1058,40 +1058,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C7">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D7">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E7">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F7">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="G7">
         <v>505</v>
       </c>
       <c r="H7">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="I7">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="J7">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="K7">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L7">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M7">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -1100,6 +1100,59 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1309,261 +1362,6 @@
       </c>
       <c r="M6">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>6</v>
-      </c>
-      <c r="E2">
-        <v>6</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>7</v>
-      </c>
-      <c r="J3">
-        <v>8</v>
-      </c>
-      <c r="K3">
-        <v>12</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
-      <c r="M3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>22</v>
-      </c>
-      <c r="D6">
-        <v>30</v>
-      </c>
-      <c r="E6">
-        <v>28</v>
-      </c>
-      <c r="F6">
-        <v>43</v>
-      </c>
-      <c r="G6">
-        <v>35</v>
-      </c>
-      <c r="H6">
-        <v>30</v>
-      </c>
-      <c r="I6">
-        <v>23</v>
-      </c>
-      <c r="J6">
-        <v>20</v>
-      </c>
-      <c r="K6">
-        <v>19</v>
-      </c>
-      <c r="L6">
-        <v>22</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>40</v>
-      </c>
-      <c r="E7">
-        <v>37</v>
-      </c>
-      <c r="F7">
-        <v>50</v>
-      </c>
-      <c r="G7">
-        <v>43</v>
-      </c>
-      <c r="H7">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>35</v>
-      </c>
-      <c r="J7">
-        <v>29</v>
-      </c>
-      <c r="K7">
-        <v>35</v>
-      </c>
-      <c r="L7">
-        <v>32</v>
-      </c>
-      <c r="M7">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1636,127 +1434,106 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>7</v>
+      </c>
+      <c r="J3">
         <v>9</v>
       </c>
-      <c r="C3">
-        <v>11</v>
-      </c>
-      <c r="D3">
-        <v>15</v>
-      </c>
-      <c r="E3">
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
         <v>9</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>14</v>
-      </c>
-      <c r="H3">
-        <v>10</v>
-      </c>
-      <c r="I3">
-        <v>24</v>
-      </c>
-      <c r="J3">
-        <v>24</v>
-      </c>
-      <c r="K3">
-        <v>22</v>
-      </c>
-      <c r="L3">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
         <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>4</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -1765,40 +1542,40 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
         <v>22</v>
       </c>
-      <c r="C6">
-        <v>26</v>
-      </c>
       <c r="D6">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G6">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H6">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I6">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="J6">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="K6">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="L6">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="M6">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1806,40 +1583,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D7">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="E7">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G7">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="H7">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="J7">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="K7">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="L7">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="M7">
-        <v>42</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1913,13 +1690,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -1931,22 +1708,22 @@
         <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1954,73 +1731,85 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3">
+        <v>9</v>
+      </c>
+      <c r="G3">
         <v>14</v>
       </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
       <c r="H3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
       </c>
       <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -2029,40 +1818,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="H6">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="J6">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="K6">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2070,40 +1859,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="G7">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="H7">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="I7">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="J7">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="K7">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="L7">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="M7">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -3394,7 +3183,7 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -3592,7 +3381,7 @@
         <v>23</v>
       </c>
       <c r="H8">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I8">
         <v>22</v>
@@ -3659,7 +3448,7 @@
         <v>4</v>
       </c>
       <c r="J10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -3881,7 +3670,7 @@
         <v>12</v>
       </c>
       <c r="F19">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G19">
         <v>18</v>
@@ -3899,7 +3688,7 @@
         <v>24</v>
       </c>
       <c r="L19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M19">
         <v>11</v>
@@ -4021,7 +3810,7 @@
         <v>29</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23">
         <v>5</v>
@@ -4084,6 +3873,9 @@
       <c r="F25">
         <v>1</v>
       </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
       <c r="K25">
         <v>2</v>
       </c>
@@ -4251,7 +4043,7 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30">
         <v>3</v>
@@ -4312,7 +4104,7 @@
         <v>35</v>
       </c>
       <c r="J32">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K32">
         <v>35</v>
@@ -4557,7 +4349,7 @@
         <v>1</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F42">
         <v>2</v>
@@ -4677,7 +4469,7 @@
         <v>7</v>
       </c>
       <c r="I45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J45">
         <v>4</v>
@@ -4975,7 +4767,7 @@
         <v>61</v>
       </c>
       <c r="H53">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I53">
         <v>100</v>
@@ -4990,7 +4782,7 @@
         <v>72</v>
       </c>
       <c r="M53">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -5359,6 +5151,9 @@
       <c r="D67">
         <v>2</v>
       </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
       <c r="F67">
         <v>1</v>
       </c>
@@ -5587,7 +5382,7 @@
         <v>18</v>
       </c>
       <c r="K74">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L74">
         <v>7</v>
@@ -5603,6 +5398,9 @@
       <c r="B75">
         <v>1</v>
       </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
       <c r="D75">
         <v>1</v>
       </c>
@@ -5648,7 +5446,7 @@
         <v>10</v>
       </c>
       <c r="H76">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I76">
         <v>16</v>
@@ -5683,7 +5481,7 @@
         <v>21</v>
       </c>
       <c r="F77">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G77">
         <v>16</v>
@@ -5797,7 +5595,7 @@
         <v>11</v>
       </c>
       <c r="C80">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D80">
         <v>2</v>
@@ -5992,7 +5790,7 @@
         <v>6</v>
       </c>
       <c r="C86">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D86">
         <v>2</v>
@@ -6013,7 +5811,7 @@
         <v>8</v>
       </c>
       <c r="J86">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K86">
         <v>13</v>
@@ -6036,7 +5834,7 @@
         <v>8</v>
       </c>
       <c r="D87">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E87">
         <v>6</v>
@@ -6415,40 +6213,40 @@
         <v>6</v>
       </c>
       <c r="B98">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C98">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D98">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E98">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F98">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="G98">
         <v>505</v>
       </c>
       <c r="H98">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="I98">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="J98">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="K98">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L98">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M98">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -6886,7 +6684,7 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -7008,7 +6806,7 @@
         <v>18</v>
       </c>
       <c r="K6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -7106,7 +6904,7 @@
         <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
         <v>3</v>
@@ -7169,7 +6967,7 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -7207,7 +7005,7 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -7228,7 +7026,7 @@
         <v>8</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6">
         <v>13</v>
@@ -7410,7 +7208,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>12</v>
@@ -7428,7 +7226,7 @@
         <v>13</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -7451,7 +7249,7 @@
         <v>12</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6">
         <v>18</v>
@@ -7469,7 +7267,7 @@
         <v>24</v>
       </c>
       <c r="L6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M6">
         <v>11</v>
@@ -7830,7 +7628,7 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -7868,7 +7666,7 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -8088,7 +7886,7 @@
         <v>13</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6">
         <v>11</v>
@@ -8129,7 +7927,7 @@
         <v>21</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>16</v>
@@ -8377,6 +8175,168 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8607,7 +8567,221 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>11</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>11</v>
+      </c>
+      <c r="M6">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8708,7 +8882,7 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -8743,7 +8917,7 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -8772,262 +8946,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-      <c r="H2">
-        <v>10</v>
-      </c>
-      <c r="I2">
-        <v>6</v>
-      </c>
-      <c r="J2">
-        <v>5</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>13</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>11</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>14</v>
-      </c>
-      <c r="L3">
-        <v>14</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>26</v>
-      </c>
-      <c r="C6">
-        <v>34</v>
-      </c>
-      <c r="D6">
-        <v>18</v>
-      </c>
-      <c r="E6">
-        <v>16</v>
-      </c>
-      <c r="F6">
-        <v>28</v>
-      </c>
-      <c r="G6">
-        <v>23</v>
-      </c>
-      <c r="H6">
-        <v>22</v>
-      </c>
-      <c r="I6">
-        <v>16</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>25</v>
-      </c>
-      <c r="L6">
-        <v>33</v>
-      </c>
-      <c r="M6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>28</v>
-      </c>
-      <c r="C7">
-        <v>38</v>
-      </c>
-      <c r="D7">
-        <v>34</v>
-      </c>
-      <c r="E7">
-        <v>23</v>
-      </c>
-      <c r="F7">
-        <v>39</v>
-      </c>
-      <c r="G7">
-        <v>31</v>
-      </c>
-      <c r="H7">
-        <v>37</v>
-      </c>
-      <c r="I7">
-        <v>34</v>
-      </c>
-      <c r="J7">
-        <v>21</v>
-      </c>
-      <c r="K7">
-        <v>42</v>
-      </c>
-      <c r="L7">
-        <v>52</v>
-      </c>
-      <c r="M7">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9190,7 +9109,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9299,168 +9218,6 @@
       </c>
       <c r="H6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -10207,7 +9964,7 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -10245,7 +10002,7 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>3</v>
@@ -10378,7 +10135,7 @@
         <v>4</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -10480,7 +10237,7 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6">
         <v>16</v>
@@ -10666,7 +10423,7 @@
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10679,9 +10436,10 @@
     <col min="8" max="8" width="4.7109375" customWidth="1"/>
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10689,55 +10447,55 @@
         <v>2017</v>
       </c>
       <c r="C1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="D1" s="1">
         <v>2019</v>
       </c>
-      <c r="D1" s="1">
+      <c r="E1" s="1">
         <v>2020</v>
       </c>
-      <c r="E1" s="1">
+      <c r="F1" s="1">
         <v>2021</v>
       </c>
-      <c r="F1" s="1">
+      <c r="G1" s="1">
         <v>2022</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
         <v>2023</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
         <v>2024</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2025</v>
       </c>
-      <c r="J1" s="1">
+      <c r="K1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="H3">
+      <c r="E3">
         <v>1</v>
       </c>
       <c r="I3">
@@ -10746,30 +10504,33 @@
       <c r="J3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -10778,10 +10539,13 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -10795,21 +10559,24 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>3</v>
       </c>
       <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
         <v>4</v>
       </c>
     </row>
@@ -10820,7 +10587,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10883,133 +10650,189 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
+      <c r="D2">
+        <v>3</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
       <c r="H2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>13</v>
+      </c>
       <c r="E3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>11</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>14</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
       <c r="K4">
         <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>28</v>
+      </c>
+      <c r="C7">
+        <v>38</v>
+      </c>
+      <c r="D7">
+        <v>34</v>
+      </c>
+      <c r="E7">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>39</v>
+      </c>
+      <c r="G7">
+        <v>31</v>
+      </c>
+      <c r="H7">
+        <v>37</v>
+      </c>
+      <c r="I7">
+        <v>34</v>
+      </c>
+      <c r="J7">
+        <v>21</v>
+      </c>
+      <c r="K7">
+        <v>42</v>
+      </c>
+      <c r="L7">
+        <v>52</v>
+      </c>
+      <c r="M7">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -11959,7 +11782,7 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -11985,7 +11808,7 @@
         <v>8</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>6</v>
@@ -12951,7 +12774,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -13014,27 +12837,33 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
@@ -13043,41 +12872,68 @@
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -13086,63 +12942,28 @@
         <v>3</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
-        <v>7</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
-      <c r="M7">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -13723,6 +13544,9 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
       <c r="F3">
         <v>1</v>
       </c>
@@ -13787,7 +13611,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -14038,7 +13862,7 @@
 
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -14048,9 +13872,10 @@
     <col min="5" max="5" width="4.7109375" customWidth="1"/>
     <col min="6" max="6" width="4.7109375" customWidth="1"/>
     <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14067,13 +13892,16 @@
         <v>2019</v>
       </c>
       <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
         <v>2024</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -14084,7 +13912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -14095,21 +13923,24 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -14126,9 +13957,12 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
         <v>2</v>
       </c>
     </row>
@@ -14516,10 +14350,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -14580,36 +14414,27 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
+      <c r="D3">
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -14618,13 +14443,10 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -14632,89 +14454,94 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7">
         <v>7</v>
       </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>10</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -16088,6 +15915,9 @@
       <c r="H2">
         <v>3</v>
       </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
       <c r="K2">
         <v>1</v>
       </c>
@@ -16193,7 +16023,7 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -16215,7 +16045,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -16279,147 +16109,197 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
       <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>16</v>
+      </c>
+      <c r="G6">
         <v>11</v>
       </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
       <c r="H6">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="L6">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>27</v>
+      </c>
+      <c r="F7">
+        <v>36</v>
+      </c>
+      <c r="G7">
+        <v>19</v>
+      </c>
+      <c r="H7">
+        <v>25</v>
+      </c>
+      <c r="I7">
+        <v>29</v>
+      </c>
+      <c r="J7">
+        <v>30</v>
+      </c>
+      <c r="K7">
+        <v>48</v>
+      </c>
+      <c r="L7">
+        <v>44</v>
+      </c>
+      <c r="M7">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -16999,7 +16879,7 @@
 
 <file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -17011,9 +16891,10 @@
     <col min="7" max="7" width="4.7109375" customWidth="1"/>
     <col min="8" max="8" width="4.7109375" customWidth="1"/>
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -17021,70 +16902,76 @@
         <v>2015</v>
       </c>
       <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
         <v>2017</v>
       </c>
-      <c r="D1" s="1">
+      <c r="E1" s="1">
         <v>2018</v>
       </c>
-      <c r="E1" s="1">
+      <c r="F1" s="1">
         <v>2019</v>
       </c>
-      <c r="F1" s="1">
+      <c r="G1" s="1">
         <v>2020</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
         <v>2022</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
         <v>2023</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2024</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
       <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -17095,21 +16982,24 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
         <v>2</v>
       </c>
     </row>
@@ -17835,7 +17725,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2">
         <v>3</v>
@@ -17940,7 +17830,7 @@
         <v>18</v>
       </c>
       <c r="H5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I5">
         <v>16</v>
@@ -17981,7 +17871,7 @@
         <v>23</v>
       </c>
       <c r="H6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I6">
         <v>22</v>
@@ -18707,50 +18597,205 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
         <v>2016</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>10</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-ytd.xlsx
+++ b/output/cta-violent-crime-ytd.xlsx
@@ -9,17 +9,17 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="West Town" sheetId="3" r:id="rId3"/>
-    <sheet name="Englewood" sheetId="4" r:id="rId4"/>
-    <sheet name="Avondale" sheetId="5" r:id="rId5"/>
-    <sheet name="Douglas" sheetId="6" r:id="rId6"/>
-    <sheet name="Grand Crossing" sheetId="7" r:id="rId7"/>
+    <sheet name="Englewood" sheetId="3" r:id="rId3"/>
+    <sheet name="Avondale" sheetId="4" r:id="rId4"/>
+    <sheet name="Douglas" sheetId="5" r:id="rId5"/>
+    <sheet name="Grand Boulevard" sheetId="6" r:id="rId6"/>
+    <sheet name="West Town" sheetId="7" r:id="rId7"/>
     <sheet name="Austin" sheetId="8" r:id="rId8"/>
-    <sheet name="Grand Boulevard" sheetId="9" r:id="rId9"/>
-    <sheet name="Mount Greenwood" sheetId="10" r:id="rId10"/>
-    <sheet name="Humboldt Park" sheetId="11" r:id="rId11"/>
-    <sheet name="Garfield Park" sheetId="12" r:id="rId12"/>
-    <sheet name="Loop" sheetId="13" r:id="rId13"/>
+    <sheet name="Mount Greenwood" sheetId="9" r:id="rId9"/>
+    <sheet name="Humboldt Park" sheetId="10" r:id="rId10"/>
+    <sheet name="Garfield Park" sheetId="11" r:id="rId11"/>
+    <sheet name="Loop" sheetId="12" r:id="rId12"/>
+    <sheet name="Grand Crossing" sheetId="13" r:id="rId13"/>
     <sheet name="United Center" sheetId="14" r:id="rId14"/>
     <sheet name="Ashburn" sheetId="15" r:id="rId15"/>
     <sheet name="Rush &amp; Division" sheetId="16" r:id="rId16"/>
@@ -34,11 +34,11 @@
     <sheet name="South Chicago" sheetId="25" r:id="rId25"/>
     <sheet name="Roseland" sheetId="26" r:id="rId26"/>
     <sheet name="Fuller Park" sheetId="27" r:id="rId27"/>
-    <sheet name="O'Hare" sheetId="28" r:id="rId28"/>
-    <sheet name="Little Italy, UIC" sheetId="29" r:id="rId29"/>
-    <sheet name="Hyde Park" sheetId="30" r:id="rId30"/>
-    <sheet name="Calumet Heights" sheetId="31" r:id="rId31"/>
-    <sheet name="Kenwood" sheetId="32" r:id="rId32"/>
+    <sheet name="Little Italy, UIC" sheetId="28" r:id="rId28"/>
+    <sheet name="Hyde Park" sheetId="29" r:id="rId29"/>
+    <sheet name="Calumet Heights" sheetId="30" r:id="rId30"/>
+    <sheet name="Kenwood" sheetId="31" r:id="rId31"/>
+    <sheet name="O'Hare" sheetId="32" r:id="rId32"/>
     <sheet name="Chicago Lawn" sheetId="33" r:id="rId33"/>
     <sheet name="Wrigleyville" sheetId="34" r:id="rId34"/>
     <sheet name="Auburn Gresham" sheetId="35" r:id="rId35"/>
@@ -1101,59 +1101,6 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1362,6 +1309,261 @@
       </c>
       <c r="M6">
         <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>7</v>
+      </c>
+      <c r="J3">
+        <v>9</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>28</v>
+      </c>
+      <c r="F6">
+        <v>43</v>
+      </c>
+      <c r="G6">
+        <v>35</v>
+      </c>
+      <c r="H6">
+        <v>30</v>
+      </c>
+      <c r="I6">
+        <v>23</v>
+      </c>
+      <c r="J6">
+        <v>21</v>
+      </c>
+      <c r="K6">
+        <v>19</v>
+      </c>
+      <c r="L6">
+        <v>22</v>
+      </c>
+      <c r="M6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>37</v>
+      </c>
+      <c r="F7">
+        <v>50</v>
+      </c>
+      <c r="G7">
+        <v>43</v>
+      </c>
+      <c r="H7">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>35</v>
+      </c>
+      <c r="J7">
+        <v>31</v>
+      </c>
+      <c r="K7">
+        <v>35</v>
+      </c>
+      <c r="L7">
+        <v>32</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1434,106 +1636,127 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
       <c r="C3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="J3">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="M3">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I5">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -1542,40 +1765,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F6">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G6">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H6">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="I6">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="J6">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="K6">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="L6">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1583,40 +1806,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D7">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="F7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G7">
+        <v>61</v>
+      </c>
+      <c r="H7">
+        <v>59</v>
+      </c>
+      <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7">
+        <v>87</v>
+      </c>
+      <c r="K7">
+        <v>73</v>
+      </c>
+      <c r="L7">
+        <v>72</v>
+      </c>
+      <c r="M7">
         <v>43</v>
-      </c>
-      <c r="H7">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>35</v>
-      </c>
-      <c r="J7">
-        <v>31</v>
-      </c>
-      <c r="K7">
-        <v>35</v>
-      </c>
-      <c r="L7">
-        <v>32</v>
-      </c>
-      <c r="M7">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1690,13 +1913,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -1708,22 +1931,22 @@
         <v>4</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1731,85 +1954,73 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
         <v>10</v>
       </c>
-      <c r="I3">
-        <v>24</v>
-      </c>
-      <c r="J3">
-        <v>24</v>
-      </c>
-      <c r="K3">
-        <v>22</v>
-      </c>
       <c r="L3">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>4</v>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -1818,40 +2029,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H6">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="I6">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="J6">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="K6">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1859,40 +2070,40 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>27</v>
+      </c>
+      <c r="F7">
         <v>36</v>
       </c>
-      <c r="C7">
-        <v>41</v>
-      </c>
-      <c r="D7">
-        <v>58</v>
-      </c>
-      <c r="E7">
-        <v>56</v>
-      </c>
-      <c r="F7">
-        <v>55</v>
-      </c>
       <c r="G7">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="H7">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="J7">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="K7">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="L7">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="M7">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -8175,168 +8386,6 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8567,9 +8616,174 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -8632,29 +8846,32 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="D2">
         <v>3</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
       <c r="H2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2">
         <v>4</v>
@@ -8664,116 +8881,154 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
       <c r="J4">
         <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="L6">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>28</v>
+      </c>
+      <c r="C7">
+        <v>38</v>
+      </c>
+      <c r="D7">
+        <v>34</v>
+      </c>
+      <c r="E7">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>39</v>
+      </c>
+      <c r="G7">
+        <v>31</v>
+      </c>
+      <c r="H7">
+        <v>37</v>
+      </c>
+      <c r="I7">
+        <v>34</v>
+      </c>
+      <c r="J7">
+        <v>21</v>
+      </c>
+      <c r="K7">
+        <v>42</v>
+      </c>
+      <c r="L7">
+        <v>52</v>
+      </c>
+      <c r="M7">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -8782,171 +9037,6 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>5</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9109,7 +9199,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9218,6 +9308,168 @@
       </c>
       <c r="H6">
         <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -10587,7 +10839,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10650,189 +10902,133 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>3</v>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
       <c r="H2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>5</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>13</v>
-      </c>
       <c r="E3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
       <c r="K4">
         <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>28</v>
-      </c>
-      <c r="C7">
-        <v>38</v>
-      </c>
-      <c r="D7">
-        <v>34</v>
-      </c>
-      <c r="E7">
-        <v>23</v>
-      </c>
-      <c r="F7">
-        <v>39</v>
-      </c>
-      <c r="G7">
-        <v>31</v>
-      </c>
-      <c r="H7">
-        <v>37</v>
-      </c>
-      <c r="I7">
-        <v>34</v>
-      </c>
-      <c r="J7">
-        <v>21</v>
-      </c>
-      <c r="K7">
-        <v>42</v>
-      </c>
-      <c r="L7">
-        <v>52</v>
-      </c>
-      <c r="M7">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -12774,7 +12970,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12837,33 +13033,27 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3">
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="F3">
@@ -12872,68 +13062,41 @@
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K4">
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -12942,28 +13105,63 @@
         <v>3</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7">
         <v>7</v>
       </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -14350,10 +14548,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -14414,27 +14612,36 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="I2">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3">
-        <v>1</v>
+      <c r="B3">
+        <v>2</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -14443,10 +14650,13 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -14454,94 +14664,89 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4">
+        <v>4</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>4</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
-        <v>7</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
-      <c r="M7">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -16045,7 +16250,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -16109,197 +16314,147 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
         <v>11</v>
       </c>
-      <c r="H6">
-        <v>13</v>
-      </c>
-      <c r="I6">
-        <v>13</v>
-      </c>
-      <c r="J6">
-        <v>18</v>
-      </c>
-      <c r="K6">
-        <v>31</v>
-      </c>
-      <c r="L6">
-        <v>31</v>
-      </c>
       <c r="M6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>19</v>
-      </c>
-      <c r="C7">
-        <v>29</v>
-      </c>
-      <c r="D7">
-        <v>27</v>
-      </c>
-      <c r="E7">
-        <v>27</v>
-      </c>
-      <c r="F7">
-        <v>36</v>
-      </c>
-      <c r="G7">
-        <v>19</v>
-      </c>
-      <c r="H7">
-        <v>25</v>
-      </c>
-      <c r="I7">
-        <v>29</v>
-      </c>
-      <c r="J7">
-        <v>30</v>
-      </c>
-      <c r="K7">
-        <v>48</v>
-      </c>
-      <c r="L7">
-        <v>44</v>
-      </c>
-      <c r="M7">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -18597,205 +18752,50 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>10</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-ytd.xlsx
+++ b/output/cta-violent-crime-ytd.xlsx
@@ -9,17 +9,17 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Englewood" sheetId="3" r:id="rId3"/>
-    <sheet name="Avondale" sheetId="4" r:id="rId4"/>
-    <sheet name="Douglas" sheetId="5" r:id="rId5"/>
-    <sheet name="Grand Boulevard" sheetId="6" r:id="rId6"/>
-    <sheet name="West Town" sheetId="7" r:id="rId7"/>
+    <sheet name="West Town" sheetId="3" r:id="rId3"/>
+    <sheet name="Englewood" sheetId="4" r:id="rId4"/>
+    <sheet name="Avondale" sheetId="5" r:id="rId5"/>
+    <sheet name="Douglas" sheetId="6" r:id="rId6"/>
+    <sheet name="Grand Crossing" sheetId="7" r:id="rId7"/>
     <sheet name="Austin" sheetId="8" r:id="rId8"/>
-    <sheet name="Mount Greenwood" sheetId="9" r:id="rId9"/>
-    <sheet name="Humboldt Park" sheetId="10" r:id="rId10"/>
-    <sheet name="Garfield Park" sheetId="11" r:id="rId11"/>
-    <sheet name="Loop" sheetId="12" r:id="rId12"/>
-    <sheet name="Grand Crossing" sheetId="13" r:id="rId13"/>
+    <sheet name="Grand Boulevard" sheetId="9" r:id="rId9"/>
+    <sheet name="Mount Greenwood" sheetId="10" r:id="rId10"/>
+    <sheet name="Humboldt Park" sheetId="11" r:id="rId11"/>
+    <sheet name="Garfield Park" sheetId="12" r:id="rId12"/>
+    <sheet name="Loop" sheetId="13" r:id="rId13"/>
     <sheet name="United Center" sheetId="14" r:id="rId14"/>
     <sheet name="Ashburn" sheetId="15" r:id="rId15"/>
     <sheet name="Rush &amp; Division" sheetId="16" r:id="rId16"/>
@@ -34,11 +34,11 @@
     <sheet name="South Chicago" sheetId="25" r:id="rId25"/>
     <sheet name="Roseland" sheetId="26" r:id="rId26"/>
     <sheet name="Fuller Park" sheetId="27" r:id="rId27"/>
-    <sheet name="Little Italy, UIC" sheetId="28" r:id="rId28"/>
-    <sheet name="Hyde Park" sheetId="29" r:id="rId29"/>
-    <sheet name="Calumet Heights" sheetId="30" r:id="rId30"/>
-    <sheet name="Kenwood" sheetId="31" r:id="rId31"/>
-    <sheet name="O'Hare" sheetId="32" r:id="rId32"/>
+    <sheet name="O'Hare" sheetId="28" r:id="rId28"/>
+    <sheet name="Little Italy, UIC" sheetId="29" r:id="rId29"/>
+    <sheet name="Hyde Park" sheetId="30" r:id="rId30"/>
+    <sheet name="Calumet Heights" sheetId="31" r:id="rId31"/>
+    <sheet name="Kenwood" sheetId="32" r:id="rId32"/>
     <sheet name="Chicago Lawn" sheetId="33" r:id="rId33"/>
     <sheet name="Wrigleyville" sheetId="34" r:id="rId34"/>
     <sheet name="Auburn Gresham" sheetId="35" r:id="rId35"/>
@@ -1101,6 +1101,59 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1309,261 +1362,6 @@
       </c>
       <c r="M6">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>6</v>
-      </c>
-      <c r="E2">
-        <v>6</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>7</v>
-      </c>
-      <c r="J3">
-        <v>9</v>
-      </c>
-      <c r="K3">
-        <v>12</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
-      <c r="M3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>22</v>
-      </c>
-      <c r="D6">
-        <v>30</v>
-      </c>
-      <c r="E6">
-        <v>28</v>
-      </c>
-      <c r="F6">
-        <v>43</v>
-      </c>
-      <c r="G6">
-        <v>35</v>
-      </c>
-      <c r="H6">
-        <v>30</v>
-      </c>
-      <c r="I6">
-        <v>23</v>
-      </c>
-      <c r="J6">
-        <v>21</v>
-      </c>
-      <c r="K6">
-        <v>19</v>
-      </c>
-      <c r="L6">
-        <v>22</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>40</v>
-      </c>
-      <c r="E7">
-        <v>37</v>
-      </c>
-      <c r="F7">
-        <v>50</v>
-      </c>
-      <c r="G7">
-        <v>43</v>
-      </c>
-      <c r="H7">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>35</v>
-      </c>
-      <c r="J7">
-        <v>31</v>
-      </c>
-      <c r="K7">
-        <v>35</v>
-      </c>
-      <c r="L7">
-        <v>32</v>
-      </c>
-      <c r="M7">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1636,127 +1434,106 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>7</v>
+      </c>
+      <c r="J3">
         <v>9</v>
       </c>
-      <c r="C3">
-        <v>11</v>
-      </c>
-      <c r="D3">
-        <v>15</v>
-      </c>
-      <c r="E3">
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
         <v>9</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>14</v>
-      </c>
-      <c r="H3">
-        <v>10</v>
-      </c>
-      <c r="I3">
-        <v>24</v>
-      </c>
-      <c r="J3">
-        <v>24</v>
-      </c>
-      <c r="K3">
-        <v>22</v>
-      </c>
-      <c r="L3">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
         <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>4</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -1765,40 +1542,40 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
         <v>22</v>
       </c>
-      <c r="C6">
-        <v>26</v>
-      </c>
       <c r="D6">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G6">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H6">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I6">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="J6">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="K6">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="L6">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1806,40 +1583,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D7">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="E7">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G7">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="H7">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="J7">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="K7">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="L7">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="M7">
-        <v>43</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1913,13 +1690,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -1931,22 +1708,22 @@
         <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1954,73 +1731,85 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3">
+        <v>9</v>
+      </c>
+      <c r="G3">
         <v>14</v>
       </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
       <c r="H3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
       </c>
       <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -2029,40 +1818,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="H6">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="J6">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="K6">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2070,40 +1859,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="G7">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="H7">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="I7">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="J7">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="K7">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="L7">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="M7">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -8386,6 +8175,168 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8616,7 +8567,221 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>11</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>11</v>
+      </c>
+      <c r="M6">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8781,262 +8946,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-      <c r="H2">
-        <v>10</v>
-      </c>
-      <c r="I2">
-        <v>6</v>
-      </c>
-      <c r="J2">
-        <v>5</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>13</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>11</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>14</v>
-      </c>
-      <c r="L3">
-        <v>14</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>26</v>
-      </c>
-      <c r="C6">
-        <v>34</v>
-      </c>
-      <c r="D6">
-        <v>18</v>
-      </c>
-      <c r="E6">
-        <v>16</v>
-      </c>
-      <c r="F6">
-        <v>28</v>
-      </c>
-      <c r="G6">
-        <v>23</v>
-      </c>
-      <c r="H6">
-        <v>22</v>
-      </c>
-      <c r="I6">
-        <v>16</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>25</v>
-      </c>
-      <c r="L6">
-        <v>33</v>
-      </c>
-      <c r="M6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>28</v>
-      </c>
-      <c r="C7">
-        <v>38</v>
-      </c>
-      <c r="D7">
-        <v>34</v>
-      </c>
-      <c r="E7">
-        <v>23</v>
-      </c>
-      <c r="F7">
-        <v>39</v>
-      </c>
-      <c r="G7">
-        <v>31</v>
-      </c>
-      <c r="H7">
-        <v>37</v>
-      </c>
-      <c r="I7">
-        <v>34</v>
-      </c>
-      <c r="J7">
-        <v>21</v>
-      </c>
-      <c r="K7">
-        <v>42</v>
-      </c>
-      <c r="L7">
-        <v>52</v>
-      </c>
-      <c r="M7">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9199,7 +9109,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9308,168 +9218,6 @@
       </c>
       <c r="H6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -10839,7 +10587,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10902,133 +10650,189 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
+      <c r="D2">
+        <v>3</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
       <c r="H2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>13</v>
+      </c>
       <c r="E3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>11</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>14</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
       <c r="K4">
         <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>28</v>
+      </c>
+      <c r="C7">
+        <v>38</v>
+      </c>
+      <c r="D7">
+        <v>34</v>
+      </c>
+      <c r="E7">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>39</v>
+      </c>
+      <c r="G7">
+        <v>31</v>
+      </c>
+      <c r="H7">
+        <v>37</v>
+      </c>
+      <c r="I7">
+        <v>34</v>
+      </c>
+      <c r="J7">
+        <v>21</v>
+      </c>
+      <c r="K7">
+        <v>42</v>
+      </c>
+      <c r="L7">
+        <v>52</v>
+      </c>
+      <c r="M7">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -12970,7 +12774,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -13033,27 +12837,33 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
@@ -13062,41 +12872,68 @@
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -13105,63 +12942,28 @@
         <v>3</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
-        <v>7</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
-      <c r="M7">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -14548,10 +14350,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -14612,36 +14414,27 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
+      <c r="D3">
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -14650,13 +14443,10 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -14664,89 +14454,94 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7">
         <v>7</v>
       </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>10</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -16250,7 +16045,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -16314,147 +16109,197 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
       <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>16</v>
+      </c>
+      <c r="G6">
         <v>11</v>
       </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
       <c r="H6">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="L6">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>27</v>
+      </c>
+      <c r="F7">
+        <v>36</v>
+      </c>
+      <c r="G7">
+        <v>19</v>
+      </c>
+      <c r="H7">
+        <v>25</v>
+      </c>
+      <c r="I7">
+        <v>29</v>
+      </c>
+      <c r="J7">
+        <v>30</v>
+      </c>
+      <c r="K7">
+        <v>48</v>
+      </c>
+      <c r="L7">
+        <v>44</v>
+      </c>
+      <c r="M7">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -18752,50 +18597,205 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
         <v>2016</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>10</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-ytd.xlsx
+++ b/output/cta-violent-crime-ytd.xlsx
@@ -9,17 +9,17 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Englewood" sheetId="3" r:id="rId3"/>
-    <sheet name="Avondale" sheetId="4" r:id="rId4"/>
-    <sheet name="Douglas" sheetId="5" r:id="rId5"/>
-    <sheet name="Grand Boulevard" sheetId="6" r:id="rId6"/>
-    <sheet name="West Town" sheetId="7" r:id="rId7"/>
+    <sheet name="West Town" sheetId="3" r:id="rId3"/>
+    <sheet name="Englewood" sheetId="4" r:id="rId4"/>
+    <sheet name="Avondale" sheetId="5" r:id="rId5"/>
+    <sheet name="Douglas" sheetId="6" r:id="rId6"/>
+    <sheet name="Grand Crossing" sheetId="7" r:id="rId7"/>
     <sheet name="Austin" sheetId="8" r:id="rId8"/>
-    <sheet name="Mount Greenwood" sheetId="9" r:id="rId9"/>
-    <sheet name="Humboldt Park" sheetId="10" r:id="rId10"/>
-    <sheet name="Garfield Park" sheetId="11" r:id="rId11"/>
-    <sheet name="Loop" sheetId="12" r:id="rId12"/>
-    <sheet name="Grand Crossing" sheetId="13" r:id="rId13"/>
+    <sheet name="Grand Boulevard" sheetId="9" r:id="rId9"/>
+    <sheet name="Mount Greenwood" sheetId="10" r:id="rId10"/>
+    <sheet name="Humboldt Park" sheetId="11" r:id="rId11"/>
+    <sheet name="Garfield Park" sheetId="12" r:id="rId12"/>
+    <sheet name="Loop" sheetId="13" r:id="rId13"/>
     <sheet name="United Center" sheetId="14" r:id="rId14"/>
     <sheet name="Ashburn" sheetId="15" r:id="rId15"/>
     <sheet name="Rush &amp; Division" sheetId="16" r:id="rId16"/>
@@ -34,11 +34,11 @@
     <sheet name="South Chicago" sheetId="25" r:id="rId25"/>
     <sheet name="Roseland" sheetId="26" r:id="rId26"/>
     <sheet name="Fuller Park" sheetId="27" r:id="rId27"/>
-    <sheet name="Little Italy, UIC" sheetId="28" r:id="rId28"/>
-    <sheet name="Hyde Park" sheetId="29" r:id="rId29"/>
-    <sheet name="Calumet Heights" sheetId="30" r:id="rId30"/>
-    <sheet name="Kenwood" sheetId="31" r:id="rId31"/>
-    <sheet name="O'Hare" sheetId="32" r:id="rId32"/>
+    <sheet name="O'Hare" sheetId="28" r:id="rId28"/>
+    <sheet name="Little Italy, UIC" sheetId="29" r:id="rId29"/>
+    <sheet name="Hyde Park" sheetId="30" r:id="rId30"/>
+    <sheet name="Calumet Heights" sheetId="31" r:id="rId31"/>
+    <sheet name="Kenwood" sheetId="32" r:id="rId32"/>
     <sheet name="Chicago Lawn" sheetId="33" r:id="rId33"/>
     <sheet name="Wrigleyville" sheetId="34" r:id="rId34"/>
     <sheet name="Auburn Gresham" sheetId="35" r:id="rId35"/>
@@ -50,18 +50,18 @@
     <sheet name="Chinatown" sheetId="41" r:id="rId41"/>
     <sheet name="Edgewater" sheetId="42" r:id="rId42"/>
     <sheet name="Lower West Side" sheetId="43" r:id="rId43"/>
-    <sheet name="Washington Heights" sheetId="44" r:id="rId44"/>
-    <sheet name="Brighton Park" sheetId="45" r:id="rId45"/>
-    <sheet name="Greektown" sheetId="46" r:id="rId46"/>
-    <sheet name="North Lawndale" sheetId="47" r:id="rId47"/>
-    <sheet name="West Loop" sheetId="48" r:id="rId48"/>
-    <sheet name="West Pullman" sheetId="49" r:id="rId49"/>
-    <sheet name="Belmont Cragin" sheetId="50" r:id="rId50"/>
-    <sheet name="Bucktown" sheetId="51" r:id="rId51"/>
-    <sheet name="Little Village" sheetId="52" r:id="rId52"/>
-    <sheet name="Archer Heights" sheetId="53" r:id="rId53"/>
-    <sheet name="Albany Park" sheetId="54" r:id="rId54"/>
-    <sheet name="Woodlawn" sheetId="55" r:id="rId55"/>
+    <sheet name="Brighton Park" sheetId="44" r:id="rId44"/>
+    <sheet name="Greektown" sheetId="45" r:id="rId45"/>
+    <sheet name="North Lawndale" sheetId="46" r:id="rId46"/>
+    <sheet name="West Loop" sheetId="47" r:id="rId47"/>
+    <sheet name="Belmont Cragin" sheetId="48" r:id="rId48"/>
+    <sheet name="New City" sheetId="49" r:id="rId49"/>
+    <sheet name="Woodlawn" sheetId="50" r:id="rId50"/>
+    <sheet name="West Pullman" sheetId="51" r:id="rId51"/>
+    <sheet name="Bucktown" sheetId="52" r:id="rId52"/>
+    <sheet name="Little Village" sheetId="53" r:id="rId53"/>
+    <sheet name="Archer Heights" sheetId="54" r:id="rId54"/>
+    <sheet name="Albany Park" sheetId="55" r:id="rId55"/>
     <sheet name="East Side" sheetId="56" r:id="rId56"/>
     <sheet name="South Deering" sheetId="57" r:id="rId57"/>
     <sheet name="West Elsdon" sheetId="58" r:id="rId58"/>
@@ -69,16 +69,16 @@
     <sheet name="Lincoln Park" sheetId="60" r:id="rId60"/>
     <sheet name="Avalon Park" sheetId="61" r:id="rId61"/>
     <sheet name="Streeterville" sheetId="62" r:id="rId62"/>
-    <sheet name="New City" sheetId="63" r:id="rId63"/>
-    <sheet name="Portage Park" sheetId="64" r:id="rId64"/>
-    <sheet name="Lincoln Square" sheetId="65" r:id="rId65"/>
-    <sheet name="Irving Park" sheetId="66" r:id="rId66"/>
-    <sheet name="North Park" sheetId="67" r:id="rId67"/>
-    <sheet name="Printers Row" sheetId="68" r:id="rId68"/>
-    <sheet name="Jefferson Park" sheetId="69" r:id="rId69"/>
-    <sheet name="Logan Square" sheetId="70" r:id="rId70"/>
-    <sheet name="Mckinley Park" sheetId="71" r:id="rId71"/>
-    <sheet name="Old Town" sheetId="72" r:id="rId72"/>
+    <sheet name="Portage Park" sheetId="63" r:id="rId63"/>
+    <sheet name="Lincoln Square" sheetId="64" r:id="rId64"/>
+    <sheet name="Irving Park" sheetId="65" r:id="rId65"/>
+    <sheet name="North Park" sheetId="66" r:id="rId66"/>
+    <sheet name="Printers Row" sheetId="67" r:id="rId67"/>
+    <sheet name="Jefferson Park" sheetId="68" r:id="rId68"/>
+    <sheet name="Logan Square" sheetId="69" r:id="rId69"/>
+    <sheet name="Mckinley Park" sheetId="70" r:id="rId70"/>
+    <sheet name="Old Town" sheetId="71" r:id="rId71"/>
+    <sheet name="Washington Heights" sheetId="72" r:id="rId72"/>
     <sheet name="Riverdale" sheetId="73" r:id="rId73"/>
     <sheet name="Montclare" sheetId="74" r:id="rId74"/>
     <sheet name="Morgan Park" sheetId="75" r:id="rId75"/>
@@ -865,7 +865,7 @@
         <v>65</v>
       </c>
       <c r="E2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2">
         <v>63</v>
@@ -883,13 +883,13 @@
         <v>84</v>
       </c>
       <c r="K2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L2">
         <v>102</v>
       </c>
       <c r="M2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -900,7 +900,7 @@
         <v>60</v>
       </c>
       <c r="C3">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D3">
         <v>96</v>
@@ -912,22 +912,22 @@
         <v>93</v>
       </c>
       <c r="G3">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H3">
         <v>95</v>
       </c>
       <c r="I3">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J3">
         <v>148</v>
       </c>
       <c r="K3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L3">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M3">
         <v>147</v>
@@ -1017,40 +1017,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C6">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D6">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E6">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F6">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G6">
         <v>350</v>
       </c>
       <c r="H6">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I6">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J6">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K6">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L6">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="M6">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1058,40 +1058,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C7">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D7">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="F7">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="G7">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="H7">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="I7">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="J7">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="K7">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="L7">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="M7">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -1100,6 +1100,59 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1309,261 +1362,6 @@
       </c>
       <c r="M6">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>6</v>
-      </c>
-      <c r="E2">
-        <v>6</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>7</v>
-      </c>
-      <c r="J3">
-        <v>9</v>
-      </c>
-      <c r="K3">
-        <v>12</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
-      <c r="M3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>22</v>
-      </c>
-      <c r="D6">
-        <v>30</v>
-      </c>
-      <c r="E6">
-        <v>28</v>
-      </c>
-      <c r="F6">
-        <v>43</v>
-      </c>
-      <c r="G6">
-        <v>35</v>
-      </c>
-      <c r="H6">
-        <v>30</v>
-      </c>
-      <c r="I6">
-        <v>23</v>
-      </c>
-      <c r="J6">
-        <v>21</v>
-      </c>
-      <c r="K6">
-        <v>19</v>
-      </c>
-      <c r="L6">
-        <v>22</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>40</v>
-      </c>
-      <c r="E7">
-        <v>37</v>
-      </c>
-      <c r="F7">
-        <v>50</v>
-      </c>
-      <c r="G7">
-        <v>43</v>
-      </c>
-      <c r="H7">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>35</v>
-      </c>
-      <c r="J7">
-        <v>31</v>
-      </c>
-      <c r="K7">
-        <v>35</v>
-      </c>
-      <c r="L7">
-        <v>32</v>
-      </c>
-      <c r="M7">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1636,127 +1434,106 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>7</v>
+      </c>
+      <c r="J3">
         <v>9</v>
       </c>
-      <c r="C3">
-        <v>11</v>
-      </c>
-      <c r="D3">
-        <v>15</v>
-      </c>
-      <c r="E3">
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
         <v>9</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>14</v>
-      </c>
-      <c r="H3">
-        <v>10</v>
-      </c>
-      <c r="I3">
-        <v>24</v>
-      </c>
-      <c r="J3">
-        <v>24</v>
-      </c>
-      <c r="K3">
-        <v>22</v>
-      </c>
-      <c r="L3">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
         <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>4</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -1765,40 +1542,40 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
         <v>22</v>
       </c>
-      <c r="C6">
-        <v>26</v>
-      </c>
       <c r="D6">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G6">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H6">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I6">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="J6">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="K6">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="L6">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1806,40 +1583,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D7">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="E7">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G7">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="H7">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="J7">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="K7">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="L7">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="M7">
-        <v>43</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1913,13 +1690,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -1931,22 +1708,22 @@
         <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1954,73 +1731,85 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3">
+        <v>9</v>
+      </c>
+      <c r="G3">
         <v>14</v>
       </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
       <c r="H3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
       </c>
       <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -2029,40 +1818,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="H6">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="J6">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="K6">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L6">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2070,40 +1859,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="G7">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="H7">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="I7">
-        <v>29</v>
+        <v>102</v>
       </c>
       <c r="J7">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="K7">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="L7">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="M7">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2417,7 +2206,7 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -2472,7 +2261,7 @@
         <v>4</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -3484,7 +3273,7 @@
         <v>13</v>
       </c>
       <c r="J5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -3522,7 +3311,7 @@
         <v>4</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>2</v>
@@ -3697,7 +3486,7 @@
         <v>1</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -3978,7 +3767,7 @@
         <v>7</v>
       </c>
       <c r="K21">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L21">
         <v>18</v>
@@ -4042,7 +3831,7 @@
         <v>4</v>
       </c>
       <c r="I23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>3</v>
@@ -4128,7 +3917,7 @@
         <v>8</v>
       </c>
       <c r="G27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H27">
         <v>11</v>
@@ -4157,7 +3946,7 @@
         <v>28</v>
       </c>
       <c r="C28">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D28">
         <v>34</v>
@@ -4225,7 +4014,7 @@
         <v>14</v>
       </c>
       <c r="L29">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M29">
         <v>10</v>
@@ -4303,7 +4092,7 @@
         <v>37</v>
       </c>
       <c r="F32">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G32">
         <v>43</v>
@@ -4321,7 +4110,7 @@
         <v>35</v>
       </c>
       <c r="L32">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M32">
         <v>27</v>
@@ -4401,7 +4190,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F36">
         <v>36</v>
@@ -4410,7 +4199,7 @@
         <v>19</v>
       </c>
       <c r="H36">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I36">
         <v>29</v>
@@ -4867,7 +4656,7 @@
         <v>11</v>
       </c>
       <c r="J50">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K50">
         <v>22</v>
@@ -4969,7 +4758,7 @@
         <v>58</v>
       </c>
       <c r="E53">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F53">
         <v>55</v>
@@ -4981,7 +4770,7 @@
         <v>59</v>
       </c>
       <c r="I53">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J53">
         <v>87</v>
@@ -4990,7 +4779,7 @@
         <v>73</v>
       </c>
       <c r="L53">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M53">
         <v>43</v>
@@ -5265,6 +5054,9 @@
         <v>6</v>
       </c>
       <c r="L63">
+        <v>2</v>
+      </c>
+      <c r="M63">
         <v>1</v>
       </c>
     </row>
@@ -5308,7 +5100,7 @@
         <v>24</v>
       </c>
       <c r="G65">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H65">
         <v>10</v>
@@ -5607,7 +5399,7 @@
         <v>81</v>
       </c>
       <c r="B75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -5648,7 +5440,7 @@
         <v>10</v>
       </c>
       <c r="E76">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F76">
         <v>15</v>
@@ -5669,7 +5461,7 @@
         <v>19</v>
       </c>
       <c r="L76">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M76">
         <v>9</v>
@@ -5692,7 +5484,7 @@
         <v>21</v>
       </c>
       <c r="F77">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G77">
         <v>16</v>
@@ -5830,7 +5622,7 @@
         <v>3</v>
       </c>
       <c r="K80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L80">
         <v>12</v>
@@ -6001,7 +5793,7 @@
         <v>6</v>
       </c>
       <c r="C86">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D86">
         <v>2</v>
@@ -6069,7 +5861,7 @@
         <v>1</v>
       </c>
       <c r="M87">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -6156,7 +5948,7 @@
         <v>96</v>
       </c>
       <c r="D90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I90">
         <v>2</v>
@@ -6194,13 +5986,13 @@
         <v>3</v>
       </c>
       <c r="K91">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L91">
         <v>8</v>
       </c>
       <c r="M91">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -6296,7 +6088,7 @@
         <v>4</v>
       </c>
       <c r="K94">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L94">
         <v>11</v>
@@ -6378,7 +6170,7 @@
         <v>3</v>
       </c>
       <c r="M96">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -6424,40 +6216,40 @@
         <v>6</v>
       </c>
       <c r="B98">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C98">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D98">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E98">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="F98">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="G98">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="H98">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="I98">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="J98">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="K98">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="L98">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="M98">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -7131,6 +6923,9 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
       <c r="D3">
         <v>1</v>
       </c>
@@ -7216,7 +7011,7 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -7654,7 +7449,7 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K5">
         <v>7</v>
@@ -7695,7 +7490,7 @@
         <v>13</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -7793,7 +7588,7 @@
         <v>2</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>2</v>
@@ -7901,7 +7696,7 @@
         <v>3</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>12</v>
@@ -8097,7 +7892,7 @@
         <v>13</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6">
         <v>11</v>
@@ -8138,7 +7933,7 @@
         <v>21</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>16</v>
@@ -8332,7 +8127,7 @@
         <v>10</v>
       </c>
       <c r="L5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M5">
         <v>7</v>
@@ -8373,7 +8168,7 @@
         <v>14</v>
       </c>
       <c r="L6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M6">
         <v>10</v>
@@ -8385,6 +8180,168 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8558,7 +8515,7 @@
         <v>7</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K5">
         <v>14</v>
@@ -8599,7 +8556,7 @@
         <v>11</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>22</v>
@@ -8616,7 +8573,221 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>11</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>11</v>
+      </c>
+      <c r="M6">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8781,262 +8952,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-      <c r="H2">
-        <v>10</v>
-      </c>
-      <c r="I2">
-        <v>6</v>
-      </c>
-      <c r="J2">
-        <v>5</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>13</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>11</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>14</v>
-      </c>
-      <c r="L3">
-        <v>14</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>26</v>
-      </c>
-      <c r="C6">
-        <v>34</v>
-      </c>
-      <c r="D6">
-        <v>18</v>
-      </c>
-      <c r="E6">
-        <v>16</v>
-      </c>
-      <c r="F6">
-        <v>28</v>
-      </c>
-      <c r="G6">
-        <v>23</v>
-      </c>
-      <c r="H6">
-        <v>22</v>
-      </c>
-      <c r="I6">
-        <v>16</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>25</v>
-      </c>
-      <c r="L6">
-        <v>33</v>
-      </c>
-      <c r="M6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>28</v>
-      </c>
-      <c r="C7">
-        <v>38</v>
-      </c>
-      <c r="D7">
-        <v>34</v>
-      </c>
-      <c r="E7">
-        <v>23</v>
-      </c>
-      <c r="F7">
-        <v>39</v>
-      </c>
-      <c r="G7">
-        <v>31</v>
-      </c>
-      <c r="H7">
-        <v>37</v>
-      </c>
-      <c r="I7">
-        <v>34</v>
-      </c>
-      <c r="J7">
-        <v>21</v>
-      </c>
-      <c r="K7">
-        <v>42</v>
-      </c>
-      <c r="L7">
-        <v>52</v>
-      </c>
-      <c r="M7">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9199,7 +9115,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9308,168 +9224,6 @@
       </c>
       <c r="H6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -10439,7 +10193,7 @@
         <v>7</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5">
         <v>13</v>
@@ -10460,7 +10214,7 @@
         <v>9</v>
       </c>
       <c r="L5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M5">
         <v>4</v>
@@ -10480,7 +10234,7 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6">
         <v>15</v>
@@ -10501,7 +10255,7 @@
         <v>19</v>
       </c>
       <c r="L6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M6">
         <v>9</v>
@@ -10839,7 +10593,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10902,133 +10656,189 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
+      <c r="D2">
+        <v>3</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
       <c r="H2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>13</v>
+      </c>
       <c r="E3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>11</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>14</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
       <c r="K4">
         <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>28</v>
+      </c>
+      <c r="C7">
+        <v>39</v>
+      </c>
+      <c r="D7">
+        <v>34</v>
+      </c>
+      <c r="E7">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>39</v>
+      </c>
+      <c r="G7">
+        <v>31</v>
+      </c>
+      <c r="H7">
+        <v>37</v>
+      </c>
+      <c r="I7">
+        <v>34</v>
+      </c>
+      <c r="J7">
+        <v>21</v>
+      </c>
+      <c r="K7">
+        <v>42</v>
+      </c>
+      <c r="L7">
+        <v>52</v>
+      </c>
+      <c r="M7">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -11413,7 +11223,7 @@
         <v>4</v>
       </c>
       <c r="K6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L6">
         <v>13</v>
@@ -11454,7 +11264,7 @@
         <v>7</v>
       </c>
       <c r="K7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L7">
         <v>18</v>
@@ -11572,7 +11382,7 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -11656,7 +11466,7 @@
         <v>8</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>11</v>
@@ -11872,10 +11682,10 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -11885,11 +11695,9 @@
     <col min="8" max="8" width="4.7109375" customWidth="1"/>
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11897,137 +11705,124 @@
         <v>2015</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E1" s="1">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="G1" s="1">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="H1" s="1">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="I1" s="1">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="I3">
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
         <v>1</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>5</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
         <v>2</v>
       </c>
     </row>
@@ -12058,13 +11853,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="C1" s="1">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D1" s="1">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E1" s="1">
         <v>2020</v>
@@ -12089,13 +11884,10 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="J2">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
     </row>
@@ -12103,22 +11895,7 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="J3">
         <v>1</v>
       </c>
     </row>
@@ -12126,7 +11903,7 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4">
+      <c r="C4">
         <v>1</v>
       </c>
     </row>
@@ -12135,19 +11912,28 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
       </c>
       <c r="I5">
         <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -12158,19 +11944,19 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -12188,148 +11974,6 @@
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12448,7 +12092,7 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -12538,7 +12182,7 @@
         <v>24</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6">
         <v>10</v>
@@ -12564,7 +12208,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12680,7 +12324,7 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
@@ -12743,7 +12387,7 @@
         <v>4</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12778,13 +12422,142 @@
         <v>3</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>8</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -12793,6 +12566,591 @@
 </file>
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12968,334 +13326,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
-        <v>7</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
-      <c r="M7">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13406,7 +13437,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13567,7 +13598,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13665,7 +13696,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13837,220 +13868,6 @@
       </c>
       <c r="K6">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>9</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>13</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>7</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -14548,10 +14365,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -14612,36 +14429,27 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
+      <c r="D3">
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -14650,13 +14458,10 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -14664,89 +14469,94 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7">
         <v>7</v>
       </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>10</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -15149,168 +14959,6 @@
 
 <file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -15403,7 +15051,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15559,7 +15207,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15767,7 +15415,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15870,7 +15518,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16042,6 +15690,205 @@
       </c>
       <c r="M5">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -16114,17 +15961,20 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
       <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="K2">
-        <v>1</v>
+      <c r="J2">
+        <v>2</v>
       </c>
       <c r="L2">
         <v>3</v>
@@ -16134,22 +15984,25 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
       <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
       </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
         <v>2</v>
       </c>
       <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -16157,7 +16010,16 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I4">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -16169,37 +16031,37 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -16210,37 +16072,37 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -16250,7 +16112,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -16314,147 +16176,197 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
       <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>16</v>
+      </c>
+      <c r="G6">
         <v>11</v>
       </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
       <c r="H6">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="L6">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>28</v>
+      </c>
+      <c r="F7">
+        <v>36</v>
+      </c>
+      <c r="G7">
+        <v>19</v>
+      </c>
+      <c r="H7">
+        <v>26</v>
+      </c>
+      <c r="I7">
+        <v>29</v>
+      </c>
+      <c r="J7">
+        <v>30</v>
+      </c>
+      <c r="K7">
+        <v>48</v>
+      </c>
+      <c r="L7">
+        <v>44</v>
+      </c>
+      <c r="M7">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -16463,220 +16375,6 @@
 </file>
 
 <file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>7</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16826,7 +16524,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17025,6 +16723,172 @@
       </c>
       <c r="M5">
         <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -17108,7 +16972,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -17131,7 +16995,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -18220,7 +18084,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -18228,7 +18092,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -18752,50 +18616,205 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
         <v>2016</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>10</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-ytd.xlsx
+++ b/output/cta-violent-crime-ytd.xlsx
@@ -9,17 +9,17 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="West Town" sheetId="3" r:id="rId3"/>
-    <sheet name="Englewood" sheetId="4" r:id="rId4"/>
-    <sheet name="Avondale" sheetId="5" r:id="rId5"/>
-    <sheet name="Douglas" sheetId="6" r:id="rId6"/>
-    <sheet name="Grand Crossing" sheetId="7" r:id="rId7"/>
+    <sheet name="Englewood" sheetId="3" r:id="rId3"/>
+    <sheet name="Avondale" sheetId="4" r:id="rId4"/>
+    <sheet name="Douglas" sheetId="5" r:id="rId5"/>
+    <sheet name="Grand Boulevard" sheetId="6" r:id="rId6"/>
+    <sheet name="West Town" sheetId="7" r:id="rId7"/>
     <sheet name="Austin" sheetId="8" r:id="rId8"/>
-    <sheet name="Grand Boulevard" sheetId="9" r:id="rId9"/>
-    <sheet name="Mount Greenwood" sheetId="10" r:id="rId10"/>
-    <sheet name="Humboldt Park" sheetId="11" r:id="rId11"/>
-    <sheet name="Garfield Park" sheetId="12" r:id="rId12"/>
-    <sheet name="Loop" sheetId="13" r:id="rId13"/>
+    <sheet name="Mount Greenwood" sheetId="9" r:id="rId9"/>
+    <sheet name="Humboldt Park" sheetId="10" r:id="rId10"/>
+    <sheet name="Garfield Park" sheetId="11" r:id="rId11"/>
+    <sheet name="Loop" sheetId="12" r:id="rId12"/>
+    <sheet name="Grand Crossing" sheetId="13" r:id="rId13"/>
     <sheet name="United Center" sheetId="14" r:id="rId14"/>
     <sheet name="Ashburn" sheetId="15" r:id="rId15"/>
     <sheet name="Rush &amp; Division" sheetId="16" r:id="rId16"/>
@@ -34,11 +34,11 @@
     <sheet name="South Chicago" sheetId="25" r:id="rId25"/>
     <sheet name="Roseland" sheetId="26" r:id="rId26"/>
     <sheet name="Fuller Park" sheetId="27" r:id="rId27"/>
-    <sheet name="O'Hare" sheetId="28" r:id="rId28"/>
-    <sheet name="Little Italy, UIC" sheetId="29" r:id="rId29"/>
-    <sheet name="Hyde Park" sheetId="30" r:id="rId30"/>
-    <sheet name="Calumet Heights" sheetId="31" r:id="rId31"/>
-    <sheet name="Kenwood" sheetId="32" r:id="rId32"/>
+    <sheet name="Little Italy, UIC" sheetId="28" r:id="rId28"/>
+    <sheet name="Hyde Park" sheetId="29" r:id="rId29"/>
+    <sheet name="Calumet Heights" sheetId="30" r:id="rId30"/>
+    <sheet name="Kenwood" sheetId="31" r:id="rId31"/>
+    <sheet name="O'Hare" sheetId="32" r:id="rId32"/>
     <sheet name="Chicago Lawn" sheetId="33" r:id="rId33"/>
     <sheet name="Wrigleyville" sheetId="34" r:id="rId34"/>
     <sheet name="Auburn Gresham" sheetId="35" r:id="rId35"/>
@@ -1101,59 +1101,6 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1362,6 +1309,261 @@
       </c>
       <c r="M6">
         <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>7</v>
+      </c>
+      <c r="J3">
+        <v>9</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>28</v>
+      </c>
+      <c r="F6">
+        <v>44</v>
+      </c>
+      <c r="G6">
+        <v>35</v>
+      </c>
+      <c r="H6">
+        <v>30</v>
+      </c>
+      <c r="I6">
+        <v>23</v>
+      </c>
+      <c r="J6">
+        <v>21</v>
+      </c>
+      <c r="K6">
+        <v>19</v>
+      </c>
+      <c r="L6">
+        <v>24</v>
+      </c>
+      <c r="M6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>37</v>
+      </c>
+      <c r="F7">
+        <v>51</v>
+      </c>
+      <c r="G7">
+        <v>43</v>
+      </c>
+      <c r="H7">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>35</v>
+      </c>
+      <c r="J7">
+        <v>31</v>
+      </c>
+      <c r="K7">
+        <v>35</v>
+      </c>
+      <c r="L7">
+        <v>34</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1434,106 +1636,127 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
       <c r="C3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="J3">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="M3">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I5">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -1542,40 +1765,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="F6">
+        <v>41</v>
+      </c>
+      <c r="G6">
+        <v>42</v>
+      </c>
+      <c r="H6">
+        <v>41</v>
+      </c>
+      <c r="I6">
+        <v>64</v>
+      </c>
+      <c r="J6">
         <v>44</v>
       </c>
-      <c r="G6">
-        <v>35</v>
-      </c>
-      <c r="H6">
-        <v>30</v>
-      </c>
-      <c r="I6">
-        <v>23</v>
-      </c>
-      <c r="J6">
-        <v>21</v>
-      </c>
       <c r="K6">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="L6">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1583,40 +1806,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D7">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="F7">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G7">
+        <v>61</v>
+      </c>
+      <c r="H7">
+        <v>59</v>
+      </c>
+      <c r="I7">
+        <v>102</v>
+      </c>
+      <c r="J7">
+        <v>87</v>
+      </c>
+      <c r="K7">
+        <v>73</v>
+      </c>
+      <c r="L7">
+        <v>74</v>
+      </c>
+      <c r="M7">
         <v>43</v>
-      </c>
-      <c r="H7">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>35</v>
-      </c>
-      <c r="J7">
-        <v>31</v>
-      </c>
-      <c r="K7">
-        <v>35</v>
-      </c>
-      <c r="L7">
-        <v>34</v>
-      </c>
-      <c r="M7">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1690,16 +1913,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -1708,22 +1931,22 @@
         <v>4</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1731,85 +1954,73 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
         <v>10</v>
       </c>
-      <c r="I3">
-        <v>25</v>
-      </c>
-      <c r="J3">
-        <v>24</v>
-      </c>
-      <c r="K3">
-        <v>22</v>
-      </c>
       <c r="L3">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>4</v>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -1818,40 +2029,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H6">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="I6">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="J6">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="K6">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L6">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1859,40 +2070,40 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>28</v>
+      </c>
+      <c r="F7">
         <v>36</v>
       </c>
-      <c r="C7">
-        <v>41</v>
-      </c>
-      <c r="D7">
-        <v>58</v>
-      </c>
-      <c r="E7">
-        <v>57</v>
-      </c>
-      <c r="F7">
-        <v>55</v>
-      </c>
       <c r="G7">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="H7">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="I7">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="J7">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="K7">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="L7">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="M7">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -8181,168 +8392,6 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8573,9 +8622,174 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -8638,29 +8852,32 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="D2">
         <v>3</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
       <c r="H2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2">
         <v>4</v>
@@ -8670,116 +8887,154 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
       <c r="J4">
         <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="L6">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>28</v>
+      </c>
+      <c r="C7">
+        <v>39</v>
+      </c>
+      <c r="D7">
+        <v>34</v>
+      </c>
+      <c r="E7">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>39</v>
+      </c>
+      <c r="G7">
+        <v>31</v>
+      </c>
+      <c r="H7">
+        <v>37</v>
+      </c>
+      <c r="I7">
+        <v>34</v>
+      </c>
+      <c r="J7">
+        <v>21</v>
+      </c>
+      <c r="K7">
+        <v>42</v>
+      </c>
+      <c r="L7">
+        <v>52</v>
+      </c>
+      <c r="M7">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -8788,171 +9043,6 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>5</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9115,7 +9205,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9224,6 +9314,168 @@
       </c>
       <c r="H6">
         <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -10593,7 +10845,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10656,189 +10908,133 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>3</v>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
       <c r="H2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>5</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>13</v>
-      </c>
       <c r="E3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
       <c r="K4">
         <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>28</v>
-      </c>
-      <c r="C7">
-        <v>39</v>
-      </c>
-      <c r="D7">
-        <v>34</v>
-      </c>
-      <c r="E7">
-        <v>23</v>
-      </c>
-      <c r="F7">
-        <v>39</v>
-      </c>
-      <c r="G7">
-        <v>31</v>
-      </c>
-      <c r="H7">
-        <v>37</v>
-      </c>
-      <c r="I7">
-        <v>34</v>
-      </c>
-      <c r="J7">
-        <v>21</v>
-      </c>
-      <c r="K7">
-        <v>42</v>
-      </c>
-      <c r="L7">
-        <v>52</v>
-      </c>
-      <c r="M7">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -12739,7 +12935,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12802,33 +12998,27 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3">
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="F3">
@@ -12837,68 +13027,41 @@
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K4">
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -12907,28 +13070,63 @@
         <v>3</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7">
         <v>7</v>
       </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -14365,10 +14563,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -14429,27 +14627,36 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="I2">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3">
-        <v>1</v>
+      <c r="B3">
+        <v>2</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -14458,10 +14665,13 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -14469,94 +14679,89 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4">
+        <v>4</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>4</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
-        <v>7</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
-      <c r="M7">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -16112,7 +16317,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -16176,197 +16381,147 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
         <v>11</v>
       </c>
-      <c r="H6">
-        <v>14</v>
-      </c>
-      <c r="I6">
-        <v>13</v>
-      </c>
-      <c r="J6">
-        <v>18</v>
-      </c>
-      <c r="K6">
-        <v>31</v>
-      </c>
-      <c r="L6">
-        <v>31</v>
-      </c>
       <c r="M6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>19</v>
-      </c>
-      <c r="C7">
-        <v>29</v>
-      </c>
-      <c r="D7">
-        <v>27</v>
-      </c>
-      <c r="E7">
-        <v>28</v>
-      </c>
-      <c r="F7">
-        <v>36</v>
-      </c>
-      <c r="G7">
-        <v>19</v>
-      </c>
-      <c r="H7">
-        <v>26</v>
-      </c>
-      <c r="I7">
-        <v>29</v>
-      </c>
-      <c r="J7">
-        <v>30</v>
-      </c>
-      <c r="K7">
-        <v>48</v>
-      </c>
-      <c r="L7">
-        <v>44</v>
-      </c>
-      <c r="M7">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -18616,205 +18771,50 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>10</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-ytd.xlsx
+++ b/output/cta-violent-crime-ytd.xlsx
@@ -874,7 +874,7 @@
         <v>65</v>
       </c>
       <c r="H2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I2">
         <v>82</v>
@@ -883,7 +883,7 @@
         <v>84</v>
       </c>
       <c r="K2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L2">
         <v>102</v>
@@ -903,7 +903,7 @@
         <v>63</v>
       </c>
       <c r="D3">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E3">
         <v>99</v>
@@ -924,13 +924,13 @@
         <v>148</v>
       </c>
       <c r="K3">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L3">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M3">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -965,7 +965,7 @@
         <v>16</v>
       </c>
       <c r="K4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L4">
         <v>16</v>
@@ -1023,10 +1023,10 @@
         <v>343</v>
       </c>
       <c r="D6">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E6">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F6">
         <v>390</v>
@@ -1035,22 +1035,22 @@
         <v>350</v>
       </c>
       <c r="H6">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="I6">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J6">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K6">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="L6">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M6">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1064,10 +1064,10 @@
         <v>461</v>
       </c>
       <c r="D7">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E7">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F7">
         <v>553</v>
@@ -1076,22 +1076,22 @@
         <v>507</v>
       </c>
       <c r="H7">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="I7">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="J7">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="K7">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="L7">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="M7">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -1423,7 +1423,7 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1516,7 +1516,7 @@
         <v>21</v>
       </c>
       <c r="K6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L6">
         <v>24</v>
@@ -1536,7 +1536,7 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E7">
         <v>37</v>
@@ -1557,7 +1557,7 @@
         <v>31</v>
       </c>
       <c r="K7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L7">
         <v>34</v>
@@ -1774,7 +1774,7 @@
         <v>33</v>
       </c>
       <c r="E6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F6">
         <v>41</v>
@@ -1783,10 +1783,10 @@
         <v>42</v>
       </c>
       <c r="H6">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I6">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J6">
         <v>44</v>
@@ -1815,7 +1815,7 @@
         <v>58</v>
       </c>
       <c r="E7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F7">
         <v>55</v>
@@ -1824,10 +1824,10 @@
         <v>61</v>
       </c>
       <c r="H7">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J7">
         <v>87</v>
@@ -2047,7 +2047,7 @@
         <v>11</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I6">
         <v>13</v>
@@ -2088,7 +2088,7 @@
         <v>19</v>
       </c>
       <c r="H7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I7">
         <v>29</v>
@@ -2633,7 +2633,7 @@
         <v>3</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5">
         <v>3</v>
@@ -2671,7 +2671,7 @@
         <v>4</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -3276,7 +3276,7 @@
         <v>3</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -3317,7 +3317,7 @@
         <v>3</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -3478,7 +3478,7 @@
         <v>4</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>13</v>
@@ -3601,13 +3601,13 @@
         <v>30</v>
       </c>
       <c r="K8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L8">
         <v>22</v>
       </c>
       <c r="M8">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3902,7 +3902,7 @@
         <v>19</v>
       </c>
       <c r="M19">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -4007,7 +4007,7 @@
         <v>1</v>
       </c>
       <c r="K22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22">
         <v>1</v>
@@ -4297,7 +4297,7 @@
         <v>25</v>
       </c>
       <c r="D32">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E32">
         <v>37</v>
@@ -4318,7 +4318,7 @@
         <v>31</v>
       </c>
       <c r="K32">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L32">
         <v>34</v>
@@ -4410,7 +4410,7 @@
         <v>19</v>
       </c>
       <c r="H36">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I36">
         <v>29</v>
@@ -4578,7 +4578,7 @@
         <v>2</v>
       </c>
       <c r="L42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M42">
         <v>2</v>
@@ -4616,7 +4616,7 @@
         <v>3</v>
       </c>
       <c r="K43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L43">
         <v>4</v>
@@ -4689,7 +4689,7 @@
         <v>4</v>
       </c>
       <c r="L45">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M45">
         <v>4</v>
@@ -4870,7 +4870,7 @@
         <v>10</v>
       </c>
       <c r="K50">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L50">
         <v>17</v>
@@ -4969,7 +4969,7 @@
         <v>58</v>
       </c>
       <c r="E53">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F53">
         <v>55</v>
@@ -4978,10 +4978,10 @@
         <v>61</v>
       </c>
       <c r="H53">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I53">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J53">
         <v>87</v>
@@ -5224,7 +5224,7 @@
         <v>4</v>
       </c>
       <c r="K62">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L62">
         <v>3</v>
@@ -5247,7 +5247,7 @@
         <v>3</v>
       </c>
       <c r="E63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F63">
         <v>4</v>
@@ -5314,7 +5314,7 @@
         <v>16</v>
       </c>
       <c r="H65">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I65">
         <v>19</v>
@@ -5474,7 +5474,7 @@
         <v>7</v>
       </c>
       <c r="K70">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L70">
         <v>6</v>
@@ -5701,13 +5701,13 @@
         <v>16</v>
       </c>
       <c r="H77">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I77">
         <v>34</v>
       </c>
       <c r="J77">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K77">
         <v>20</v>
@@ -5751,7 +5751,7 @@
         <v>4</v>
       </c>
       <c r="K78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L78">
         <v>3</v>
@@ -5795,7 +5795,7 @@
         <v>3</v>
       </c>
       <c r="L79">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M79">
         <v>3</v>
@@ -6159,7 +6159,7 @@
         <v>96</v>
       </c>
       <c r="D90">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I90">
         <v>2</v>
@@ -6357,7 +6357,7 @@
         <v>7</v>
       </c>
       <c r="E96">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F96">
         <v>4</v>
@@ -6433,10 +6433,10 @@
         <v>461</v>
       </c>
       <c r="D98">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E98">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F98">
         <v>553</v>
@@ -6445,22 +6445,22 @@
         <v>507</v>
       </c>
       <c r="H98">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="I98">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="J98">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="K98">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="L98">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="M98">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -7446,7 +7446,7 @@
         <v>12</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -7487,7 +7487,7 @@
         <v>19</v>
       </c>
       <c r="M6">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -7654,7 +7654,7 @@
         <v>4</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5">
         <v>10</v>
@@ -7695,7 +7695,7 @@
         <v>4</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>13</v>
@@ -8109,13 +8109,13 @@
         <v>11</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I6">
         <v>21</v>
       </c>
       <c r="J6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K6">
         <v>14</v>
@@ -8150,13 +8150,13 @@
         <v>16</v>
       </c>
       <c r="H7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I7">
         <v>34</v>
       </c>
       <c r="J7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K7">
         <v>20</v>
@@ -8471,7 +8471,7 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -8608,7 +8608,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L6">
         <v>17</v>
@@ -8706,7 +8706,7 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -8776,7 +8776,7 @@
         <v>2</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <v>2</v>
@@ -11197,7 +11197,7 @@
         <v>2</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -11238,7 +11238,7 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>3</v>
@@ -12253,7 +12253,7 @@
         <v>2</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -12381,7 +12381,7 @@
         <v>16</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6">
         <v>19</v>
@@ -12875,7 +12875,7 @@
         <v>4</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -12904,7 +12904,7 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -13275,7 +13275,7 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -13316,7 +13316,7 @@
         <v>7</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -15521,6 +15521,9 @@
       <c r="I3">
         <v>2</v>
       </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
       <c r="L3">
         <v>1</v>
       </c>
@@ -15606,7 +15609,7 @@
         <v>3</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <v>4</v>
@@ -16049,7 +16052,7 @@
         <v>1</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5">
         <v>3</v>
@@ -16090,7 +16093,7 @@
         <v>4</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M6">
         <v>4</v>
@@ -16830,7 +16833,7 @@
         <v>2</v>
       </c>
       <c r="K4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L4">
         <v>4</v>
@@ -16871,7 +16874,7 @@
         <v>7</v>
       </c>
       <c r="K5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L5">
         <v>6</v>
@@ -17955,7 +17958,7 @@
         <v>9</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -18013,7 +18016,7 @@
         <v>14</v>
       </c>
       <c r="K5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L5">
         <v>11</v>
@@ -18054,13 +18057,13 @@
         <v>30</v>
       </c>
       <c r="K6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L6">
         <v>22</v>
       </c>
       <c r="M6">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -18239,7 +18242,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -18247,7 +18250,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -18442,6 +18445,9 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
       <c r="I4">
         <v>1</v>
       </c>
@@ -18477,7 +18483,7 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <v>1</v>

--- a/output/cta-violent-crime-ytd.xlsx
+++ b/output/cta-violent-crime-ytd.xlsx
@@ -9,17 +9,17 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Englewood" sheetId="3" r:id="rId3"/>
-    <sheet name="Avondale" sheetId="4" r:id="rId4"/>
-    <sheet name="Douglas" sheetId="5" r:id="rId5"/>
-    <sheet name="Grand Boulevard" sheetId="6" r:id="rId6"/>
-    <sheet name="West Town" sheetId="7" r:id="rId7"/>
+    <sheet name="West Town" sheetId="3" r:id="rId3"/>
+    <sheet name="Englewood" sheetId="4" r:id="rId4"/>
+    <sheet name="Avondale" sheetId="5" r:id="rId5"/>
+    <sheet name="Douglas" sheetId="6" r:id="rId6"/>
+    <sheet name="Grand Crossing" sheetId="7" r:id="rId7"/>
     <sheet name="Austin" sheetId="8" r:id="rId8"/>
-    <sheet name="Mount Greenwood" sheetId="9" r:id="rId9"/>
-    <sheet name="Humboldt Park" sheetId="10" r:id="rId10"/>
-    <sheet name="Garfield Park" sheetId="11" r:id="rId11"/>
-    <sheet name="Loop" sheetId="12" r:id="rId12"/>
-    <sheet name="Grand Crossing" sheetId="13" r:id="rId13"/>
+    <sheet name="Grand Boulevard" sheetId="9" r:id="rId9"/>
+    <sheet name="Mount Greenwood" sheetId="10" r:id="rId10"/>
+    <sheet name="Humboldt Park" sheetId="11" r:id="rId11"/>
+    <sheet name="Garfield Park" sheetId="12" r:id="rId12"/>
+    <sheet name="Loop" sheetId="13" r:id="rId13"/>
     <sheet name="United Center" sheetId="14" r:id="rId14"/>
     <sheet name="Ashburn" sheetId="15" r:id="rId15"/>
     <sheet name="Rush &amp; Division" sheetId="16" r:id="rId16"/>
@@ -34,11 +34,11 @@
     <sheet name="South Chicago" sheetId="25" r:id="rId25"/>
     <sheet name="Roseland" sheetId="26" r:id="rId26"/>
     <sheet name="Fuller Park" sheetId="27" r:id="rId27"/>
-    <sheet name="Little Italy, UIC" sheetId="28" r:id="rId28"/>
-    <sheet name="Hyde Park" sheetId="29" r:id="rId29"/>
-    <sheet name="Calumet Heights" sheetId="30" r:id="rId30"/>
-    <sheet name="Kenwood" sheetId="31" r:id="rId31"/>
-    <sheet name="O'Hare" sheetId="32" r:id="rId32"/>
+    <sheet name="O'Hare" sheetId="28" r:id="rId28"/>
+    <sheet name="Little Italy, UIC" sheetId="29" r:id="rId29"/>
+    <sheet name="Hyde Park" sheetId="30" r:id="rId30"/>
+    <sheet name="Calumet Heights" sheetId="31" r:id="rId31"/>
+    <sheet name="Kenwood" sheetId="32" r:id="rId32"/>
     <sheet name="Chicago Lawn" sheetId="33" r:id="rId33"/>
     <sheet name="Wrigleyville" sheetId="34" r:id="rId34"/>
     <sheet name="Auburn Gresham" sheetId="35" r:id="rId35"/>
@@ -1101,6 +1101,59 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1309,261 +1362,6 @@
       </c>
       <c r="M6">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>6</v>
-      </c>
-      <c r="E2">
-        <v>6</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>7</v>
-      </c>
-      <c r="J3">
-        <v>9</v>
-      </c>
-      <c r="K3">
-        <v>12</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
-      <c r="M3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>22</v>
-      </c>
-      <c r="D6">
-        <v>30</v>
-      </c>
-      <c r="E6">
-        <v>28</v>
-      </c>
-      <c r="F6">
-        <v>44</v>
-      </c>
-      <c r="G6">
-        <v>35</v>
-      </c>
-      <c r="H6">
-        <v>30</v>
-      </c>
-      <c r="I6">
-        <v>23</v>
-      </c>
-      <c r="J6">
-        <v>21</v>
-      </c>
-      <c r="K6">
-        <v>20</v>
-      </c>
-      <c r="L6">
-        <v>24</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>41</v>
-      </c>
-      <c r="E7">
-        <v>37</v>
-      </c>
-      <c r="F7">
-        <v>51</v>
-      </c>
-      <c r="G7">
-        <v>43</v>
-      </c>
-      <c r="H7">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>35</v>
-      </c>
-      <c r="J7">
-        <v>31</v>
-      </c>
-      <c r="K7">
-        <v>36</v>
-      </c>
-      <c r="L7">
-        <v>34</v>
-      </c>
-      <c r="M7">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1636,127 +1434,106 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>7</v>
+      </c>
+      <c r="J3">
         <v>9</v>
       </c>
-      <c r="C3">
-        <v>11</v>
-      </c>
-      <c r="D3">
-        <v>15</v>
-      </c>
-      <c r="E3">
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
         <v>9</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>14</v>
-      </c>
-      <c r="H3">
-        <v>10</v>
-      </c>
-      <c r="I3">
-        <v>25</v>
-      </c>
-      <c r="J3">
-        <v>24</v>
-      </c>
-      <c r="K3">
-        <v>22</v>
-      </c>
-      <c r="L3">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
         <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>4</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -1765,40 +1542,40 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
         <v>22</v>
       </c>
-      <c r="C6">
-        <v>26</v>
-      </c>
       <c r="D6">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G6">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H6">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="I6">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="J6">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="K6">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="L6">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1806,40 +1583,40 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>41</v>
+      </c>
+      <c r="E7">
+        <v>37</v>
+      </c>
+      <c r="F7">
+        <v>51</v>
+      </c>
+      <c r="G7">
+        <v>43</v>
+      </c>
+      <c r="H7">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>35</v>
+      </c>
+      <c r="J7">
+        <v>31</v>
+      </c>
+      <c r="K7">
         <v>36</v>
       </c>
-      <c r="C7">
-        <v>41</v>
-      </c>
-      <c r="D7">
-        <v>58</v>
-      </c>
-      <c r="E7">
-        <v>59</v>
-      </c>
-      <c r="F7">
-        <v>55</v>
-      </c>
-      <c r="G7">
-        <v>61</v>
-      </c>
-      <c r="H7">
-        <v>61</v>
-      </c>
-      <c r="I7">
-        <v>103</v>
-      </c>
-      <c r="J7">
-        <v>87</v>
-      </c>
-      <c r="K7">
-        <v>73</v>
-      </c>
       <c r="L7">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="M7">
-        <v>43</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1913,16 +1690,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -1931,22 +1708,22 @@
         <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1954,73 +1731,85 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3">
+        <v>9</v>
+      </c>
+      <c r="G3">
         <v>14</v>
       </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
       <c r="H3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
       </c>
       <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -2029,40 +1818,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="H6">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="J6">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="K6">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L6">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2070,40 +1859,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="G7">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="H7">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="I7">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="J7">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="K7">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="L7">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="M7">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -8392,6 +8181,168 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8622,7 +8573,221 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>11</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>11</v>
+      </c>
+      <c r="M6">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8787,262 +8952,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-      <c r="H2">
-        <v>10</v>
-      </c>
-      <c r="I2">
-        <v>6</v>
-      </c>
-      <c r="J2">
-        <v>5</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>13</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>11</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>14</v>
-      </c>
-      <c r="L3">
-        <v>14</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>26</v>
-      </c>
-      <c r="C6">
-        <v>35</v>
-      </c>
-      <c r="D6">
-        <v>18</v>
-      </c>
-      <c r="E6">
-        <v>16</v>
-      </c>
-      <c r="F6">
-        <v>28</v>
-      </c>
-      <c r="G6">
-        <v>23</v>
-      </c>
-      <c r="H6">
-        <v>22</v>
-      </c>
-      <c r="I6">
-        <v>16</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>25</v>
-      </c>
-      <c r="L6">
-        <v>33</v>
-      </c>
-      <c r="M6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>28</v>
-      </c>
-      <c r="C7">
-        <v>39</v>
-      </c>
-      <c r="D7">
-        <v>34</v>
-      </c>
-      <c r="E7">
-        <v>23</v>
-      </c>
-      <c r="F7">
-        <v>39</v>
-      </c>
-      <c r="G7">
-        <v>31</v>
-      </c>
-      <c r="H7">
-        <v>37</v>
-      </c>
-      <c r="I7">
-        <v>34</v>
-      </c>
-      <c r="J7">
-        <v>21</v>
-      </c>
-      <c r="K7">
-        <v>42</v>
-      </c>
-      <c r="L7">
-        <v>52</v>
-      </c>
-      <c r="M7">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9205,7 +9115,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9314,168 +9224,6 @@
       </c>
       <c r="H6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -10845,7 +10593,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10908,133 +10656,189 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
+      <c r="D2">
+        <v>3</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
       <c r="H2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>13</v>
+      </c>
       <c r="E3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>11</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>14</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
       <c r="K4">
         <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>28</v>
+      </c>
+      <c r="C7">
+        <v>39</v>
+      </c>
+      <c r="D7">
+        <v>34</v>
+      </c>
+      <c r="E7">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>39</v>
+      </c>
+      <c r="G7">
+        <v>31</v>
+      </c>
+      <c r="H7">
+        <v>37</v>
+      </c>
+      <c r="I7">
+        <v>34</v>
+      </c>
+      <c r="J7">
+        <v>21</v>
+      </c>
+      <c r="K7">
+        <v>42</v>
+      </c>
+      <c r="L7">
+        <v>52</v>
+      </c>
+      <c r="M7">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -12935,7 +12739,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12998,27 +12802,33 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
@@ -13027,41 +12837,68 @@
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -13070,63 +12907,28 @@
         <v>3</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
-        <v>7</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
-      <c r="M7">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -14563,10 +14365,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -14627,36 +14429,27 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
+      <c r="D3">
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -14665,13 +14458,10 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -14679,89 +14469,94 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7">
         <v>7</v>
       </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>10</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -16320,7 +16115,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -16384,147 +16179,197 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
       <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>16</v>
+      </c>
+      <c r="G6">
         <v>11</v>
       </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
       <c r="H6">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="L6">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>28</v>
+      </c>
+      <c r="F7">
+        <v>36</v>
+      </c>
+      <c r="G7">
+        <v>19</v>
+      </c>
+      <c r="H7">
+        <v>28</v>
+      </c>
+      <c r="I7">
+        <v>29</v>
+      </c>
+      <c r="J7">
+        <v>30</v>
+      </c>
+      <c r="K7">
+        <v>48</v>
+      </c>
+      <c r="L7">
+        <v>44</v>
+      </c>
+      <c r="M7">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -18777,50 +18622,205 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
         <v>2016</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>10</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-ytd.xlsx
+++ b/output/cta-violent-crime-ytd.xlsx
@@ -89,10 +89,10 @@
     <sheet name="Montclare" sheetId="80" r:id="rId80"/>
     <sheet name="Hermosa" sheetId="81" r:id="rId81"/>
     <sheet name="West Ridge" sheetId="82" r:id="rId82"/>
-    <sheet name="North Center" sheetId="83" r:id="rId83"/>
-    <sheet name="Magnificent Mile" sheetId="84" r:id="rId84"/>
-    <sheet name="Riverdale" sheetId="85" r:id="rId85"/>
-    <sheet name="North Park" sheetId="86" r:id="rId86"/>
+    <sheet name="North Park" sheetId="83" r:id="rId83"/>
+    <sheet name="North Center" sheetId="84" r:id="rId84"/>
+    <sheet name="Magnificent Mile" sheetId="85" r:id="rId85"/>
+    <sheet name="Riverdale" sheetId="86" r:id="rId86"/>
     <sheet name="Galewood" sheetId="87" r:id="rId87"/>
     <sheet name="Gold Coast" sheetId="88" r:id="rId88"/>
     <sheet name="Mount Greenwood" sheetId="89" r:id="rId89"/>
@@ -859,7 +859,7 @@
         <v>31</v>
       </c>
       <c r="C2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2">
         <v>65</v>
@@ -877,13 +877,13 @@
         <v>76</v>
       </c>
       <c r="I2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L2">
         <v>102</v>
@@ -897,7 +897,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3">
         <v>63</v>
@@ -909,22 +909,22 @@
         <v>99</v>
       </c>
       <c r="F3">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G3">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H3">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I3">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J3">
         <v>148</v>
       </c>
       <c r="K3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="L3">
         <v>173</v>
@@ -1009,7 +1009,7 @@
         <v>4</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1023,28 +1023,28 @@
         <v>343</v>
       </c>
       <c r="D6">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E6">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F6">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G6">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H6">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I6">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J6">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K6">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="L6">
         <v>336</v>
@@ -1058,40 +1058,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C7">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D7">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E7">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F7">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G7">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="H7">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="I7">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="J7">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="K7">
-        <v>643</v>
+        <v>653</v>
       </c>
       <c r="L7">
         <v>631</v>
       </c>
       <c r="M7">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -1165,7 +1165,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1255,7 +1255,7 @@
         <v>3</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>13</v>
@@ -1287,7 +1287,7 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -1296,7 +1296,7 @@
         <v>7</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <v>19</v>
@@ -1406,7 +1406,7 @@
         <v>2</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1514,7 +1514,7 @@
         <v>2</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -1549,13 +1549,13 @@
         <v>17</v>
       </c>
       <c r="I6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6">
         <v>9</v>
       </c>
       <c r="K6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L6">
         <v>17</v>
@@ -1700,7 +1700,7 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <v>4</v>
@@ -1790,7 +1790,7 @@
         <v>4</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>12</v>
@@ -2557,7 +2557,7 @@
         <v>6</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>3</v>
@@ -2641,7 +2641,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L6">
         <v>33</v>
@@ -2670,7 +2670,7 @@
         <v>39</v>
       </c>
       <c r="G7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H7">
         <v>37</v>
@@ -2682,7 +2682,7 @@
         <v>21</v>
       </c>
       <c r="K7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L7">
         <v>52</v>
@@ -3208,7 +3208,7 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5">
         <v>11</v>
@@ -3229,7 +3229,7 @@
         <v>7</v>
       </c>
       <c r="K5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L5">
         <v>9</v>
@@ -3249,7 +3249,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6">
         <v>13</v>
@@ -3270,7 +3270,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L6">
         <v>17</v>
@@ -3440,10 +3440,10 @@
         <v>13</v>
       </c>
       <c r="J5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L5">
         <v>20</v>
@@ -3545,7 +3545,7 @@
         <v>35</v>
       </c>
       <c r="G8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H8">
         <v>35</v>
@@ -3928,7 +3928,7 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J21">
         <v>7</v>
@@ -3951,7 +3951,7 @@
         <v>3</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -4125,7 +4125,7 @@
         <v>39</v>
       </c>
       <c r="G28">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H28">
         <v>37</v>
@@ -4137,7 +4137,7 @@
         <v>21</v>
       </c>
       <c r="K28">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L28">
         <v>52</v>
@@ -4178,7 +4178,7 @@
         <v>11</v>
       </c>
       <c r="K29">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L29">
         <v>22</v>
@@ -4348,7 +4348,7 @@
         <v>42</v>
       </c>
       <c r="B36">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C36">
         <v>29</v>
@@ -4360,16 +4360,16 @@
         <v>28</v>
       </c>
       <c r="F36">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G36">
         <v>19</v>
       </c>
       <c r="H36">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I36">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J36">
         <v>30</v>
@@ -4381,7 +4381,7 @@
         <v>44</v>
       </c>
       <c r="M36">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -4563,7 +4563,7 @@
         <v>4</v>
       </c>
       <c r="H43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I43">
         <v>5</v>
@@ -4703,13 +4703,13 @@
         <v>17</v>
       </c>
       <c r="I47">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J47">
         <v>9</v>
       </c>
       <c r="K47">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L47">
         <v>17</v>
@@ -4805,7 +4805,7 @@
         <v>7</v>
       </c>
       <c r="D50">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E50">
         <v>13</v>
@@ -4826,7 +4826,7 @@
         <v>10</v>
       </c>
       <c r="K50">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L50">
         <v>17</v>
@@ -5279,7 +5279,7 @@
         <v>4</v>
       </c>
       <c r="K65">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L65">
         <v>12</v>
@@ -5311,7 +5311,7 @@
         <v>1</v>
       </c>
       <c r="K66">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -5412,7 +5412,7 @@
         <v>6</v>
       </c>
       <c r="E70">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F70">
         <v>18</v>
@@ -5540,7 +5540,7 @@
         <v>10</v>
       </c>
       <c r="G74">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H74">
         <v>11</v>
@@ -5613,7 +5613,7 @@
         <v>15</v>
       </c>
       <c r="G76">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H76">
         <v>14</v>
@@ -5622,7 +5622,7 @@
         <v>16</v>
       </c>
       <c r="J76">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K76">
         <v>19</v>
@@ -5657,7 +5657,7 @@
         <v>16</v>
       </c>
       <c r="H77">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I77">
         <v>34</v>
@@ -5666,7 +5666,7 @@
         <v>25</v>
       </c>
       <c r="K77">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L77">
         <v>19</v>
@@ -5960,7 +5960,7 @@
         <v>6</v>
       </c>
       <c r="C86">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D86">
         <v>2</v>
@@ -5969,7 +5969,7 @@
         <v>7</v>
       </c>
       <c r="F86">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G86">
         <v>19</v>
@@ -6331,7 +6331,7 @@
         <v>7</v>
       </c>
       <c r="K96">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L96">
         <v>3</v>
@@ -6371,6 +6371,9 @@
       <c r="J97">
         <v>3</v>
       </c>
+      <c r="K97">
+        <v>1</v>
+      </c>
       <c r="L97">
         <v>1</v>
       </c>
@@ -6383,40 +6386,40 @@
         <v>6</v>
       </c>
       <c r="B98">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C98">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D98">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E98">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F98">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G98">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="H98">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="I98">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="J98">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="K98">
-        <v>643</v>
+        <v>653</v>
       </c>
       <c r="L98">
         <v>631</v>
       </c>
       <c r="M98">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -7042,7 +7045,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -7054,7 +7057,7 @@
         <v>7</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -7111,6 +7114,9 @@
       <c r="L5">
         <v>1</v>
       </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
@@ -7135,10 +7141,10 @@
         <v>11</v>
       </c>
       <c r="H6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J6">
         <v>18</v>
@@ -7158,7 +7164,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7">
         <v>29</v>
@@ -7170,16 +7176,16 @@
         <v>28</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7">
         <v>19</v>
       </c>
       <c r="H7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J7">
         <v>30</v>
@@ -7191,7 +7197,7 @@
         <v>44</v>
       </c>
       <c r="M7">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -7936,7 +7942,7 @@
         <v>3</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3">
         <v>7</v>
@@ -7945,7 +7951,7 @@
         <v>8</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3">
         <v>4</v>
@@ -8040,7 +8046,7 @@
         <v>16</v>
       </c>
       <c r="H7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I7">
         <v>34</v>
@@ -8049,7 +8055,7 @@
         <v>25</v>
       </c>
       <c r="K7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L7">
         <v>19</v>
@@ -8484,7 +8490,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -8499,9 +8505,10 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8533,13 +8540,16 @@
         <v>2023</v>
       </c>
       <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="L1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -8559,7 +8569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -8578,11 +8588,14 @@
       <c r="J3">
         <v>1</v>
       </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -8590,7 +8603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -8612,14 +8625,14 @@
       <c r="J5">
         <v>1</v>
       </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
       <c r="L5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -8654,6 +8667,9 @@
         <v>1</v>
       </c>
       <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
         <v>3</v>
       </c>
     </row>
@@ -8784,7 +8800,7 @@
         <v>5</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>3</v>
@@ -8889,7 +8905,7 @@
         <v>35</v>
       </c>
       <c r="G6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H6">
         <v>35</v>
@@ -9212,6 +9228,9 @@
       <c r="I2">
         <v>3</v>
       </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
       <c r="K2">
         <v>2</v>
       </c>
@@ -9300,7 +9319,7 @@
         <v>13</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5">
         <v>10</v>
@@ -9341,7 +9360,7 @@
         <v>15</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6">
         <v>14</v>
@@ -9350,7 +9369,7 @@
         <v>16</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K6">
         <v>19</v>
@@ -10557,7 +10576,7 @@
         <v>4</v>
       </c>
       <c r="K5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L5">
         <v>18</v>
@@ -10598,7 +10617,7 @@
         <v>11</v>
       </c>
       <c r="K6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L6">
         <v>22</v>
@@ -11215,10 +11234,10 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>14</v>
@@ -11256,10 +11275,10 @@
         <v>13</v>
       </c>
       <c r="J6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L6">
         <v>20</v>
@@ -12476,7 +12495,7 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5">
         <v>9</v>
@@ -12517,7 +12536,7 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6">
         <v>11</v>
@@ -14105,7 +14124,7 @@
         <v>2</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -14146,7 +14165,7 @@
         <v>4</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -14834,6 +14853,9 @@
       <c r="B5">
         <v>2</v>
       </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
       <c r="E5">
         <v>1</v>
       </c>
@@ -14846,7 +14868,7 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -15005,7 +15027,7 @@
         <v>4</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4">
         <v>14</v>
@@ -15046,7 +15068,7 @@
         <v>6</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5">
         <v>18</v>
@@ -15332,7 +15354,7 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -15430,7 +15452,7 @@
         <v>8</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7">
         <v>7</v>
@@ -16098,7 +16120,7 @@
         <v>4</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -16188,7 +16210,7 @@
         <v>7</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -18039,6 +18061,109 @@
 
 <file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -18123,7 +18248,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18181,7 +18306,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18305,109 +18430,6 @@
       </c>
       <c r="J5">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-ytd.xlsx
+++ b/output/cta-violent-crime-ytd.xlsx
@@ -9,97 +9,97 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Austin" sheetId="3" r:id="rId3"/>
-    <sheet name="Chatham" sheetId="4" r:id="rId4"/>
-    <sheet name="New City" sheetId="5" r:id="rId5"/>
-    <sheet name="Belmont Cragin" sheetId="6" r:id="rId6"/>
-    <sheet name="Woodlawn" sheetId="7" r:id="rId7"/>
-    <sheet name="West Loop" sheetId="8" r:id="rId8"/>
-    <sheet name="Loop" sheetId="9" r:id="rId9"/>
-    <sheet name="Uptown" sheetId="10" r:id="rId10"/>
-    <sheet name="Lake View" sheetId="11" r:id="rId11"/>
-    <sheet name="North Lawndale" sheetId="12" r:id="rId12"/>
-    <sheet name="Grand Boulevard" sheetId="13" r:id="rId13"/>
-    <sheet name="West Town" sheetId="14" r:id="rId14"/>
-    <sheet name="South Shore" sheetId="15" r:id="rId15"/>
-    <sheet name="Englewood" sheetId="16" r:id="rId16"/>
-    <sheet name="Greektown" sheetId="17" r:id="rId17"/>
-    <sheet name="Edgewater" sheetId="18" r:id="rId18"/>
-    <sheet name="Little Italy, UIC" sheetId="19" r:id="rId19"/>
-    <sheet name="Gage Park" sheetId="20" r:id="rId20"/>
-    <sheet name="Humboldt Park" sheetId="21" r:id="rId21"/>
-    <sheet name="Grand Crossing" sheetId="22" r:id="rId22"/>
-    <sheet name="Lower West Side" sheetId="23" r:id="rId23"/>
-    <sheet name="Near South Side" sheetId="24" r:id="rId24"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="25" r:id="rId25"/>
-    <sheet name="Roseland" sheetId="26" r:id="rId26"/>
-    <sheet name="Norwood Park" sheetId="27" r:id="rId27"/>
-    <sheet name="Garfield Park" sheetId="28" r:id="rId28"/>
-    <sheet name="Wrigleyville" sheetId="29" r:id="rId29"/>
-    <sheet name="Auburn Gresham" sheetId="30" r:id="rId30"/>
-    <sheet name="Rogers Park" sheetId="31" r:id="rId31"/>
-    <sheet name="Washington Park" sheetId="32" r:id="rId32"/>
-    <sheet name="Chicago Lawn" sheetId="33" r:id="rId33"/>
-    <sheet name="O'Hare" sheetId="34" r:id="rId34"/>
-    <sheet name="Kenwood" sheetId="35" r:id="rId35"/>
-    <sheet name="Calumet Heights" sheetId="36" r:id="rId36"/>
-    <sheet name="Hyde Park" sheetId="37" r:id="rId37"/>
-    <sheet name="Fuller Park" sheetId="38" r:id="rId38"/>
-    <sheet name="South Chicago" sheetId="39" r:id="rId39"/>
-    <sheet name="Armour Square" sheetId="40" r:id="rId40"/>
-    <sheet name="Douglas" sheetId="41" r:id="rId41"/>
-    <sheet name="Avondale" sheetId="42" r:id="rId42"/>
-    <sheet name="United Center" sheetId="43" r:id="rId43"/>
-    <sheet name="Grant Park" sheetId="44" r:id="rId44"/>
-    <sheet name="Jefferson Park" sheetId="45" r:id="rId45"/>
-    <sheet name="Streeterville" sheetId="46" r:id="rId46"/>
-    <sheet name="Millenium Park" sheetId="47" r:id="rId47"/>
-    <sheet name="River North" sheetId="48" r:id="rId48"/>
-    <sheet name="Beverly" sheetId="49" r:id="rId49"/>
-    <sheet name="Albany Park" sheetId="50" r:id="rId50"/>
-    <sheet name="South Deering" sheetId="51" r:id="rId51"/>
-    <sheet name="West Elsdon" sheetId="52" r:id="rId52"/>
-    <sheet name="Pullman" sheetId="53" r:id="rId53"/>
-    <sheet name="West Pullman" sheetId="54" r:id="rId54"/>
-    <sheet name="Morgan Park" sheetId="55" r:id="rId55"/>
-    <sheet name="Wicker Park" sheetId="56" r:id="rId56"/>
-    <sheet name="Little Village" sheetId="57" r:id="rId57"/>
-    <sheet name="Irving Park" sheetId="58" r:id="rId58"/>
-    <sheet name="Jackson Park" sheetId="59" r:id="rId59"/>
-    <sheet name="Brighton Park" sheetId="60" r:id="rId60"/>
-    <sheet name="Bridgeport" sheetId="61" r:id="rId61"/>
-    <sheet name="Clearing" sheetId="62" r:id="rId62"/>
-    <sheet name="Old Town" sheetId="63" r:id="rId63"/>
-    <sheet name="Mckinley Park" sheetId="64" r:id="rId64"/>
-    <sheet name="Chinatown" sheetId="65" r:id="rId65"/>
-    <sheet name="Bucktown" sheetId="66" r:id="rId66"/>
-    <sheet name="Ukrainian Village" sheetId="67" r:id="rId67"/>
-    <sheet name="Rush &amp; Division" sheetId="68" r:id="rId68"/>
-    <sheet name="Ashburn" sheetId="69" r:id="rId69"/>
-    <sheet name="Washington Heights" sheetId="70" r:id="rId70"/>
-    <sheet name="Printers Row" sheetId="71" r:id="rId71"/>
-    <sheet name="Logan Square" sheetId="72" r:id="rId72"/>
-    <sheet name="Lincoln Park" sheetId="73" r:id="rId73"/>
-    <sheet name="Lincoln Square" sheetId="74" r:id="rId74"/>
-    <sheet name="Archer Heights" sheetId="75" r:id="rId75"/>
-    <sheet name="Avalon Park" sheetId="76" r:id="rId76"/>
-    <sheet name="Burnside" sheetId="77" r:id="rId77"/>
-    <sheet name="East Side" sheetId="78" r:id="rId78"/>
-    <sheet name="Portage Park" sheetId="79" r:id="rId79"/>
-    <sheet name="Montclare" sheetId="80" r:id="rId80"/>
-    <sheet name="Hermosa" sheetId="81" r:id="rId81"/>
-    <sheet name="West Ridge" sheetId="82" r:id="rId82"/>
-    <sheet name="North Park" sheetId="83" r:id="rId83"/>
-    <sheet name="North Center" sheetId="84" r:id="rId84"/>
-    <sheet name="Magnificent Mile" sheetId="85" r:id="rId85"/>
-    <sheet name="Riverdale" sheetId="86" r:id="rId86"/>
-    <sheet name="Galewood" sheetId="87" r:id="rId87"/>
-    <sheet name="Gold Coast" sheetId="88" r:id="rId88"/>
-    <sheet name="Mount Greenwood" sheetId="89" r:id="rId89"/>
-    <sheet name="West Lawn" sheetId="90" r:id="rId90"/>
-    <sheet name="Boystown" sheetId="91" r:id="rId91"/>
-    <sheet name="East Village" sheetId="92" r:id="rId92"/>
-    <sheet name="Oakland" sheetId="93" r:id="rId93"/>
+    <sheet name="Oakland" sheetId="3" r:id="rId3"/>
+    <sheet name="Austin" sheetId="4" r:id="rId4"/>
+    <sheet name="Chatham" sheetId="5" r:id="rId5"/>
+    <sheet name="New City" sheetId="6" r:id="rId6"/>
+    <sheet name="Belmont Cragin" sheetId="7" r:id="rId7"/>
+    <sheet name="Woodlawn" sheetId="8" r:id="rId8"/>
+    <sheet name="West Loop" sheetId="9" r:id="rId9"/>
+    <sheet name="Loop" sheetId="10" r:id="rId10"/>
+    <sheet name="Uptown" sheetId="11" r:id="rId11"/>
+    <sheet name="Lake View" sheetId="12" r:id="rId12"/>
+    <sheet name="North Lawndale" sheetId="13" r:id="rId13"/>
+    <sheet name="Grand Boulevard" sheetId="14" r:id="rId14"/>
+    <sheet name="West Town" sheetId="15" r:id="rId15"/>
+    <sheet name="South Shore" sheetId="16" r:id="rId16"/>
+    <sheet name="Englewood" sheetId="17" r:id="rId17"/>
+    <sheet name="Greektown" sheetId="18" r:id="rId18"/>
+    <sheet name="Edgewater" sheetId="19" r:id="rId19"/>
+    <sheet name="Little Italy, UIC" sheetId="20" r:id="rId20"/>
+    <sheet name="Gage Park" sheetId="21" r:id="rId21"/>
+    <sheet name="Humboldt Park" sheetId="22" r:id="rId22"/>
+    <sheet name="Grand Crossing" sheetId="23" r:id="rId23"/>
+    <sheet name="Lower West Side" sheetId="24" r:id="rId24"/>
+    <sheet name="Near South Side" sheetId="25" r:id="rId25"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="26" r:id="rId26"/>
+    <sheet name="Roseland" sheetId="27" r:id="rId27"/>
+    <sheet name="Norwood Park" sheetId="28" r:id="rId28"/>
+    <sheet name="Garfield Park" sheetId="29" r:id="rId29"/>
+    <sheet name="Wrigleyville" sheetId="30" r:id="rId30"/>
+    <sheet name="Auburn Gresham" sheetId="31" r:id="rId31"/>
+    <sheet name="Rogers Park" sheetId="32" r:id="rId32"/>
+    <sheet name="Washington Park" sheetId="33" r:id="rId33"/>
+    <sheet name="Chicago Lawn" sheetId="34" r:id="rId34"/>
+    <sheet name="O'Hare" sheetId="35" r:id="rId35"/>
+    <sheet name="Kenwood" sheetId="36" r:id="rId36"/>
+    <sheet name="Calumet Heights" sheetId="37" r:id="rId37"/>
+    <sheet name="Hyde Park" sheetId="38" r:id="rId38"/>
+    <sheet name="Fuller Park" sheetId="39" r:id="rId39"/>
+    <sheet name="South Chicago" sheetId="40" r:id="rId40"/>
+    <sheet name="Armour Square" sheetId="41" r:id="rId41"/>
+    <sheet name="Douglas" sheetId="42" r:id="rId42"/>
+    <sheet name="Avondale" sheetId="43" r:id="rId43"/>
+    <sheet name="United Center" sheetId="44" r:id="rId44"/>
+    <sheet name="Grant Park" sheetId="45" r:id="rId45"/>
+    <sheet name="Jefferson Park" sheetId="46" r:id="rId46"/>
+    <sheet name="Streeterville" sheetId="47" r:id="rId47"/>
+    <sheet name="Millenium Park" sheetId="48" r:id="rId48"/>
+    <sheet name="River North" sheetId="49" r:id="rId49"/>
+    <sheet name="Beverly" sheetId="50" r:id="rId50"/>
+    <sheet name="Albany Park" sheetId="51" r:id="rId51"/>
+    <sheet name="South Deering" sheetId="52" r:id="rId52"/>
+    <sheet name="West Elsdon" sheetId="53" r:id="rId53"/>
+    <sheet name="Pullman" sheetId="54" r:id="rId54"/>
+    <sheet name="West Pullman" sheetId="55" r:id="rId55"/>
+    <sheet name="Morgan Park" sheetId="56" r:id="rId56"/>
+    <sheet name="Wicker Park" sheetId="57" r:id="rId57"/>
+    <sheet name="Little Village" sheetId="58" r:id="rId58"/>
+    <sheet name="Irving Park" sheetId="59" r:id="rId59"/>
+    <sheet name="Jackson Park" sheetId="60" r:id="rId60"/>
+    <sheet name="Brighton Park" sheetId="61" r:id="rId61"/>
+    <sheet name="Bridgeport" sheetId="62" r:id="rId62"/>
+    <sheet name="Clearing" sheetId="63" r:id="rId63"/>
+    <sheet name="Old Town" sheetId="64" r:id="rId64"/>
+    <sheet name="Mckinley Park" sheetId="65" r:id="rId65"/>
+    <sheet name="Chinatown" sheetId="66" r:id="rId66"/>
+    <sheet name="Bucktown" sheetId="67" r:id="rId67"/>
+    <sheet name="Ukrainian Village" sheetId="68" r:id="rId68"/>
+    <sheet name="Rush &amp; Division" sheetId="69" r:id="rId69"/>
+    <sheet name="Ashburn" sheetId="70" r:id="rId70"/>
+    <sheet name="Washington Heights" sheetId="71" r:id="rId71"/>
+    <sheet name="Printers Row" sheetId="72" r:id="rId72"/>
+    <sheet name="Logan Square" sheetId="73" r:id="rId73"/>
+    <sheet name="Lincoln Park" sheetId="74" r:id="rId74"/>
+    <sheet name="Lincoln Square" sheetId="75" r:id="rId75"/>
+    <sheet name="Archer Heights" sheetId="76" r:id="rId76"/>
+    <sheet name="Avalon Park" sheetId="77" r:id="rId77"/>
+    <sheet name="Burnside" sheetId="78" r:id="rId78"/>
+    <sheet name="East Side" sheetId="79" r:id="rId79"/>
+    <sheet name="Portage Park" sheetId="80" r:id="rId80"/>
+    <sheet name="Montclare" sheetId="81" r:id="rId81"/>
+    <sheet name="Hermosa" sheetId="82" r:id="rId82"/>
+    <sheet name="West Ridge" sheetId="83" r:id="rId83"/>
+    <sheet name="North Park" sheetId="84" r:id="rId84"/>
+    <sheet name="North Center" sheetId="85" r:id="rId85"/>
+    <sheet name="Magnificent Mile" sheetId="86" r:id="rId86"/>
+    <sheet name="Riverdale" sheetId="87" r:id="rId87"/>
+    <sheet name="Galewood" sheetId="88" r:id="rId88"/>
+    <sheet name="Gold Coast" sheetId="89" r:id="rId89"/>
+    <sheet name="Mount Greenwood" sheetId="90" r:id="rId90"/>
+    <sheet name="West Lawn" sheetId="91" r:id="rId91"/>
+    <sheet name="Boystown" sheetId="92" r:id="rId92"/>
+    <sheet name="East Village" sheetId="93" r:id="rId93"/>
     <sheet name="Dunning" sheetId="94" r:id="rId94"/>
     <sheet name="Hegewisch" sheetId="95" r:id="rId95"/>
     <sheet name="Andersonville" sheetId="96" r:id="rId96"/>
@@ -874,10 +874,10 @@
         <v>65</v>
       </c>
       <c r="H2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J2">
         <v>85</v>
@@ -886,7 +886,7 @@
         <v>101</v>
       </c>
       <c r="L2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M2">
         <v>83</v>
@@ -900,28 +900,28 @@
         <v>61</v>
       </c>
       <c r="C3">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D3">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E3">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F3">
         <v>94</v>
       </c>
       <c r="G3">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H3">
         <v>96</v>
       </c>
       <c r="I3">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J3">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K3">
         <v>162</v>
@@ -1017,7 +1017,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C6">
         <v>343</v>
@@ -1026,31 +1026,31 @@
         <v>306</v>
       </c>
       <c r="E6">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F6">
         <v>391</v>
       </c>
       <c r="G6">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H6">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I6">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J6">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="K6">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L6">
         <v>336</v>
       </c>
       <c r="M6">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1058,40 +1058,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C7">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D7">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E7">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F7">
         <v>555</v>
       </c>
       <c r="G7">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="H7">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="I7">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="J7">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="K7">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L7">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M7">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
   </sheetData>
@@ -1101,7 +1101,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -1164,32 +1164,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
       <c r="C2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -1199,81 +1205,84 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>13</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -1281,43 +1290,84 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="G6">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="H6">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="K6">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="L6">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>36</v>
+      </c>
+      <c r="C7">
+        <v>41</v>
+      </c>
+      <c r="D7">
+        <v>58</v>
+      </c>
+      <c r="E7">
+        <v>59</v>
+      </c>
+      <c r="F7">
+        <v>55</v>
+      </c>
+      <c r="G7">
+        <v>62</v>
+      </c>
+      <c r="H7">
+        <v>61</v>
+      </c>
+      <c r="I7">
+        <v>103</v>
+      </c>
+      <c r="J7">
+        <v>89</v>
+      </c>
+      <c r="K7">
+        <v>73</v>
+      </c>
+      <c r="L7">
+        <v>74</v>
+      </c>
+      <c r="M7">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1391,136 +1441,118 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>4</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="B4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
       <c r="C5">
-        <v>10</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1528,40 +1560,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
         <v>19</v>
       </c>
-      <c r="D6">
+      <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
         <v>8</v>
       </c>
-      <c r="E6">
+      <c r="J6">
         <v>11</v>
       </c>
-      <c r="F6">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>17</v>
-      </c>
-      <c r="I6">
-        <v>20</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
-      </c>
       <c r="K6">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L6">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1634,41 +1666,35 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L2">
         <v>3</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1676,9 +1702,12 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
@@ -1688,74 +1717,86 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K3">
         <v>3</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
       <c r="H4">
         <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>10</v>
       </c>
-      <c r="C5">
-        <v>12</v>
-      </c>
       <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
         <v>16</v>
       </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>21</v>
-      </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>14</v>
-      </c>
       <c r="J5">
         <v>2</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>5</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1763,40 +1804,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>19</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
         <v>12</v>
-      </c>
-      <c r="C6">
-        <v>14</v>
-      </c>
-      <c r="D6">
-        <v>17</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-      <c r="F6">
-        <v>24</v>
       </c>
       <c r="G6">
         <v>16</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="L6">
+        <v>17</v>
+      </c>
+      <c r="M6">
         <v>12</v>
-      </c>
-      <c r="M6">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1805,6 +1846,241 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>16</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>21</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>14</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>24</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>19</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <v>12</v>
+      </c>
+      <c r="M6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1933,7 +2209,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -1971,7 +2247,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -2012,7 +2288,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2226,7 +2502,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2441,7 +2717,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2696,7 +2972,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2831,220 +3107,6 @@
       </c>
       <c r="J6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>6</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>11</v>
-      </c>
-      <c r="I6">
-        <v>9</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3118,12 +3180,15 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
-      <c r="H2">
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
@@ -3133,66 +3198,45 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
       <c r="M4">
         <v>1</v>
       </c>
@@ -3202,40 +3246,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
         <v>11</v>
       </c>
-      <c r="F5">
-        <v>21</v>
-      </c>
-      <c r="G5">
-        <v>13</v>
-      </c>
-      <c r="H5">
-        <v>7</v>
-      </c>
       <c r="I5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3243,40 +3287,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>8</v>
       </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>13</v>
-      </c>
-      <c r="F6">
-        <v>23</v>
-      </c>
       <c r="G6">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>11</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3371,7 +3415,7 @@
         <v>8</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2">
         <v>3</v>
@@ -3548,7 +3592,7 @@
         <v>24</v>
       </c>
       <c r="H8">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I8">
         <v>22</v>
@@ -4154,7 +4198,7 @@
         <v>8</v>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D29">
         <v>7</v>
@@ -4219,7 +4263,7 @@
         <v>11</v>
       </c>
       <c r="L30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>4</v>
@@ -4256,7 +4300,7 @@
         <v>41</v>
       </c>
       <c r="E32">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F32">
         <v>51</v>
@@ -4307,7 +4351,7 @@
         <v>41</v>
       </c>
       <c r="B35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35">
         <v>7</v>
@@ -4363,13 +4407,13 @@
         <v>37</v>
       </c>
       <c r="G36">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H36">
         <v>30</v>
       </c>
       <c r="I36">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J36">
         <v>30</v>
@@ -4487,7 +4531,7 @@
         <v>5</v>
       </c>
       <c r="H41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I41">
         <v>6</v>
@@ -4785,7 +4829,7 @@
         <v>3</v>
       </c>
       <c r="J49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K49">
         <v>1</v>
@@ -4931,7 +4975,7 @@
         <v>55</v>
       </c>
       <c r="G53">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H53">
         <v>61</v>
@@ -4940,7 +4984,7 @@
         <v>103</v>
       </c>
       <c r="J53">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K53">
         <v>73</v>
@@ -5162,7 +5206,7 @@
         <v>2</v>
       </c>
       <c r="E62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F62">
         <v>4</v>
@@ -5261,7 +5305,7 @@
         <v>17</v>
       </c>
       <c r="E65">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F65">
         <v>24</v>
@@ -5397,6 +5441,9 @@
       <c r="H69">
         <v>1</v>
       </c>
+      <c r="M69">
+        <v>2</v>
+      </c>
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="2" t="s">
@@ -5424,7 +5471,7 @@
         <v>9</v>
       </c>
       <c r="I70">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J70">
         <v>7</v>
@@ -5479,7 +5526,7 @@
         <v>7</v>
       </c>
       <c r="G72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H72">
         <v>1</v>
@@ -5619,7 +5666,7 @@
         <v>14</v>
       </c>
       <c r="I76">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J76">
         <v>12</v>
@@ -5739,7 +5786,7 @@
         <v>2</v>
       </c>
       <c r="H79">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I79">
         <v>11</v>
@@ -5762,7 +5809,7 @@
         <v>86</v>
       </c>
       <c r="B80">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C80">
         <v>6</v>
@@ -5789,7 +5836,7 @@
         <v>3</v>
       </c>
       <c r="K80">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L80">
         <v>12</v>
@@ -5922,7 +5969,7 @@
         <v>12</v>
       </c>
       <c r="D85">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E85">
         <v>5</v>
@@ -6167,7 +6214,7 @@
         <v>98</v>
       </c>
       <c r="B92">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C92">
         <v>3</v>
@@ -6328,7 +6375,7 @@
         <v>10</v>
       </c>
       <c r="J96">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K96">
         <v>7</v>
@@ -6386,40 +6433,40 @@
         <v>6</v>
       </c>
       <c r="B98">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C98">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D98">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E98">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F98">
         <v>555</v>
       </c>
       <c r="G98">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="H98">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="I98">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="J98">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="K98">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L98">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M98">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
   </sheetData>
@@ -6528,6 +6575,238 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>21</v>
+      </c>
+      <c r="G5">
+        <v>13</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>7</v>
+      </c>
+      <c r="K5">
+        <v>15</v>
+      </c>
+      <c r="L5">
+        <v>9</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>13</v>
+      </c>
+      <c r="F6">
+        <v>23</v>
+      </c>
+      <c r="G6">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>10</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>17</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6600,7 +6879,7 @@
         <v>6</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -6710,7 +6989,7 @@
         <v>11</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>4</v>
@@ -6721,7 +7000,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6795,6 +7074,9 @@
       <c r="G2">
         <v>1</v>
       </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
       <c r="K2">
         <v>4</v>
       </c>
@@ -6915,7 +7197,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>6</v>
@@ -6938,7 +7220,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7060,7 +7342,7 @@
         <v>15</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>7</v>
@@ -7144,7 +7426,7 @@
         <v>18</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J6">
         <v>18</v>
@@ -7179,13 +7461,13 @@
         <v>37</v>
       </c>
       <c r="G7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H7">
         <v>30</v>
       </c>
       <c r="I7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J7">
         <v>30</v>
@@ -7205,7 +7487,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7393,7 +7675,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7530,7 +7812,7 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -7571,7 +7853,7 @@
         <v>2</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7">
         <v>4</v>
@@ -7603,7 +7885,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7675,7 +7957,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -7794,7 +8076,7 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>11</v>
@@ -7817,7 +8099,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8069,7 +8351,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8233,7 +8515,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8415,7 +8697,7 @@
         <v>30</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6">
         <v>44</v>
@@ -8456,7 +8738,7 @@
         <v>41</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7">
         <v>51</v>
@@ -8481,196 +8763,6 @@
       </c>
       <c r="M7">
         <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -8680,250 +8772,85 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
     <col min="5" max="5" width="4.7109375" customWidth="1"/>
     <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="E1" s="1">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
       <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>6</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
       <c r="C3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>9</v>
-      </c>
-      <c r="M3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>24</v>
-      </c>
-      <c r="G5">
-        <v>18</v>
-      </c>
-      <c r="H5">
-        <v>28</v>
-      </c>
-      <c r="I5">
-        <v>16</v>
-      </c>
-      <c r="J5">
-        <v>14</v>
-      </c>
-      <c r="K5">
-        <v>17</v>
-      </c>
-      <c r="L5">
-        <v>11</v>
-      </c>
-      <c r="M5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>22</v>
-      </c>
-      <c r="C6">
-        <v>34</v>
-      </c>
-      <c r="D6">
-        <v>22</v>
-      </c>
-      <c r="E6">
-        <v>33</v>
-      </c>
-      <c r="F6">
-        <v>35</v>
-      </c>
-      <c r="G6">
-        <v>24</v>
-      </c>
-      <c r="H6">
-        <v>35</v>
-      </c>
-      <c r="I6">
-        <v>22</v>
-      </c>
-      <c r="J6">
-        <v>30</v>
-      </c>
-      <c r="K6">
-        <v>33</v>
-      </c>
-      <c r="L6">
-        <v>22</v>
-      </c>
-      <c r="M6">
-        <v>35</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -8997,64 +8924,52 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
       <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
       </c>
       <c r="K3">
         <v>1</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
@@ -9062,41 +8977,29 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>13</v>
-      </c>
       <c r="C5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>1</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -9104,40 +9007,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -9210,35 +9113,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
       <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9246,57 +9143,36 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>6</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="C4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -9304,40 +9180,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>6</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -9345,40 +9221,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -9452,19 +9328,31 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
       </c>
       <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -9475,42 +9363,57 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
       <c r="L4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -9518,40 +9421,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>7</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -9559,40 +9462,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>15</v>
+      </c>
+      <c r="F6">
+        <v>15</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>17</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>19</v>
+      </c>
+      <c r="L6">
+        <v>17</v>
+      </c>
+      <c r="M6">
         <v>9</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -9665,68 +9568,65 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -9735,22 +9635,28 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <v>4</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -9760,6 +9666,9 @@
       </c>
       <c r="L5">
         <v>1</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -9767,40 +9676,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
         <v>8</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -9809,6 +9718,214 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9970,7 +10087,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10086,7 +10203,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10249,7 +10366,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10414,7 +10531,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10506,7 +10623,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -10593,7 +10710,7 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>7</v>
@@ -10631,7 +10748,260 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>9</v>
+      </c>
+      <c r="M3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>25</v>
+      </c>
+      <c r="D5">
+        <v>14</v>
+      </c>
+      <c r="E5">
+        <v>24</v>
+      </c>
+      <c r="F5">
+        <v>24</v>
+      </c>
+      <c r="G5">
+        <v>18</v>
+      </c>
+      <c r="H5">
+        <v>29</v>
+      </c>
+      <c r="I5">
+        <v>16</v>
+      </c>
+      <c r="J5">
+        <v>14</v>
+      </c>
+      <c r="K5">
+        <v>17</v>
+      </c>
+      <c r="L5">
+        <v>11</v>
+      </c>
+      <c r="M5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>34</v>
+      </c>
+      <c r="D6">
+        <v>22</v>
+      </c>
+      <c r="E6">
+        <v>33</v>
+      </c>
+      <c r="F6">
+        <v>35</v>
+      </c>
+      <c r="G6">
+        <v>24</v>
+      </c>
+      <c r="H6">
+        <v>36</v>
+      </c>
+      <c r="I6">
+        <v>22</v>
+      </c>
+      <c r="J6">
+        <v>30</v>
+      </c>
+      <c r="K6">
+        <v>33</v>
+      </c>
+      <c r="L6">
+        <v>22</v>
+      </c>
+      <c r="M6">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10755,7 +11125,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -10779,7 +11149,7 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <v>5</v>
@@ -10793,7 +11163,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -10820,7 +11190,7 @@
         <v>3</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>12</v>
@@ -10834,242 +11204,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>5</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>6</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>10</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>12</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>10</v>
-      </c>
-      <c r="J5">
-        <v>9</v>
-      </c>
-      <c r="K5">
-        <v>13</v>
-      </c>
-      <c r="L5">
-        <v>12</v>
-      </c>
-      <c r="M5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>8</v>
-      </c>
-      <c r="D6">
-        <v>20</v>
-      </c>
-      <c r="E6">
-        <v>12</v>
-      </c>
-      <c r="F6">
-        <v>16</v>
-      </c>
-      <c r="G6">
-        <v>18</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>16</v>
-      </c>
-      <c r="J6">
-        <v>15</v>
-      </c>
-      <c r="K6">
-        <v>24</v>
-      </c>
-      <c r="L6">
-        <v>19</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11292,7 +11427,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11486,205 +11621,6 @@
       </c>
       <c r="M7">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>7</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -11757,16 +11693,13 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
       <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
@@ -11776,42 +11709,30 @@
         <v>2</v>
       </c>
       <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
       <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M3">
         <v>3</v>
@@ -11821,7 +11742,7 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -11833,36 +11754,30 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5">
         <v>4</v>
       </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
       <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
         <v>2</v>
       </c>
     </row>
@@ -11871,22 +11786,22 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -11895,16 +11810,16 @@
         <v>4</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -11913,77 +11828,6 @@
 </file>
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12048,50 +11892,74 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
       <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I4">
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -12100,40 +11968,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -12141,40 +12009,111 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>11</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <v>10</v>
+      </c>
+      <c r="M6">
         <v>7</v>
       </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>8</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -12183,163 +12122,6 @@
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12404,74 +12186,50 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
       <c r="D3">
         <v>3</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
         <v>2</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
@@ -12480,40 +12238,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -12521,40 +12279,197 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -12564,50 +12479,220 @@
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
         <v>2020</v>
       </c>
-      <c r="C1" s="1">
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
+      </c>
+      <c r="H5">
+        <v>9</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>12</v>
+      </c>
+      <c r="K5">
+        <v>8</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>13</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>14</v>
+      </c>
+      <c r="J6">
+        <v>18</v>
+      </c>
+      <c r="K6">
+        <v>13</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -12617,7 +12702,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -12632,9 +12717,10 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12654,42 +12740,66 @@
         <v>2019</v>
       </c>
       <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
         <v>2021</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="J1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="K1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="L1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
         <v>2</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
       <c r="J2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -12697,89 +12807,127 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>6</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>16</v>
+      </c>
+      <c r="G6">
+        <v>18</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>16</v>
+      </c>
+      <c r="J6">
+        <v>15</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>19</v>
+      </c>
+      <c r="M6">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -12788,6 +12936,59 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12920,7 +13121,7 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -12952,7 +13153,7 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>3</v>
@@ -12966,7 +13167,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13117,7 +13318,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13260,7 +13461,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13348,7 +13549,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13445,7 +13646,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -13483,7 +13684,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -13524,7 +13725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13648,167 +13849,6 @@
       </c>
       <c r="J5">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -13839,25 +13879,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E1" s="1">
         <v>2019</v>
       </c>
       <c r="F1" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="G1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H1" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="I1" s="1">
         <v>2024</v>
@@ -13873,13 +13913,10 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="K2">
         <v>1</v>
       </c>
     </row>
@@ -13887,13 +13924,16 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
         <v>1</v>
       </c>
       <c r="K3">
@@ -13913,27 +13953,27 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
         <v>1</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -13942,31 +13982,31 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>2</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6">
         <v>4</v>
@@ -13978,6 +14018,167 @@
 </file>
 
 <file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14188,7 +14389,179 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14315,136 +14688,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14595,7 +14839,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14756,7 +15000,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14894,7 +15138,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15004,7 +15248,7 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -15080,7 +15324,7 @@
         <v>9</v>
       </c>
       <c r="I5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J5">
         <v>7</v>
@@ -15100,7 +15344,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15250,7 +15494,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15472,7 +15716,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15583,7 +15827,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15656,7 +15900,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15858,7 +16102,136 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16010,221 +16383,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>9</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>13</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>7</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16390,7 +16549,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16505,7 +16664,7 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I4">
         <v>8</v>
@@ -16543,7 +16702,7 @@
         <v>7</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -16561,220 +16720,6 @@
         <v>5</v>
       </c>
       <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>7</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
-      <c r="M6">
         <v>1</v>
       </c>
     </row>
@@ -16848,47 +16793,65 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
       <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>1</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -16900,25 +16863,34 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
       <c r="H5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -16929,37 +16901,37 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -16971,6 +16943,193 @@
 </file>
 
 <file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17056,6 +17215,9 @@
       <c r="H3">
         <v>2</v>
       </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
       <c r="K3">
         <v>1</v>
       </c>
@@ -17112,7 +17274,7 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -17126,7 +17288,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17224,7 +17386,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17321,7 +17483,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17384,7 +17546,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17495,103 +17657,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -17655,28 +17723,19 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
       <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
         <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17684,12 +17743,15 @@
         <v>2</v>
       </c>
       <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
@@ -17699,15 +17761,15 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
         <v>2</v>
       </c>
     </row>
@@ -17718,98 +17780,90 @@
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="L4">
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
       </c>
       <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
         <v>7</v>
       </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
       <c r="L6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>11</v>
-      </c>
-      <c r="I7">
-        <v>9</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
-      </c>
-      <c r="M7">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -17818,6 +17872,100 @@
 </file>
 
 <file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17880,7 +18028,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17963,7 +18111,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18059,7 +18207,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18162,7 +18310,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18248,7 +18396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18306,7 +18454,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18437,7 +18585,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18505,62 +18653,6 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
         <v>1</v>
       </c>
     </row>
@@ -18584,7 +18676,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C1" s="1">
         <v>2023</v>
@@ -18592,9 +18684,9 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="B2">
         <v>1</v>
       </c>
     </row>
@@ -18603,6 +18695,9 @@
         <v>5</v>
       </c>
       <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
         <v>1</v>
       </c>
     </row>
@@ -18611,7 +18706,7 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -18688,37 +18783,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>9</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>9</v>
-      </c>
-      <c r="J2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -18729,85 +18812,49 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>4</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
+      <c r="F4">
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -18816,40 +18863,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -18857,40 +18904,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="H7">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="I7">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>43</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -18899,6 +18946,59 @@
 </file>
 
 <file path=xl/worksheets/sheet90.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet91.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18959,7 +19059,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet91.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18997,7 +19097,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet93.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19047,84 +19147,6 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet93.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
         <v>1</v>
       </c>
     </row>

--- a/output/cta-violent-crime-ytd.xlsx
+++ b/output/cta-violent-crime-ytd.xlsx
@@ -9,29 +9,29 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Austin" sheetId="3" r:id="rId3"/>
-    <sheet name="Avondale" sheetId="4" r:id="rId4"/>
-    <sheet name="Rush &amp; Division" sheetId="5" r:id="rId5"/>
-    <sheet name="Oakland" sheetId="6" r:id="rId6"/>
-    <sheet name="Chatham" sheetId="7" r:id="rId7"/>
-    <sheet name="New City" sheetId="8" r:id="rId8"/>
-    <sheet name="Belmont Cragin" sheetId="9" r:id="rId9"/>
-    <sheet name="Woodlawn" sheetId="10" r:id="rId10"/>
-    <sheet name="West Loop" sheetId="11" r:id="rId11"/>
-    <sheet name="Loop" sheetId="12" r:id="rId12"/>
-    <sheet name="Uptown" sheetId="13" r:id="rId13"/>
-    <sheet name="Lake View" sheetId="14" r:id="rId14"/>
-    <sheet name="North Lawndale" sheetId="15" r:id="rId15"/>
-    <sheet name="Grand Boulevard" sheetId="16" r:id="rId16"/>
-    <sheet name="West Town" sheetId="17" r:id="rId17"/>
-    <sheet name="South Shore" sheetId="18" r:id="rId18"/>
-    <sheet name="Englewood" sheetId="19" r:id="rId19"/>
-    <sheet name="Greektown" sheetId="20" r:id="rId20"/>
-    <sheet name="Edgewater" sheetId="21" r:id="rId21"/>
-    <sheet name="Little Italy, UIC" sheetId="22" r:id="rId22"/>
-    <sheet name="Gage Park" sheetId="23" r:id="rId23"/>
-    <sheet name="Humboldt Park" sheetId="24" r:id="rId24"/>
-    <sheet name="Grand Crossing" sheetId="25" r:id="rId25"/>
+    <sheet name="Grand Crossing" sheetId="3" r:id="rId3"/>
+    <sheet name="South Shore" sheetId="4" r:id="rId4"/>
+    <sheet name="Austin" sheetId="5" r:id="rId5"/>
+    <sheet name="Avondale" sheetId="6" r:id="rId6"/>
+    <sheet name="Rush &amp; Division" sheetId="7" r:id="rId7"/>
+    <sheet name="Oakland" sheetId="8" r:id="rId8"/>
+    <sheet name="Chatham" sheetId="9" r:id="rId9"/>
+    <sheet name="New City" sheetId="10" r:id="rId10"/>
+    <sheet name="Belmont Cragin" sheetId="11" r:id="rId11"/>
+    <sheet name="Woodlawn" sheetId="12" r:id="rId12"/>
+    <sheet name="West Loop" sheetId="13" r:id="rId13"/>
+    <sheet name="Loop" sheetId="14" r:id="rId14"/>
+    <sheet name="Uptown" sheetId="15" r:id="rId15"/>
+    <sheet name="Lake View" sheetId="16" r:id="rId16"/>
+    <sheet name="North Lawndale" sheetId="17" r:id="rId17"/>
+    <sheet name="Grand Boulevard" sheetId="18" r:id="rId18"/>
+    <sheet name="West Town" sheetId="19" r:id="rId19"/>
+    <sheet name="Englewood" sheetId="20" r:id="rId20"/>
+    <sheet name="Greektown" sheetId="21" r:id="rId21"/>
+    <sheet name="Edgewater" sheetId="22" r:id="rId22"/>
+    <sheet name="Little Italy, UIC" sheetId="23" r:id="rId23"/>
+    <sheet name="Gage Park" sheetId="24" r:id="rId24"/>
+    <sheet name="Humboldt Park" sheetId="25" r:id="rId25"/>
     <sheet name="Lower West Side" sheetId="26" r:id="rId26"/>
     <sheet name="Near South Side" sheetId="27" r:id="rId27"/>
     <sheet name="Sheffield &amp; DePaul" sheetId="28" r:id="rId28"/>
@@ -868,13 +868,13 @@
         <v>51</v>
       </c>
       <c r="F2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G2">
         <v>65</v>
       </c>
       <c r="H2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I2">
         <v>88</v>
@@ -883,13 +883,13 @@
         <v>86</v>
       </c>
       <c r="K2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L2">
         <v>105</v>
       </c>
       <c r="M2">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -924,13 +924,13 @@
         <v>151</v>
       </c>
       <c r="K3">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L3">
         <v>175</v>
       </c>
       <c r="M3">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1017,7 +1017,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C6">
         <v>347</v>
@@ -1026,31 +1026,31 @@
         <v>307</v>
       </c>
       <c r="E6">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F6">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G6">
         <v>355</v>
       </c>
       <c r="H6">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I6">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J6">
         <v>294</v>
       </c>
       <c r="K6">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L6">
         <v>339</v>
       </c>
       <c r="M6">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1058,7 +1058,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C7">
         <v>468</v>
@@ -1067,31 +1067,31 @@
         <v>479</v>
       </c>
       <c r="E7">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F7">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="G7">
         <v>516</v>
       </c>
       <c r="H7">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="I7">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="J7">
         <v>549</v>
       </c>
       <c r="K7">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="L7">
         <v>639</v>
       </c>
       <c r="M7">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>
@@ -1100,6 +1100,307 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1243,7 +1544,7 @@
         <v>7</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1284,7 +1585,7 @@
         <v>8</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -1313,7 +1614,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1429,7 +1730,7 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3">
         <v>2</v>
@@ -1527,7 +1828,7 @@
         <v>3</v>
       </c>
       <c r="K7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>8</v>
@@ -1541,7 +1842,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1681,7 +1982,7 @@
         <v>23</v>
       </c>
       <c r="M3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1744,7 +2045,7 @@
         <v>33</v>
       </c>
       <c r="E6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F6">
         <v>41</v>
@@ -1756,7 +2057,7 @@
         <v>44</v>
       </c>
       <c r="I6">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J6">
         <v>46</v>
@@ -1785,7 +2086,7 @@
         <v>58</v>
       </c>
       <c r="E7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F7">
         <v>55</v>
@@ -1797,7 +2098,7 @@
         <v>62</v>
       </c>
       <c r="I7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J7">
         <v>89</v>
@@ -1809,480 +2110,7 @@
         <v>75</v>
       </c>
       <c r="M7">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>13</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>19</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>11</v>
-      </c>
-      <c r="K6">
-        <v>13</v>
-      </c>
-      <c r="L6">
-        <v>10</v>
-      </c>
-      <c r="M6">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>6</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>8</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>16</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>20</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>11</v>
-      </c>
-      <c r="F6">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>17</v>
-      </c>
-      <c r="I6">
-        <v>20</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
-      </c>
-      <c r="K6">
-        <v>18</v>
-      </c>
-      <c r="L6">
-        <v>17</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2355,11 +2183,8 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2367,74 +2192,71 @@
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
       <c r="G2">
         <v>2</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
         <v>3</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
@@ -2443,40 +2265,37 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
         <v>13</v>
       </c>
-      <c r="D5">
-        <v>16</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>21</v>
-      </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
       <c r="H5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2484,40 +2303,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>19</v>
+      </c>
+      <c r="H6">
         <v>12</v>
       </c>
-      <c r="C6">
-        <v>15</v>
-      </c>
-      <c r="D6">
-        <v>17</v>
-      </c>
-      <c r="E6">
+      <c r="I6">
         <v>8</v>
       </c>
-      <c r="F6">
-        <v>24</v>
-      </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
+      <c r="J6">
         <v>11</v>
       </c>
-      <c r="I6">
-        <v>19</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
       <c r="K6">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2530,7 +2349,7 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -2591,28 +2410,37 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2622,69 +2450,99 @@
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
       <c r="C5">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>5</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2692,40 +2550,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="L6">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2801,14 +2659,23 @@
       <c r="B2">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -2817,46 +2684,58 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>1</v>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
       </c>
       <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J4">
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
@@ -2865,40 +2744,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H5">
         <v>5</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J5">
         <v>2</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2906,40 +2785,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>24</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>19</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
         <v>11</v>
       </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
+      <c r="L6">
+        <v>12</v>
+      </c>
+      <c r="M6">
         <v>7</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>11</v>
-      </c>
-      <c r="M6">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2949,7 +2828,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -3012,23 +2891,23 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
       </c>
       <c r="L2">
         <v>2</v>
@@ -3044,29 +2923,17 @@
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
       <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>3</v>
@@ -3077,84 +2944,89 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>7</v>
-      </c>
-      <c r="J4">
-        <v>9</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
         <v>10</v>
       </c>
-      <c r="G5">
-        <v>8</v>
-      </c>
-      <c r="H5">
-        <v>8</v>
-      </c>
-      <c r="I5">
-        <v>11</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-      <c r="M5">
-        <v>6</v>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3164,7 +3036,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -3227,32 +3099,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>3</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
       <c r="H2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <v>4</v>
@@ -3262,154 +3131,116 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>13</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>11</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
       <c r="J4">
         <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>11</v>
+      </c>
+      <c r="M6">
         <v>10</v>
-      </c>
-      <c r="K6">
-        <v>27</v>
-      </c>
-      <c r="L6">
-        <v>33</v>
-      </c>
-      <c r="M6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>28</v>
-      </c>
-      <c r="C7">
-        <v>39</v>
-      </c>
-      <c r="D7">
-        <v>34</v>
-      </c>
-      <c r="E7">
-        <v>23</v>
-      </c>
-      <c r="F7">
-        <v>39</v>
-      </c>
-      <c r="G7">
-        <v>32</v>
-      </c>
-      <c r="H7">
-        <v>37</v>
-      </c>
-      <c r="I7">
-        <v>36</v>
-      </c>
-      <c r="J7">
-        <v>21</v>
-      </c>
-      <c r="K7">
-        <v>44</v>
-      </c>
-      <c r="L7">
-        <v>52</v>
-      </c>
-      <c r="M7">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -3754,7 +3585,7 @@
         <v>7</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10">
         <v>3</v>
@@ -3815,6 +3646,9 @@
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
       <c r="C14">
         <v>4</v>
       </c>
@@ -4020,7 +3854,7 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>2</v>
@@ -4395,7 +4229,7 @@
         <v>38</v>
       </c>
       <c r="F32">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G32">
         <v>43</v>
@@ -4502,7 +4336,7 @@
         <v>20</v>
       </c>
       <c r="H36">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I36">
         <v>31</v>
@@ -4517,7 +4351,7 @@
         <v>44</v>
       </c>
       <c r="M36">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5038,7 +4872,7 @@
         <v>9</v>
       </c>
       <c r="K52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L52">
         <v>9</v>
@@ -5061,7 +4895,7 @@
         <v>58</v>
       </c>
       <c r="E53">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F53">
         <v>55</v>
@@ -5073,7 +4907,7 @@
         <v>62</v>
       </c>
       <c r="I53">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J53">
         <v>89</v>
@@ -5085,7 +4919,7 @@
         <v>75</v>
       </c>
       <c r="M53">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -5409,7 +5243,7 @@
         <v>16</v>
       </c>
       <c r="H65">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I65">
         <v>19</v>
@@ -5688,7 +5522,7 @@
         <v>11</v>
       </c>
       <c r="I74">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J74">
         <v>19</v>
@@ -6010,7 +5844,7 @@
         <v>6</v>
       </c>
       <c r="M82">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -6126,7 +5960,7 @@
         <v>11</v>
       </c>
       <c r="K86">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L86">
         <v>10</v>
@@ -6295,7 +6129,7 @@
         <v>3</v>
       </c>
       <c r="K91">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L91">
         <v>8</v>
@@ -6458,7 +6292,7 @@
         <v>8</v>
       </c>
       <c r="F96">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G96">
         <v>4</v>
@@ -6528,7 +6362,7 @@
         <v>6</v>
       </c>
       <c r="B98">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C98">
         <v>468</v>
@@ -6537,31 +6371,31 @@
         <v>479</v>
       </c>
       <c r="E98">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F98">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="G98">
         <v>516</v>
       </c>
       <c r="H98">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="I98">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="J98">
         <v>549</v>
       </c>
       <c r="K98">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="L98">
         <v>639</v>
       </c>
       <c r="M98">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>
@@ -6670,149 +6504,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -6875,148 +6567,331 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>13</v>
+      </c>
       <c r="E3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G3">
         <v>4</v>
       </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
       <c r="I3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>14</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>6</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>28</v>
+      </c>
+      <c r="C7">
+        <v>39</v>
+      </c>
+      <c r="D7">
+        <v>34</v>
+      </c>
+      <c r="E7">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>39</v>
+      </c>
+      <c r="G7">
+        <v>32</v>
+      </c>
+      <c r="H7">
+        <v>37</v>
+      </c>
+      <c r="I7">
+        <v>36</v>
+      </c>
+      <c r="J7">
+        <v>21</v>
+      </c>
+      <c r="K7">
+        <v>44</v>
+      </c>
+      <c r="L7">
+        <v>52</v>
+      </c>
+      <c r="M7">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -7090,12 +6965,15 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
-      <c r="H2">
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
@@ -7105,66 +6983,45 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
       <c r="M4">
         <v>1</v>
       </c>
@@ -7174,40 +7031,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -7215,40 +7072,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>8</v>
       </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>14</v>
-      </c>
-      <c r="F6">
-        <v>23</v>
-      </c>
       <c r="G6">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>11</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -7257,6 +7114,238 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>21</v>
+      </c>
+      <c r="G5">
+        <v>13</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>7</v>
+      </c>
+      <c r="K5">
+        <v>15</v>
+      </c>
+      <c r="L5">
+        <v>10</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>23</v>
+      </c>
+      <c r="G6">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>10</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>18</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7451,7 +7540,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7664,273 +7753,6 @@
       </c>
       <c r="M6">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>15</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>24</v>
-      </c>
-      <c r="D6">
-        <v>17</v>
-      </c>
-      <c r="E6">
-        <v>16</v>
-      </c>
-      <c r="F6">
-        <v>16</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>18</v>
-      </c>
-      <c r="I6">
-        <v>15</v>
-      </c>
-      <c r="J6">
-        <v>18</v>
-      </c>
-      <c r="K6">
-        <v>31</v>
-      </c>
-      <c r="L6">
-        <v>31</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>21</v>
-      </c>
-      <c r="C7">
-        <v>29</v>
-      </c>
-      <c r="D7">
-        <v>27</v>
-      </c>
-      <c r="E7">
-        <v>28</v>
-      </c>
-      <c r="F7">
-        <v>37</v>
-      </c>
-      <c r="G7">
-        <v>20</v>
-      </c>
-      <c r="H7">
-        <v>30</v>
-      </c>
-      <c r="I7">
-        <v>31</v>
-      </c>
-      <c r="J7">
-        <v>30</v>
-      </c>
-      <c r="K7">
-        <v>48</v>
-      </c>
-      <c r="L7">
-        <v>44</v>
-      </c>
-      <c r="M7">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -8807,7 +8629,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -8871,40 +8693,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8912,28 +8734,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>5</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>5</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J3">
         <v>7</v>
@@ -8942,30 +8764,24 @@
         <v>10</v>
       </c>
       <c r="L3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
       <c r="E4">
         <v>1</v>
       </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
       <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -8973,84 +8789,104 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>13</v>
-      </c>
-      <c r="C5">
-        <v>25</v>
-      </c>
-      <c r="D5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>24</v>
-      </c>
-      <c r="F5">
-        <v>24</v>
-      </c>
-      <c r="G5">
-        <v>18</v>
-      </c>
-      <c r="H5">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>16</v>
-      </c>
-      <c r="J5">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C6">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H6">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I6">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J6">
+        <v>18</v>
+      </c>
+      <c r="K6">
+        <v>31</v>
+      </c>
+      <c r="L6">
+        <v>31</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>21</v>
+      </c>
+      <c r="C7">
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>28</v>
+      </c>
+      <c r="F7">
+        <v>37</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="H7">
+        <v>31</v>
+      </c>
+      <c r="I7">
+        <v>31</v>
+      </c>
+      <c r="J7">
         <v>30</v>
       </c>
-      <c r="K6">
-        <v>33</v>
-      </c>
-      <c r="L6">
-        <v>22</v>
-      </c>
-      <c r="M6">
-        <v>36</v>
+      <c r="K7">
+        <v>48</v>
+      </c>
+      <c r="L7">
+        <v>44</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -9297,7 +9133,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -9448,7 +9284,7 @@
         <v>38</v>
       </c>
       <c r="F7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G7">
         <v>43</v>
@@ -10411,7 +10247,7 @@
         <v>3</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -10524,7 +10360,7 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -10990,10 +10826,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -11054,132 +10890,148 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="E2">
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
-      <c r="J2">
-        <v>1</v>
+      <c r="L2">
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
       </c>
       <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
         <v>2</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4">
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="M5">
         <v>7</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -12914,23 +12766,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12938,34 +12808,61 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>9</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
       <c r="M4">
         <v>1</v>
       </c>
@@ -12975,40 +12872,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -13016,40 +12913,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -13219,7 +13116,7 @@
         <v>9</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J5">
         <v>12</v>
@@ -13260,7 +13157,7 @@
         <v>11</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J6">
         <v>19</v>
@@ -14528,85 +14425,199 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
     <col min="5" max="5" width="4.7109375" customWidth="1"/>
     <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
         <v>2017</v>
       </c>
-      <c r="C1" s="1">
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
         <v>2019</v>
       </c>
-      <c r="D1" s="1">
+      <c r="G1" s="1">
         <v>2020</v>
       </c>
-      <c r="E1" s="1">
+      <c r="H1" s="1">
         <v>2021</v>
       </c>
-      <c r="F1" s="1">
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="E2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
         <v>2</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -15105,7 +15116,7 @@
 
 <file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -15119,64 +15130,65 @@
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
         <v>2016</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
         <v>2017</v>
       </c>
-      <c r="D1" s="1">
+      <c r="E1" s="1">
         <v>2018</v>
       </c>
-      <c r="E1" s="1">
+      <c r="F1" s="1">
         <v>2020</v>
       </c>
-      <c r="F1" s="1">
+      <c r="G1" s="1">
         <v>2021</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
         <v>2022</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
         <v>2023</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2024</v>
       </c>
-      <c r="J1" s="1">
+      <c r="K1" s="1">
         <v>2025</v>
       </c>
-      <c r="K1" s="1">
+      <c r="L1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>2</v>
@@ -15184,78 +15196,87 @@
       <c r="K2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
         <v>3</v>
       </c>
     </row>
@@ -16169,7 +16190,7 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -16229,38 +16250,23 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16271,7 +16277,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -16280,35 +16286,23 @@
         <v>4</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>5</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>6</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -16317,40 +16311,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G5">
         <v>12</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -16358,40 +16352,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
         <v>8</v>
       </c>
-      <c r="D6">
-        <v>20</v>
-      </c>
-      <c r="E6">
-        <v>12</v>
-      </c>
-      <c r="F6">
-        <v>16</v>
-      </c>
       <c r="G6">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H6">
         <v>8</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -16976,6 +16970,9 @@
       <c r="J2">
         <v>2</v>
       </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
       <c r="L2">
         <v>3</v>
       </c>
@@ -17096,7 +17093,7 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -17837,7 +17834,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -17846,160 +17843,76 @@
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
     <col min="5" max="5" width="4.7109375" customWidth="1"/>
     <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="E1" s="1">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -18855,10 +18768,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -18867,9 +18780,13 @@
     <col min="7" max="7" width="4.7109375" customWidth="1"/>
     <col min="8" max="8" width="4.7109375" customWidth="1"/>
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -18886,95 +18803,197 @@
         <v>2018</v>
       </c>
       <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="G1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="H1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="I1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>6</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>10</v>
+      </c>
+      <c r="J5">
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>13</v>
+      </c>
+      <c r="L5">
+        <v>12</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="J6">
+        <v>16</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>19</v>
+      </c>
+      <c r="M6">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-ytd.xlsx
+++ b/output/cta-violent-crime-ytd.xlsx
@@ -9,31 +9,31 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Grand Crossing" sheetId="3" r:id="rId3"/>
-    <sheet name="South Shore" sheetId="4" r:id="rId4"/>
-    <sheet name="Austin" sheetId="5" r:id="rId5"/>
-    <sheet name="Avondale" sheetId="6" r:id="rId6"/>
-    <sheet name="Rush &amp; Division" sheetId="7" r:id="rId7"/>
-    <sheet name="Oakland" sheetId="8" r:id="rId8"/>
-    <sheet name="Chatham" sheetId="9" r:id="rId9"/>
-    <sheet name="New City" sheetId="10" r:id="rId10"/>
-    <sheet name="Belmont Cragin" sheetId="11" r:id="rId11"/>
-    <sheet name="Woodlawn" sheetId="12" r:id="rId12"/>
-    <sheet name="West Loop" sheetId="13" r:id="rId13"/>
-    <sheet name="Loop" sheetId="14" r:id="rId14"/>
-    <sheet name="Uptown" sheetId="15" r:id="rId15"/>
-    <sheet name="Lake View" sheetId="16" r:id="rId16"/>
-    <sheet name="North Lawndale" sheetId="17" r:id="rId17"/>
-    <sheet name="Grand Boulevard" sheetId="18" r:id="rId18"/>
-    <sheet name="West Town" sheetId="19" r:id="rId19"/>
-    <sheet name="Englewood" sheetId="20" r:id="rId20"/>
-    <sheet name="Greektown" sheetId="21" r:id="rId21"/>
-    <sheet name="Edgewater" sheetId="22" r:id="rId22"/>
-    <sheet name="Little Italy, UIC" sheetId="23" r:id="rId23"/>
-    <sheet name="Gage Park" sheetId="24" r:id="rId24"/>
-    <sheet name="Humboldt Park" sheetId="25" r:id="rId25"/>
-    <sheet name="Lower West Side" sheetId="26" r:id="rId26"/>
-    <sheet name="Near South Side" sheetId="27" r:id="rId27"/>
+    <sheet name="Near South Side" sheetId="3" r:id="rId3"/>
+    <sheet name="Grand Crossing" sheetId="4" r:id="rId4"/>
+    <sheet name="South Shore" sheetId="5" r:id="rId5"/>
+    <sheet name="Austin" sheetId="6" r:id="rId6"/>
+    <sheet name="Avondale" sheetId="7" r:id="rId7"/>
+    <sheet name="Rush &amp; Division" sheetId="8" r:id="rId8"/>
+    <sheet name="Oakland" sheetId="9" r:id="rId9"/>
+    <sheet name="Chatham" sheetId="10" r:id="rId10"/>
+    <sheet name="New City" sheetId="11" r:id="rId11"/>
+    <sheet name="Belmont Cragin" sheetId="12" r:id="rId12"/>
+    <sheet name="Woodlawn" sheetId="13" r:id="rId13"/>
+    <sheet name="West Loop" sheetId="14" r:id="rId14"/>
+    <sheet name="Loop" sheetId="15" r:id="rId15"/>
+    <sheet name="Uptown" sheetId="16" r:id="rId16"/>
+    <sheet name="Lake View" sheetId="17" r:id="rId17"/>
+    <sheet name="North Lawndale" sheetId="18" r:id="rId18"/>
+    <sheet name="Grand Boulevard" sheetId="19" r:id="rId19"/>
+    <sheet name="West Town" sheetId="20" r:id="rId20"/>
+    <sheet name="Englewood" sheetId="21" r:id="rId21"/>
+    <sheet name="Greektown" sheetId="22" r:id="rId22"/>
+    <sheet name="Edgewater" sheetId="23" r:id="rId23"/>
+    <sheet name="Little Italy, UIC" sheetId="24" r:id="rId24"/>
+    <sheet name="Gage Park" sheetId="25" r:id="rId25"/>
+    <sheet name="Humboldt Park" sheetId="26" r:id="rId26"/>
+    <sheet name="Lower West Side" sheetId="27" r:id="rId27"/>
     <sheet name="Sheffield &amp; DePaul" sheetId="28" r:id="rId28"/>
     <sheet name="Roseland" sheetId="29" r:id="rId29"/>
     <sheet name="Norwood Park" sheetId="30" r:id="rId30"/>
@@ -859,7 +859,7 @@
         <v>31</v>
       </c>
       <c r="C2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D2">
         <v>68</v>
@@ -909,7 +909,7 @@
         <v>100</v>
       </c>
       <c r="F3">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G3">
         <v>93</v>
@@ -924,10 +924,10 @@
         <v>151</v>
       </c>
       <c r="K3">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M3">
         <v>150</v>
@@ -968,7 +968,7 @@
         <v>18</v>
       </c>
       <c r="L4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M4">
         <v>23</v>
@@ -1017,40 +1017,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C6">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D6">
         <v>307</v>
       </c>
       <c r="E6">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F6">
         <v>393</v>
       </c>
       <c r="G6">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H6">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I6">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J6">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K6">
         <v>374</v>
       </c>
       <c r="L6">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="M6">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1058,40 +1058,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C7">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D7">
         <v>479</v>
       </c>
       <c r="E7">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F7">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="G7">
+        <v>518</v>
+      </c>
+      <c r="H7">
         <v>516</v>
       </c>
-      <c r="H7">
-        <v>514</v>
-      </c>
       <c r="I7">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="J7">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="K7">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L7">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="M7">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -1100,6 +1100,241 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>6</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
+      </c>
+      <c r="J5">
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>13</v>
+      </c>
+      <c r="L5">
+        <v>12</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>16</v>
+      </c>
+      <c r="G6">
+        <v>18</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>16</v>
+      </c>
+      <c r="J6">
+        <v>16</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>19</v>
+      </c>
+      <c r="M6">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1271,7 +1506,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1400,7 +1635,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1607,234 +1842,6 @@
       </c>
       <c r="M6">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>11</v>
-      </c>
-      <c r="I7">
-        <v>9</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
-      </c>
-      <c r="M7">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1908,37 +1915,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>9</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>9</v>
-      </c>
-      <c r="J2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -1949,85 +1944,49 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>4</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
+      <c r="F4">
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -2036,40 +1995,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2077,40 +2036,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="H7">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="I7">
-        <v>104</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>89</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>44</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2120,7 +2079,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -2183,32 +2142,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
       <c r="C2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -2218,81 +2183,84 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>13</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -2300,43 +2268,84 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="G6">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="H6">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="K6">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="L6">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>36</v>
+      </c>
+      <c r="C7">
+        <v>42</v>
+      </c>
+      <c r="D7">
+        <v>58</v>
+      </c>
+      <c r="E7">
+        <v>61</v>
+      </c>
+      <c r="F7">
+        <v>55</v>
+      </c>
+      <c r="G7">
+        <v>62</v>
+      </c>
+      <c r="H7">
+        <v>62</v>
+      </c>
+      <c r="I7">
+        <v>104</v>
+      </c>
+      <c r="J7">
+        <v>89</v>
+      </c>
+      <c r="K7">
+        <v>73</v>
+      </c>
+      <c r="L7">
+        <v>76</v>
+      </c>
+      <c r="M7">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2410,139 +2419,118 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>4</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="B4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
       <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>6</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2550,40 +2538,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>19</v>
+      </c>
+      <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6">
         <v>11</v>
       </c>
-      <c r="F6">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>17</v>
-      </c>
-      <c r="I6">
-        <v>20</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
-      </c>
       <c r="K6">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L6">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2656,41 +2644,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L2">
         <v>3</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2698,86 +2683,101 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K3">
         <v>3</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
       <c r="H4">
         <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
         <v>10</v>
       </c>
-      <c r="C5">
-        <v>13</v>
-      </c>
-      <c r="D5">
+      <c r="I5">
         <v>16</v>
       </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>21</v>
-      </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>14</v>
-      </c>
       <c r="J5">
         <v>2</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>5</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2785,40 +2785,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
         <v>12</v>
-      </c>
-      <c r="C6">
-        <v>15</v>
-      </c>
-      <c r="D6">
-        <v>17</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>24</v>
       </c>
       <c r="G6">
         <v>16</v>
       </c>
       <c r="H6">
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
+        <v>18</v>
+      </c>
+      <c r="L6">
+        <v>17</v>
+      </c>
+      <c r="M6">
         <v>12</v>
-      </c>
-      <c r="I6">
-        <v>19</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>11</v>
-      </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
-      <c r="M6">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2827,6 +2827,241 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>13</v>
+      </c>
+      <c r="D5">
+        <v>16</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>21</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>14</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>24</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>19</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>11</v>
+      </c>
+      <c r="L6">
+        <v>12</v>
+      </c>
+      <c r="M6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3027,220 +3262,6 @@
       </c>
       <c r="M6">
         <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>11</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>11</v>
-      </c>
-      <c r="M6">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3421,7 +3442,7 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -3442,7 +3463,7 @@
         <v>4</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M6">
         <v>2</v>
@@ -3480,7 +3501,7 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>4</v>
@@ -3512,13 +3533,13 @@
         <v>24</v>
       </c>
       <c r="H8">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I8">
         <v>22</v>
       </c>
       <c r="J8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K8">
         <v>33</v>
@@ -3907,7 +3928,7 @@
         <v>20</v>
       </c>
       <c r="L21">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M21">
         <v>4</v>
@@ -4089,7 +4110,7 @@
         <v>34</v>
       </c>
       <c r="E28">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F28">
         <v>39</v>
@@ -4151,7 +4172,7 @@
         <v>15</v>
       </c>
       <c r="L29">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M29">
         <v>10</v>
@@ -4226,7 +4247,7 @@
         <v>42</v>
       </c>
       <c r="E32">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F32">
         <v>52</v>
@@ -4321,7 +4342,7 @@
         <v>21</v>
       </c>
       <c r="C36">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D36">
         <v>27</v>
@@ -4336,7 +4357,7 @@
         <v>20</v>
       </c>
       <c r="H36">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I36">
         <v>31</v>
@@ -4597,7 +4618,7 @@
         <v>1</v>
       </c>
       <c r="F45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45">
         <v>4</v>
@@ -4916,7 +4937,7 @@
         <v>73</v>
       </c>
       <c r="L53">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M53">
         <v>44</v>
@@ -5159,7 +5180,7 @@
         <v>3</v>
       </c>
       <c r="M62">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -5409,7 +5430,7 @@
         <v>17</v>
       </c>
       <c r="L70">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M70">
         <v>3</v>
@@ -5598,7 +5619,7 @@
         <v>17</v>
       </c>
       <c r="J76">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K76">
         <v>19</v>
@@ -5630,13 +5651,13 @@
         <v>13</v>
       </c>
       <c r="G77">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H77">
         <v>21</v>
       </c>
       <c r="I77">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J77">
         <v>25</v>
@@ -5738,7 +5759,7 @@
         <v>86</v>
       </c>
       <c r="B80">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C80">
         <v>6</v>
@@ -6027,7 +6048,7 @@
         <v>1</v>
       </c>
       <c r="G88">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H88">
         <v>4</v>
@@ -6132,7 +6153,7 @@
         <v>10</v>
       </c>
       <c r="L91">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M91">
         <v>9</v>
@@ -6234,7 +6255,7 @@
         <v>8</v>
       </c>
       <c r="L94">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M94">
         <v>10</v>
@@ -6362,40 +6383,40 @@
         <v>6</v>
       </c>
       <c r="B98">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C98">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D98">
         <v>479</v>
       </c>
       <c r="E98">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F98">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="G98">
+        <v>518</v>
+      </c>
+      <c r="H98">
         <v>516</v>
       </c>
-      <c r="H98">
-        <v>514</v>
-      </c>
       <c r="I98">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="J98">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="K98">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L98">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="M98">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -6504,6 +6525,220 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>11</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>12</v>
+      </c>
+      <c r="M6">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6684,7 +6919,7 @@
         <v>18</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6">
         <v>28</v>
@@ -6725,7 +6960,7 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7">
         <v>39</v>
@@ -6757,7 +6992,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6892,220 +7127,6 @@
       </c>
       <c r="J6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>6</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>11</v>
-      </c>
-      <c r="I6">
-        <v>9</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -7179,12 +7200,15 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
-      <c r="H2">
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
@@ -7194,66 +7218,45 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
       <c r="M4">
         <v>1</v>
       </c>
@@ -7263,40 +7266,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -7304,40 +7307,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>8</v>
       </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>14</v>
-      </c>
-      <c r="F6">
-        <v>23</v>
-      </c>
       <c r="G6">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>11</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -7346,6 +7349,238 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>21</v>
+      </c>
+      <c r="G5">
+        <v>13</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>7</v>
+      </c>
+      <c r="K5">
+        <v>15</v>
+      </c>
+      <c r="L5">
+        <v>10</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>23</v>
+      </c>
+      <c r="G6">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>10</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>18</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7540,7 +7775,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7760,7 +7995,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7941,216 +8176,6 @@
       </c>
       <c r="M5">
         <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>12</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>3</v>
-      </c>
-      <c r="M7">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -8560,13 +8585,13 @@
         <v>7</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H6">
         <v>12</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J6">
         <v>15</v>
@@ -8601,13 +8626,13 @@
         <v>13</v>
       </c>
       <c r="G7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7">
         <v>21</v>
       </c>
       <c r="I7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J7">
         <v>25</v>
@@ -8692,98 +8717,53 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
       <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -8791,19 +8771,7 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -8812,40 +8780,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8853,40 +8821,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="J7">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -9240,7 +9208,7 @@
         <v>30</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F6">
         <v>44</v>
@@ -9281,7 +9249,7 @@
         <v>42</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F7">
         <v>52</v>
@@ -9622,7 +9590,7 @@
         <v>3</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9706,7 +9674,7 @@
         <v>4</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>4</v>
@@ -9903,7 +9871,7 @@
         <v>11</v>
       </c>
       <c r="J5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K5">
         <v>9</v>
@@ -9944,7 +9912,7 @@
         <v>17</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K6">
         <v>19</v>
@@ -10108,7 +10076,7 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -10149,7 +10117,7 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -10826,10 +10794,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -10890,28 +10858,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10919,119 +10899,159 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>15</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>9</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
         <v>1</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>25</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>16</v>
+      </c>
+      <c r="G6">
         <v>11</v>
       </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>8</v>
-      </c>
-      <c r="H5">
-        <v>8</v>
-      </c>
-      <c r="I5">
-        <v>11</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-      <c r="M5">
-        <v>7</v>
+      <c r="H6">
+        <v>20</v>
+      </c>
+      <c r="I6">
+        <v>15</v>
+      </c>
+      <c r="J6">
+        <v>18</v>
+      </c>
+      <c r="K6">
+        <v>31</v>
+      </c>
+      <c r="L6">
+        <v>31</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>21</v>
+      </c>
+      <c r="C7">
+        <v>30</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>28</v>
+      </c>
+      <c r="F7">
+        <v>37</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="H7">
+        <v>32</v>
+      </c>
+      <c r="I7">
+        <v>31</v>
+      </c>
+      <c r="J7">
+        <v>30</v>
+      </c>
+      <c r="K7">
+        <v>48</v>
+      </c>
+      <c r="L7">
+        <v>44</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -11369,7 +11389,7 @@
         <v>11</v>
       </c>
       <c r="L5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M5">
         <v>7</v>
@@ -11410,7 +11430,7 @@
         <v>15</v>
       </c>
       <c r="L6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M6">
         <v>10</v>
@@ -11548,7 +11568,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -11586,7 +11606,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -12433,6 +12453,9 @@
       <c r="D3">
         <v>3</v>
       </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
       <c r="G3">
         <v>2</v>
       </c>
@@ -12515,7 +12538,7 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -12703,10 +12726,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -12767,40 +12790,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>6</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>2</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12808,145 +12819,119 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H5">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J5">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>22</v>
-      </c>
-      <c r="C6">
-        <v>34</v>
-      </c>
-      <c r="D6">
-        <v>22</v>
-      </c>
-      <c r="E6">
-        <v>33</v>
-      </c>
-      <c r="F6">
-        <v>35</v>
-      </c>
-      <c r="G6">
-        <v>24</v>
-      </c>
-      <c r="H6">
-        <v>36</v>
-      </c>
-      <c r="I6">
-        <v>22</v>
-      </c>
-      <c r="J6">
-        <v>30</v>
-      </c>
-      <c r="K6">
-        <v>33</v>
-      </c>
-      <c r="L6">
-        <v>22</v>
-      </c>
-      <c r="M6">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -14489,58 +14474,103 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
       </c>
       <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
       <c r="E3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
       <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -14549,34 +14579,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <v>17</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="M5">
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -14584,40 +14620,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -15542,7 +15578,7 @@
         <v>2</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15618,7 +15654,7 @@
         <v>17</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M5">
         <v>3</v>
@@ -15949,7 +15985,7 @@
         <v>16</v>
       </c>
       <c r="L6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -15990,7 +16026,7 @@
         <v>20</v>
       </c>
       <c r="L7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M7">
         <v>4</v>
@@ -16250,59 +16286,59 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
         <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -16311,40 +16347,34 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -16352,40 +16382,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>3</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -16447,7 +16477,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -16505,7 +16535,7 @@
         <v>4</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -16513,7 +16543,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -16534,7 +16564,7 @@
         <v>4</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -17834,85 +17864,205 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
     <col min="5" max="5" width="4.7109375" customWidth="1"/>
     <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
         <v>2017</v>
       </c>
-      <c r="C1" s="1">
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
         <v>2019</v>
       </c>
-      <c r="D1" s="1">
+      <c r="G1" s="1">
         <v>2020</v>
       </c>
-      <c r="E1" s="1">
+      <c r="H1" s="1">
         <v>2021</v>
       </c>
-      <c r="F1" s="1">
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
       <c r="E2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>13</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -18768,7 +18918,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -18777,223 +18927,76 @@
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
     <col min="5" max="5" width="4.7109375" customWidth="1"/>
     <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="E1" s="1">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>5</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>6</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>12</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>10</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-      <c r="K5">
-        <v>13</v>
-      </c>
-      <c r="L5">
-        <v>12</v>
-      </c>
-      <c r="M5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>8</v>
-      </c>
-      <c r="D6">
-        <v>20</v>
-      </c>
-      <c r="E6">
-        <v>12</v>
-      </c>
-      <c r="F6">
-        <v>16</v>
-      </c>
-      <c r="G6">
-        <v>18</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>16</v>
-      </c>
-      <c r="J6">
-        <v>16</v>
-      </c>
-      <c r="K6">
-        <v>24</v>
-      </c>
-      <c r="L6">
-        <v>19</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-ytd.xlsx
+++ b/output/cta-violent-crime-ytd.xlsx
@@ -9,41 +9,41 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Near South Side" sheetId="3" r:id="rId3"/>
-    <sheet name="Grand Crossing" sheetId="4" r:id="rId4"/>
-    <sheet name="South Shore" sheetId="5" r:id="rId5"/>
-    <sheet name="Austin" sheetId="6" r:id="rId6"/>
-    <sheet name="Avondale" sheetId="7" r:id="rId7"/>
-    <sheet name="Rush &amp; Division" sheetId="8" r:id="rId8"/>
-    <sheet name="Oakland" sheetId="9" r:id="rId9"/>
-    <sheet name="Chatham" sheetId="10" r:id="rId10"/>
-    <sheet name="New City" sheetId="11" r:id="rId11"/>
-    <sheet name="Belmont Cragin" sheetId="12" r:id="rId12"/>
-    <sheet name="Woodlawn" sheetId="13" r:id="rId13"/>
-    <sheet name="West Loop" sheetId="14" r:id="rId14"/>
-    <sheet name="Loop" sheetId="15" r:id="rId15"/>
-    <sheet name="Uptown" sheetId="16" r:id="rId16"/>
-    <sheet name="Lake View" sheetId="17" r:id="rId17"/>
-    <sheet name="North Lawndale" sheetId="18" r:id="rId18"/>
-    <sheet name="Grand Boulevard" sheetId="19" r:id="rId19"/>
-    <sheet name="West Town" sheetId="20" r:id="rId20"/>
-    <sheet name="Englewood" sheetId="21" r:id="rId21"/>
-    <sheet name="Greektown" sheetId="22" r:id="rId22"/>
-    <sheet name="Edgewater" sheetId="23" r:id="rId23"/>
-    <sheet name="Little Italy, UIC" sheetId="24" r:id="rId24"/>
-    <sheet name="Gage Park" sheetId="25" r:id="rId25"/>
-    <sheet name="Humboldt Park" sheetId="26" r:id="rId26"/>
-    <sheet name="Lower West Side" sheetId="27" r:id="rId27"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="28" r:id="rId28"/>
-    <sheet name="Roseland" sheetId="29" r:id="rId29"/>
-    <sheet name="Norwood Park" sheetId="30" r:id="rId30"/>
-    <sheet name="Garfield Park" sheetId="31" r:id="rId31"/>
-    <sheet name="Wrigleyville" sheetId="32" r:id="rId32"/>
-    <sheet name="Auburn Gresham" sheetId="33" r:id="rId33"/>
-    <sheet name="Rogers Park" sheetId="34" r:id="rId34"/>
-    <sheet name="Washington Park" sheetId="35" r:id="rId35"/>
-    <sheet name="Chicago Lawn" sheetId="36" r:id="rId36"/>
-    <sheet name="O'Hare" sheetId="37" r:id="rId37"/>
+    <sheet name="Loop" sheetId="3" r:id="rId3"/>
+    <sheet name="O'Hare" sheetId="4" r:id="rId4"/>
+    <sheet name="Near South Side" sheetId="5" r:id="rId5"/>
+    <sheet name="Grand Crossing" sheetId="6" r:id="rId6"/>
+    <sheet name="South Shore" sheetId="7" r:id="rId7"/>
+    <sheet name="Austin" sheetId="8" r:id="rId8"/>
+    <sheet name="Avondale" sheetId="9" r:id="rId9"/>
+    <sheet name="Rush &amp; Division" sheetId="10" r:id="rId10"/>
+    <sheet name="Oakland" sheetId="11" r:id="rId11"/>
+    <sheet name="Chatham" sheetId="12" r:id="rId12"/>
+    <sheet name="New City" sheetId="13" r:id="rId13"/>
+    <sheet name="Belmont Cragin" sheetId="14" r:id="rId14"/>
+    <sheet name="Woodlawn" sheetId="15" r:id="rId15"/>
+    <sheet name="West Loop" sheetId="16" r:id="rId16"/>
+    <sheet name="Uptown" sheetId="17" r:id="rId17"/>
+    <sheet name="Lake View" sheetId="18" r:id="rId18"/>
+    <sheet name="North Lawndale" sheetId="19" r:id="rId19"/>
+    <sheet name="Grand Boulevard" sheetId="20" r:id="rId20"/>
+    <sheet name="West Town" sheetId="21" r:id="rId21"/>
+    <sheet name="Englewood" sheetId="22" r:id="rId22"/>
+    <sheet name="Greektown" sheetId="23" r:id="rId23"/>
+    <sheet name="Edgewater" sheetId="24" r:id="rId24"/>
+    <sheet name="Little Italy, UIC" sheetId="25" r:id="rId25"/>
+    <sheet name="Gage Park" sheetId="26" r:id="rId26"/>
+    <sheet name="Humboldt Park" sheetId="27" r:id="rId27"/>
+    <sheet name="Lower West Side" sheetId="28" r:id="rId28"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="29" r:id="rId29"/>
+    <sheet name="Roseland" sheetId="30" r:id="rId30"/>
+    <sheet name="Norwood Park" sheetId="31" r:id="rId31"/>
+    <sheet name="Garfield Park" sheetId="32" r:id="rId32"/>
+    <sheet name="Wrigleyville" sheetId="33" r:id="rId33"/>
+    <sheet name="Auburn Gresham" sheetId="34" r:id="rId34"/>
+    <sheet name="Rogers Park" sheetId="35" r:id="rId35"/>
+    <sheet name="Washington Park" sheetId="36" r:id="rId36"/>
+    <sheet name="Chicago Lawn" sheetId="37" r:id="rId37"/>
     <sheet name="Kenwood" sheetId="38" r:id="rId38"/>
     <sheet name="Calumet Heights" sheetId="39" r:id="rId39"/>
     <sheet name="Hyde Park" sheetId="40" r:id="rId40"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="104">
   <si>
     <t>crime_category</t>
   </si>
@@ -868,7 +868,7 @@
         <v>51</v>
       </c>
       <c r="F2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>65</v>
@@ -889,7 +889,7 @@
         <v>105</v>
       </c>
       <c r="M2">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -903,7 +903,7 @@
         <v>64</v>
       </c>
       <c r="D3">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E3">
         <v>100</v>
@@ -915,19 +915,19 @@
         <v>93</v>
       </c>
       <c r="H3">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I3">
         <v>148</v>
       </c>
       <c r="J3">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K3">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L3">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M3">
         <v>150</v>
@@ -997,7 +997,7 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -1020,37 +1020,37 @@
         <v>280</v>
       </c>
       <c r="C6">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D6">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E6">
         <v>320</v>
       </c>
       <c r="F6">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G6">
         <v>357</v>
       </c>
       <c r="H6">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I6">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J6">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K6">
         <v>374</v>
       </c>
       <c r="L6">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M6">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1061,37 +1061,37 @@
         <v>381</v>
       </c>
       <c r="C7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D7">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E7">
         <v>479</v>
       </c>
       <c r="F7">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="G7">
         <v>518</v>
       </c>
       <c r="H7">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="I7">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="J7">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K7">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L7">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="M7">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -1100,6 +1100,302 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>13</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1334,7 +1630,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1506,7 +1802,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1569,6 +1865,9 @@
       <c r="E3">
         <v>2</v>
       </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
       <c r="H3">
         <v>1</v>
       </c>
@@ -1618,7 +1917,7 @@
         <v>2</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1635,7 +1934,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1849,7 +2148,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2070,508 +2369,6 @@
       </c>
       <c r="M7">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>9</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>7</v>
-      </c>
-      <c r="I2">
-        <v>9</v>
-      </c>
-      <c r="J2">
-        <v>15</v>
-      </c>
-      <c r="K2">
-        <v>11</v>
-      </c>
-      <c r="L2">
-        <v>13</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>11</v>
-      </c>
-      <c r="D3">
-        <v>15</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>14</v>
-      </c>
-      <c r="H3">
-        <v>10</v>
-      </c>
-      <c r="I3">
-        <v>25</v>
-      </c>
-      <c r="J3">
-        <v>24</v>
-      </c>
-      <c r="K3">
-        <v>22</v>
-      </c>
-      <c r="L3">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>4</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>4</v>
-      </c>
-      <c r="M4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>22</v>
-      </c>
-      <c r="C6">
-        <v>27</v>
-      </c>
-      <c r="D6">
-        <v>33</v>
-      </c>
-      <c r="E6">
-        <v>50</v>
-      </c>
-      <c r="F6">
-        <v>41</v>
-      </c>
-      <c r="G6">
-        <v>43</v>
-      </c>
-      <c r="H6">
-        <v>44</v>
-      </c>
-      <c r="I6">
-        <v>66</v>
-      </c>
-      <c r="J6">
-        <v>46</v>
-      </c>
-      <c r="K6">
-        <v>38</v>
-      </c>
-      <c r="L6">
-        <v>35</v>
-      </c>
-      <c r="M6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>36</v>
-      </c>
-      <c r="C7">
-        <v>42</v>
-      </c>
-      <c r="D7">
-        <v>58</v>
-      </c>
-      <c r="E7">
-        <v>61</v>
-      </c>
-      <c r="F7">
-        <v>55</v>
-      </c>
-      <c r="G7">
-        <v>62</v>
-      </c>
-      <c r="H7">
-        <v>62</v>
-      </c>
-      <c r="I7">
-        <v>104</v>
-      </c>
-      <c r="J7">
-        <v>89</v>
-      </c>
-      <c r="K7">
-        <v>73</v>
-      </c>
-      <c r="L7">
-        <v>76</v>
-      </c>
-      <c r="M7">
-        <v>44</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>13</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>19</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>11</v>
-      </c>
-      <c r="K6">
-        <v>14</v>
-      </c>
-      <c r="L6">
-        <v>10</v>
-      </c>
-      <c r="M6">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2645,139 +2442,118 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>4</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="B4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
       <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>6</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2785,40 +2561,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>19</v>
+      </c>
+      <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6">
         <v>11</v>
       </c>
-      <c r="F6">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>17</v>
-      </c>
-      <c r="I6">
-        <v>20</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
-      </c>
       <c r="K6">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L6">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2891,41 +2667,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L2">
         <v>3</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2933,86 +2706,101 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K3">
         <v>3</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
       <c r="H4">
         <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
         <v>10</v>
       </c>
-      <c r="C5">
-        <v>13</v>
-      </c>
-      <c r="D5">
+      <c r="I5">
         <v>16</v>
       </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>21</v>
-      </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>14</v>
-      </c>
       <c r="J5">
         <v>2</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>5</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3020,40 +2808,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
         <v>12</v>
-      </c>
-      <c r="C6">
-        <v>15</v>
-      </c>
-      <c r="D6">
-        <v>17</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>24</v>
       </c>
       <c r="G6">
         <v>16</v>
       </c>
       <c r="H6">
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
+        <v>18</v>
+      </c>
+      <c r="L6">
+        <v>17</v>
+      </c>
+      <c r="M6">
         <v>12</v>
-      </c>
-      <c r="I6">
-        <v>19</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>11</v>
-      </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
-      <c r="M6">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3066,7 +2854,7 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -3126,6 +2914,9 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
         <v>1</v>
       </c>
@@ -3135,20 +2926,29 @@
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
       <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3156,30 +2956,42 @@
         <v>2</v>
       </c>
       <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -3190,37 +3002,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>5</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3228,40 +3043,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>24</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>19</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>11</v>
+      </c>
+      <c r="L6">
+        <v>12</v>
+      </c>
+      <c r="M6">
         <v>7</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>10</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3381,7 +3196,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -3413,7 +3228,7 @@
         <v>7</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -3480,7 +3295,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7">
         <v>14</v>
@@ -3533,7 +3348,7 @@
         <v>24</v>
       </c>
       <c r="H8">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I8">
         <v>22</v>
@@ -3632,7 +3447,7 @@
         <v>2</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -4172,7 +3987,7 @@
         <v>15</v>
       </c>
       <c r="L29">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M29">
         <v>10</v>
@@ -4256,7 +4071,7 @@
         <v>43</v>
       </c>
       <c r="H32">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I32">
         <v>36</v>
@@ -4265,7 +4080,7 @@
         <v>31</v>
       </c>
       <c r="K32">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L32">
         <v>34</v>
@@ -4301,7 +4116,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D35">
         <v>6</v>
@@ -4369,7 +4184,7 @@
         <v>48</v>
       </c>
       <c r="L36">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M36">
         <v>27</v>
@@ -4878,7 +4693,7 @@
         <v>5</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G52">
         <v>7</v>
@@ -4887,7 +4702,7 @@
         <v>8</v>
       </c>
       <c r="I52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J52">
         <v>9</v>
@@ -4913,7 +4728,7 @@
         <v>42</v>
       </c>
       <c r="D53">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E53">
         <v>61</v>
@@ -4940,7 +4755,7 @@
         <v>76</v>
       </c>
       <c r="M53">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -5328,7 +5143,7 @@
         <v>4</v>
       </c>
       <c r="I67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -5372,7 +5187,7 @@
         <v>7</v>
       </c>
       <c r="M68">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -5762,7 +5577,7 @@
         <v>13</v>
       </c>
       <c r="C80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D80">
         <v>2</v>
@@ -5818,7 +5633,7 @@
         <v>5</v>
       </c>
       <c r="J81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L81">
         <v>2</v>
@@ -6386,37 +6201,37 @@
         <v>381</v>
       </c>
       <c r="C98">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D98">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E98">
         <v>479</v>
       </c>
       <c r="F98">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="G98">
         <v>518</v>
       </c>
       <c r="H98">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="I98">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="J98">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K98">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L98">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="M98">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -6528,6 +6343,214 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>10</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
@@ -6737,7 +6760,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6992,7 +7015,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7127,220 +7150,6 @@
       </c>
       <c r="J6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>6</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>11</v>
-      </c>
-      <c r="I6">
-        <v>9</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -7414,12 +7223,15 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
-      <c r="H2">
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
@@ -7429,66 +7241,45 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
       <c r="M4">
         <v>1</v>
       </c>
@@ -7498,40 +7289,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -7539,40 +7330,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>8</v>
       </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>14</v>
-      </c>
-      <c r="F6">
-        <v>23</v>
-      </c>
       <c r="G6">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>11</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -7581,6 +7372,238 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>21</v>
+      </c>
+      <c r="G5">
+        <v>13</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>7</v>
+      </c>
+      <c r="K5">
+        <v>15</v>
+      </c>
+      <c r="L5">
+        <v>10</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>23</v>
+      </c>
+      <c r="G6">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>10</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>18</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7775,7 +7798,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7995,7 +8018,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8183,7 +8206,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8390,261 +8413,6 @@
       </c>
       <c r="M6">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>5</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>5</v>
-      </c>
-      <c r="I3">
-        <v>7</v>
-      </c>
-      <c r="J3">
-        <v>8</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>14</v>
-      </c>
-      <c r="C6">
-        <v>12</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>13</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>12</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>22</v>
-      </c>
-      <c r="J6">
-        <v>15</v>
-      </c>
-      <c r="K6">
-        <v>14</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>20</v>
-      </c>
-      <c r="C7">
-        <v>19</v>
-      </c>
-      <c r="D7">
-        <v>11</v>
-      </c>
-      <c r="E7">
-        <v>21</v>
-      </c>
-      <c r="F7">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>17</v>
-      </c>
-      <c r="H7">
-        <v>21</v>
-      </c>
-      <c r="I7">
-        <v>35</v>
-      </c>
-      <c r="J7">
-        <v>25</v>
-      </c>
-      <c r="K7">
-        <v>21</v>
-      </c>
-      <c r="L7">
-        <v>19</v>
-      </c>
-      <c r="M7">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -8717,17 +8485,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
       <c r="F2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="J2">
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="L2">
+        <v>13</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -8737,41 +8526,86 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="H3">
+        <v>10</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="L3">
+        <v>23</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K5">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -8780,40 +8614,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8821,40 +8655,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -8863,170 +8697,6 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9091,95 +8761,95 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I3">
         <v>7</v>
       </c>
       <c r="J3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="C4">
         <v>1</v>
       </c>
       <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
       <c r="M4">
@@ -9190,7 +8860,7 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I5">
+      <c r="D5">
         <v>1</v>
       </c>
     </row>
@@ -9199,40 +8869,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="H6">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J6">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K6">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L6">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9240,40 +8910,212 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>19</v>
+      </c>
+      <c r="D7">
         <v>11</v>
       </c>
+      <c r="E7">
+        <v>21</v>
+      </c>
+      <c r="F7">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>17</v>
+      </c>
+      <c r="H7">
+        <v>21</v>
+      </c>
+      <c r="I7">
+        <v>35</v>
+      </c>
+      <c r="J7">
+        <v>25</v>
+      </c>
+      <c r="K7">
+        <v>21</v>
+      </c>
+      <c r="L7">
+        <v>19</v>
+      </c>
+      <c r="M7">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
       <c r="C7">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>36</v>
-      </c>
-      <c r="L7">
-        <v>34</v>
-      </c>
-      <c r="M7">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -9283,7 +9125,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -9346,46 +9188,76 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
       </c>
       <c r="J2">
         <v>1</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
       <c r="D3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9393,77 +9265,112 @@
         <v>3</v>
       </c>
       <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>42</v>
+      </c>
+      <c r="E7">
+        <v>40</v>
+      </c>
+      <c r="F7">
+        <v>52</v>
+      </c>
+      <c r="G7">
+        <v>43</v>
+      </c>
+      <c r="H7">
+        <v>40</v>
+      </c>
+      <c r="I7">
+        <v>36</v>
+      </c>
+      <c r="J7">
+        <v>31</v>
+      </c>
+      <c r="K7">
+        <v>37</v>
+      </c>
+      <c r="L7">
+        <v>34</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -9537,59 +9444,44 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
       <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
       </c>
       <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="M3">
         <v>2</v>
       </c>
     </row>
@@ -9597,7 +9489,7 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
@@ -9605,41 +9497,29 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>13</v>
-      </c>
       <c r="C5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>1</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -9647,40 +9527,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -9753,35 +9633,32 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9789,36 +9666,27 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>6</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
         <v>2</v>
       </c>
     </row>
@@ -9826,20 +9694,8 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="C4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -9847,40 +9703,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G5">
         <v>6</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -9888,40 +9744,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -9995,19 +9851,31 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
       </c>
       <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -10018,42 +9886,57 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
       <c r="L4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -10061,40 +9944,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>7</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10102,40 +9985,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>15</v>
+      </c>
+      <c r="F6">
+        <v>15</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>17</v>
+      </c>
+      <c r="J6">
+        <v>13</v>
+      </c>
+      <c r="K6">
+        <v>19</v>
+      </c>
+      <c r="L6">
+        <v>17</v>
+      </c>
+      <c r="M6">
         <v>9</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -10208,68 +10091,65 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="J2">
         <v>2</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -10278,22 +10158,28 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -10303,6 +10189,9 @@
       </c>
       <c r="L5">
         <v>1</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10310,40 +10199,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
         <v>8</v>
       </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>9</v>
-      </c>
       <c r="H6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>2</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -10353,7 +10242,7 @@
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10366,146 +10255,192 @@
     <col min="8" max="8" width="4.7109375" customWidth="1"/>
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
         <v>2016</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
         <v>2017</v>
       </c>
-      <c r="D1" s="1">
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
         <v>2019</v>
       </c>
-      <c r="E1" s="1">
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
         <v>2021</v>
       </c>
-      <c r="F1" s="1">
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="G1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="H1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="I1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="J1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>5</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
       <c r="E3">
         <v>1</v>
       </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
         <v>2</v>
       </c>
       <c r="J3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -10794,7 +10729,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10807,251 +10742,146 @@
     <col min="8" max="8" width="4.7109375" customWidth="1"/>
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="E1" s="1">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="G1" s="1">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
         <v>7</v>
       </c>
-      <c r="F3">
-        <v>15</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>25</v>
-      </c>
-      <c r="D6">
-        <v>17</v>
-      </c>
-      <c r="E6">
-        <v>16</v>
-      </c>
-      <c r="F6">
-        <v>16</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>20</v>
-      </c>
-      <c r="I6">
-        <v>15</v>
-      </c>
-      <c r="J6">
-        <v>18</v>
-      </c>
-      <c r="K6">
-        <v>31</v>
-      </c>
-      <c r="L6">
-        <v>31</v>
-      </c>
-      <c r="M6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>21</v>
-      </c>
-      <c r="C7">
-        <v>30</v>
-      </c>
-      <c r="D7">
-        <v>27</v>
-      </c>
-      <c r="E7">
-        <v>28</v>
-      </c>
-      <c r="F7">
-        <v>37</v>
-      </c>
-      <c r="G7">
-        <v>20</v>
-      </c>
-      <c r="H7">
-        <v>32</v>
-      </c>
-      <c r="I7">
-        <v>31</v>
-      </c>
       <c r="J7">
-        <v>30</v>
-      </c>
-      <c r="K7">
-        <v>48</v>
-      </c>
-      <c r="L7">
-        <v>44</v>
-      </c>
-      <c r="M7">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -11340,7 +11170,7 @@
         <v>2</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -11430,7 +11260,7 @@
         <v>15</v>
       </c>
       <c r="L6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M6">
         <v>10</v>
@@ -11571,7 +11401,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -11609,7 +11439,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -11722,7 +11552,7 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -11841,7 +11671,7 @@
         <v>7</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -12726,10 +12556,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -12789,148 +12619,143 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
+      <c r="G3">
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>9</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>10</v>
-      </c>
-      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
         <v>8</v>
       </c>
-      <c r="H5">
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>12</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7">
         <v>8</v>
       </c>
-      <c r="I5">
-        <v>11</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-      <c r="M5">
+      <c r="L7">
+        <v>3</v>
+      </c>
+      <c r="M7">
         <v>7</v>
       </c>
     </row>
@@ -13507,6 +13332,9 @@
       <c r="G5">
         <v>4</v>
       </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
       <c r="I5">
         <v>1</v>
       </c>
@@ -13534,7 +13362,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -14410,7 +14238,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -14474,40 +14302,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14515,28 +14343,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>5</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>5</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J3">
         <v>7</v>
@@ -14545,30 +14373,24 @@
         <v>10</v>
       </c>
       <c r="L3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
       <c r="E4">
         <v>1</v>
       </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
       <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -14576,84 +14398,104 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>13</v>
-      </c>
-      <c r="C5">
-        <v>25</v>
-      </c>
-      <c r="D5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>24</v>
-      </c>
-      <c r="F5">
-        <v>24</v>
-      </c>
-      <c r="G5">
-        <v>18</v>
-      </c>
-      <c r="H5">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>16</v>
-      </c>
-      <c r="J5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C6">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>16</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>20</v>
+      </c>
+      <c r="I6">
+        <v>15</v>
+      </c>
+      <c r="J6">
+        <v>18</v>
+      </c>
+      <c r="K6">
+        <v>31</v>
+      </c>
+      <c r="L6">
         <v>33</v>
       </c>
-      <c r="F6">
-        <v>35</v>
-      </c>
-      <c r="G6">
-        <v>24</v>
-      </c>
-      <c r="H6">
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>21</v>
+      </c>
+      <c r="C7">
+        <v>30</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>28</v>
+      </c>
+      <c r="F7">
         <v>37</v>
       </c>
-      <c r="I6">
-        <v>22</v>
-      </c>
-      <c r="J6">
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="H7">
+        <v>32</v>
+      </c>
+      <c r="I7">
         <v>31</v>
       </c>
-      <c r="K6">
-        <v>33</v>
-      </c>
-      <c r="L6">
-        <v>22</v>
-      </c>
-      <c r="M6">
-        <v>36</v>
+      <c r="J7">
+        <v>30</v>
+      </c>
+      <c r="K7">
+        <v>48</v>
+      </c>
+      <c r="L7">
+        <v>46</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -16223,10 +16065,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -16287,135 +16129,148 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="E2">
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
+      <c r="L2">
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
       </c>
       <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
         <v>2</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4">
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="M5">
         <v>7</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -17067,7 +16922,7 @@
         <v>3</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -17076,7 +16931,7 @@
         <v>7</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -17108,7 +16963,7 @@
         <v>5</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>7</v>
@@ -17117,7 +16972,7 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6">
         <v>9</v>
@@ -17546,6 +17401,9 @@
       <c r="B4">
         <v>1</v>
       </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
       <c r="E4">
         <v>1</v>
       </c>
@@ -17561,7 +17419,7 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -17927,23 +17785,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17951,34 +17827,61 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>9</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
       <c r="M4">
         <v>1</v>
       </c>
@@ -17988,40 +17891,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -18029,40 +17932,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -18918,85 +18821,199 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
     <col min="5" max="5" width="4.7109375" customWidth="1"/>
     <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
         <v>2017</v>
       </c>
-      <c r="C1" s="1">
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
         <v>2019</v>
       </c>
-      <c r="D1" s="1">
+      <c r="G1" s="1">
         <v>2020</v>
       </c>
-      <c r="E1" s="1">
+      <c r="H1" s="1">
         <v>2021</v>
       </c>
-      <c r="F1" s="1">
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="E2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
         <v>2</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-ytd.xlsx
+++ b/output/cta-violent-crime-ytd.xlsx
@@ -9,25 +9,25 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="South Shore" sheetId="3" r:id="rId3"/>
-    <sheet name="Albany Park" sheetId="4" r:id="rId4"/>
-    <sheet name="Old Town" sheetId="5" r:id="rId5"/>
-    <sheet name="Loop" sheetId="6" r:id="rId6"/>
-    <sheet name="O'Hare" sheetId="7" r:id="rId7"/>
-    <sheet name="Near South Side" sheetId="8" r:id="rId8"/>
-    <sheet name="Grand Crossing" sheetId="9" r:id="rId9"/>
-    <sheet name="Austin" sheetId="10" r:id="rId10"/>
-    <sheet name="Avondale" sheetId="11" r:id="rId11"/>
-    <sheet name="Rush &amp; Division" sheetId="12" r:id="rId12"/>
-    <sheet name="Oakland" sheetId="13" r:id="rId13"/>
-    <sheet name="Chatham" sheetId="14" r:id="rId14"/>
-    <sheet name="New City" sheetId="15" r:id="rId15"/>
-    <sheet name="Belmont Cragin" sheetId="16" r:id="rId16"/>
-    <sheet name="Woodlawn" sheetId="17" r:id="rId17"/>
-    <sheet name="West Loop" sheetId="18" r:id="rId18"/>
-    <sheet name="Uptown" sheetId="19" r:id="rId19"/>
-    <sheet name="Lake View" sheetId="20" r:id="rId20"/>
-    <sheet name="North Lawndale" sheetId="21" r:id="rId21"/>
+    <sheet name="Albany Park" sheetId="3" r:id="rId3"/>
+    <sheet name="Woodlawn" sheetId="4" r:id="rId4"/>
+    <sheet name="North Lawndale" sheetId="5" r:id="rId5"/>
+    <sheet name="South Shore" sheetId="6" r:id="rId6"/>
+    <sheet name="Old Town" sheetId="7" r:id="rId7"/>
+    <sheet name="Loop" sheetId="8" r:id="rId8"/>
+    <sheet name="O'Hare" sheetId="9" r:id="rId9"/>
+    <sheet name="Near South Side" sheetId="10" r:id="rId10"/>
+    <sheet name="Grand Crossing" sheetId="11" r:id="rId11"/>
+    <sheet name="Austin" sheetId="12" r:id="rId12"/>
+    <sheet name="Avondale" sheetId="13" r:id="rId13"/>
+    <sheet name="Rush &amp; Division" sheetId="14" r:id="rId14"/>
+    <sheet name="Oakland" sheetId="15" r:id="rId15"/>
+    <sheet name="Chatham" sheetId="16" r:id="rId16"/>
+    <sheet name="New City" sheetId="17" r:id="rId17"/>
+    <sheet name="Belmont Cragin" sheetId="18" r:id="rId18"/>
+    <sheet name="West Loop" sheetId="19" r:id="rId19"/>
+    <sheet name="Uptown" sheetId="20" r:id="rId20"/>
+    <sheet name="Lake View" sheetId="21" r:id="rId21"/>
     <sheet name="Grand Boulevard" sheetId="22" r:id="rId22"/>
     <sheet name="West Town" sheetId="23" r:id="rId23"/>
     <sheet name="Englewood" sheetId="24" r:id="rId24"/>
@@ -856,13 +856,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2">
         <v>50</v>
       </c>
       <c r="D2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E2">
         <v>51</v>
@@ -871,25 +871,25 @@
         <v>65</v>
       </c>
       <c r="G2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L2">
         <v>105</v>
       </c>
       <c r="M2">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -900,7 +900,7 @@
         <v>61</v>
       </c>
       <c r="C3">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3">
         <v>99</v>
@@ -909,7 +909,7 @@
         <v>100</v>
       </c>
       <c r="F3">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G3">
         <v>94</v>
@@ -918,13 +918,13 @@
         <v>99</v>
       </c>
       <c r="I3">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J3">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K3">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L3">
         <v>179</v>
@@ -965,7 +965,7 @@
         <v>16</v>
       </c>
       <c r="K4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L4">
         <v>17</v>
@@ -1017,40 +1017,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C6">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D6">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E6">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="F6">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G6">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H6">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="I6">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J6">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K6">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L6">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M6">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1058,40 +1058,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C7">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D7">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E7">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="F7">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="G7">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="H7">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="I7">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="J7">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="K7">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="L7">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M7">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -1101,7 +1101,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -1164,187 +1164,144 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
       <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
       <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>3</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
       <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>13</v>
-      </c>
-      <c r="C5">
-        <v>25</v>
-      </c>
-      <c r="D5">
-        <v>15</v>
-      </c>
-      <c r="E5">
-        <v>24</v>
-      </c>
-      <c r="F5">
-        <v>24</v>
-      </c>
-      <c r="G5">
-        <v>18</v>
-      </c>
-      <c r="H5">
-        <v>30</v>
-      </c>
-      <c r="I5">
-        <v>16</v>
-      </c>
-      <c r="J5">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>18</v>
-      </c>
-      <c r="L5">
-        <v>11</v>
-      </c>
-      <c r="M5">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>36</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>12</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7">
+        <v>8</v>
+      </c>
+      <c r="L7">
+        <v>3</v>
+      </c>
+      <c r="M7">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1354,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -1418,135 +1375,200 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
       <c r="E3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K4">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
       <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>22</v>
+      </c>
+      <c r="C7">
+        <v>30</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>37</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="H7">
+        <v>32</v>
+      </c>
+      <c r="I7">
+        <v>31</v>
+      </c>
+      <c r="J7">
+        <v>31</v>
+      </c>
+      <c r="K7">
+        <v>48</v>
+      </c>
+      <c r="L7">
+        <v>46</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1619,23 +1641,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1643,34 +1683,61 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>9</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
       <c r="M4">
         <v>1</v>
       </c>
@@ -1680,40 +1747,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1721,40 +1788,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1763,6 +1830,416 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>13</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1850,7 +2327,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2085,7 +2562,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2198,6 +2675,9 @@
       <c r="C4">
         <v>4</v>
       </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
       <c r="E4">
         <v>2</v>
       </c>
@@ -2225,7 +2705,7 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2257,7 +2737,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2389,221 +2869,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>9</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>13</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>8</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2824,235 +3090,6 @@
       </c>
       <c r="M7">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>13</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>20</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>11</v>
-      </c>
-      <c r="K6">
-        <v>14</v>
-      </c>
-      <c r="L6">
-        <v>10</v>
-      </c>
-      <c r="M6">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3132,7 +3169,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -3153,7 +3190,7 @@
         <v>3</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3219,7 +3256,7 @@
         <v>18</v>
       </c>
       <c r="K5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L5">
         <v>20</v>
@@ -3239,7 +3276,7 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3315,7 +3352,7 @@
         <v>23</v>
       </c>
       <c r="E8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F8">
         <v>35</v>
@@ -3324,13 +3361,13 @@
         <v>24</v>
       </c>
       <c r="H8">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I8">
         <v>22</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K8">
         <v>34</v>
@@ -3358,6 +3395,9 @@
       <c r="G9">
         <v>1</v>
       </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
       <c r="I9">
         <v>2</v>
       </c>
@@ -3515,7 +3555,7 @@
         <v>1</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15">
         <v>1</v>
@@ -3581,7 +3621,7 @@
         <v>3</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -3898,7 +3938,7 @@
         <v>39</v>
       </c>
       <c r="D28">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E28">
         <v>24</v>
@@ -3998,7 +4038,7 @@
         <v>3</v>
       </c>
       <c r="K30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -4050,7 +4090,7 @@
         <v>40</v>
       </c>
       <c r="I32">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J32">
         <v>31</v>
@@ -4130,7 +4170,7 @@
         <v>42</v>
       </c>
       <c r="B36">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C36">
         <v>30</v>
@@ -4188,7 +4228,7 @@
         <v>2</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F38">
         <v>3</v>
@@ -4275,7 +4315,7 @@
         <v>6</v>
       </c>
       <c r="J41">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K41">
         <v>11</v>
@@ -4307,7 +4347,7 @@
         <v>3</v>
       </c>
       <c r="I42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J42">
         <v>6</v>
@@ -4608,10 +4648,10 @@
         <v>10</v>
       </c>
       <c r="K50">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L50">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M50">
         <v>13</v>
@@ -4713,13 +4753,13 @@
         <v>55</v>
       </c>
       <c r="G53">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H53">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I53">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J53">
         <v>89</v>
@@ -4763,7 +4803,7 @@
         <v>5</v>
       </c>
       <c r="J54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K54">
         <v>3</v>
@@ -4985,7 +5025,7 @@
         <v>4</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E63">
         <v>4</v>
@@ -5070,7 +5110,7 @@
         <v>12</v>
       </c>
       <c r="M65">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -5203,7 +5243,7 @@
         <v>10</v>
       </c>
       <c r="F70">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G70">
         <v>12</v>
@@ -5395,13 +5435,13 @@
         <v>10</v>
       </c>
       <c r="E76">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F76">
         <v>15</v>
       </c>
       <c r="G76">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H76">
         <v>14</v>
@@ -5577,7 +5617,7 @@
         <v>4</v>
       </c>
       <c r="K80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L80">
         <v>12</v>
@@ -5626,7 +5666,7 @@
         <v>11</v>
       </c>
       <c r="C82">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D82">
         <v>3</v>
@@ -5713,7 +5753,7 @@
         <v>5</v>
       </c>
       <c r="E85">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F85">
         <v>4</v>
@@ -5745,7 +5785,7 @@
         <v>92</v>
       </c>
       <c r="B86">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C86">
         <v>10</v>
@@ -5769,7 +5809,7 @@
         <v>8</v>
       </c>
       <c r="J86">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K86">
         <v>14</v>
@@ -5789,7 +5829,7 @@
         <v>4</v>
       </c>
       <c r="C87">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D87">
         <v>4</v>
@@ -6037,7 +6077,7 @@
         <v>6</v>
       </c>
       <c r="I94">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J94">
         <v>4</v>
@@ -6125,7 +6165,7 @@
         <v>3</v>
       </c>
       <c r="M96">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -6174,40 +6214,40 @@
         <v>6</v>
       </c>
       <c r="B98">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C98">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D98">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E98">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="F98">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="G98">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="H98">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="I98">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="J98">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="K98">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="L98">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M98">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -6379,140 +6419,125 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="B4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
       <c r="C5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>6</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -6520,40 +6545,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
         <v>20</v>
       </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>11</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
         <v>12</v>
       </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>17</v>
-      </c>
       <c r="I6">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K6">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L6">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -6626,41 +6651,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L2">
         <v>3</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -6668,86 +6690,101 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K3">
         <v>3</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
       <c r="H4">
         <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
         <v>10</v>
       </c>
-      <c r="C5">
-        <v>13</v>
-      </c>
-      <c r="D5">
+      <c r="I5">
         <v>16</v>
       </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>21</v>
-      </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>14</v>
-      </c>
       <c r="J5">
         <v>2</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>5</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -6755,40 +6792,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
         <v>12</v>
-      </c>
-      <c r="C6">
-        <v>15</v>
-      </c>
-      <c r="D6">
-        <v>17</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>24</v>
       </c>
       <c r="G6">
         <v>16</v>
       </c>
       <c r="H6">
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
+        <v>18</v>
+      </c>
+      <c r="L6">
+        <v>17</v>
+      </c>
+      <c r="M6">
         <v>12</v>
-      </c>
-      <c r="I6">
-        <v>19</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>11</v>
-      </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
-      <c r="M6">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -7157,7 +7194,7 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -7198,7 +7235,7 @@
         <v>6</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -7284,7 +7321,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -7438,7 +7475,7 @@
         <v>39</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
         <v>24</v>
@@ -7557,7 +7594,7 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -7586,7 +7623,7 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -7965,7 +8002,7 @@
         <v>2</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -8009,7 +8046,7 @@
         <v>15</v>
       </c>
       <c r="L5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -8047,10 +8084,10 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M6">
         <v>13</v>
@@ -8158,7 +8195,7 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -8242,7 +8279,7 @@
         <v>3</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -8418,7 +8455,7 @@
         <v>4</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K5">
         <v>4</v>
@@ -8459,7 +8496,7 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6">
         <v>11</v>
@@ -8478,10 +8515,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -8492,11 +8529,9 @@
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8513,38 +8548,29 @@
         <v>2018</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G1" s="1">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
+      <c r="D2">
         <v>1</v>
       </c>
       <c r="F2">
@@ -8554,136 +8580,117 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>7</v>
-      </c>
-      <c r="J4">
-        <v>9</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
         <v>8</v>
       </c>
-      <c r="H5">
-        <v>8</v>
-      </c>
-      <c r="I5">
-        <v>11</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-      <c r="M5">
-        <v>8</v>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -8788,6 +8795,9 @@
       <c r="I3">
         <v>3</v>
       </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
       <c r="K3">
         <v>1</v>
       </c>
@@ -8862,7 +8872,7 @@
         <v>5</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>3</v>
@@ -9714,7 +9724,7 @@
         <v>31</v>
       </c>
       <c r="I6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J6">
         <v>21</v>
@@ -9755,7 +9765,7 @@
         <v>40</v>
       </c>
       <c r="I7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J7">
         <v>31</v>
@@ -10260,7 +10270,7 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>4</v>
@@ -10350,7 +10360,7 @@
         <v>7</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5">
         <v>13</v>
@@ -10391,13 +10401,13 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6">
         <v>15</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H6">
         <v>14</v>
@@ -10847,7 +10857,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10861,9 +10871,11 @@
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10880,99 +10892,114 @@
         <v>2018</v>
       </c>
       <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
         <v>2020</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="H1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="I1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="J1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="K1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2">
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
       <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -10983,42 +11010,57 @@
       <c r="I5">
         <v>4</v>
       </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
         <v>8</v>
       </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
       <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
         <v>4</v>
       </c>
     </row>
@@ -11242,7 +11284,7 @@
         <v>1</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -11280,7 +11322,7 @@
         <v>3</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -11381,7 +11423,7 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -11451,7 +11493,7 @@
         <v>3</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5">
         <v>6</v>
@@ -11772,7 +11814,7 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
         <v>2</v>
@@ -11880,7 +11922,7 @@
         <v>4</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>12</v>
@@ -12010,7 +12052,7 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <v>4</v>
@@ -12103,7 +12145,7 @@
         <v>18</v>
       </c>
       <c r="K6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L6">
         <v>20</v>
@@ -12468,7 +12510,7 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -12509,7 +12551,7 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -12816,10 +12858,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -12879,8 +12921,17 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -12889,16 +12940,22 @@
         <v>2</v>
       </c>
       <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12908,111 +12965,125 @@
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="D3">
+      <c r="C3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>9</v>
-      </c>
-      <c r="F4">
-        <v>14</v>
-      </c>
-      <c r="G4">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>6</v>
-      </c>
-      <c r="I4">
-        <v>14</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>13</v>
-      </c>
-      <c r="L4">
-        <v>4</v>
-      </c>
-      <c r="M4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G5">
+        <v>11</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>14</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
         <v>12</v>
       </c>
-      <c r="H5">
-        <v>9</v>
-      </c>
-      <c r="I5">
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>24</v>
+      </c>
+      <c r="G6">
         <v>16</v>
       </c>
-      <c r="J5">
-        <v>7</v>
-      </c>
-      <c r="K5">
-        <v>17</v>
-      </c>
-      <c r="L5">
-        <v>7</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
+      <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>19</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>11</v>
+      </c>
+      <c r="L6">
+        <v>12</v>
+      </c>
+      <c r="M6">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -14308,10 +14379,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -14372,40 +14443,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>9</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>9</v>
-      </c>
-      <c r="J2">
-        <v>15</v>
-      </c>
-      <c r="K2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14413,168 +14472,119 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
+        <v>11</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>22</v>
-      </c>
-      <c r="C6">
-        <v>27</v>
-      </c>
-      <c r="D6">
-        <v>33</v>
-      </c>
-      <c r="E6">
-        <v>50</v>
-      </c>
-      <c r="F6">
-        <v>41</v>
-      </c>
-      <c r="G6">
-        <v>44</v>
-      </c>
-      <c r="H6">
-        <v>44</v>
-      </c>
-      <c r="I6">
-        <v>67</v>
-      </c>
-      <c r="J6">
-        <v>46</v>
-      </c>
-      <c r="K6">
-        <v>38</v>
-      </c>
-      <c r="L6">
-        <v>35</v>
-      </c>
-      <c r="M6">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>36</v>
-      </c>
-      <c r="C7">
-        <v>42</v>
-      </c>
-      <c r="D7">
-        <v>59</v>
-      </c>
-      <c r="E7">
-        <v>61</v>
-      </c>
-      <c r="F7">
-        <v>55</v>
-      </c>
-      <c r="G7">
-        <v>63</v>
-      </c>
-      <c r="H7">
-        <v>62</v>
-      </c>
-      <c r="I7">
-        <v>105</v>
-      </c>
-      <c r="J7">
-        <v>89</v>
-      </c>
-      <c r="K7">
-        <v>73</v>
-      </c>
-      <c r="L7">
-        <v>76</v>
-      </c>
-      <c r="M7">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -15191,6 +15201,9 @@
       <c r="E5">
         <v>4</v>
       </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
       <c r="I5">
         <v>1</v>
       </c>
@@ -15218,7 +15231,7 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -16099,10 +16112,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -16112,146 +16125,190 @@
     <col min="8" max="8" width="4.7109375" customWidth="1"/>
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
         <v>2016</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
         <v>2017</v>
       </c>
-      <c r="D1" s="1">
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
         <v>2019</v>
       </c>
-      <c r="E1" s="1">
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
         <v>2021</v>
       </c>
-      <c r="F1" s="1">
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="G1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="H1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="I1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="J1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2">
-        <v>5</v>
-      </c>
       <c r="J2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
       <c r="E3">
         <v>1</v>
       </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
       <c r="H3">
         <v>2</v>
       </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
       <c r="J3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>9</v>
+      </c>
+      <c r="F4">
+        <v>14</v>
+      </c>
+      <c r="G4">
+        <v>9</v>
       </c>
       <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>6</v>
+      </c>
+      <c r="I4">
+        <v>14</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>13</v>
+      </c>
+      <c r="L4">
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>19</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J5">
         <v>7</v>
       </c>
-      <c r="J7">
-        <v>9</v>
+      <c r="K5">
+        <v>17</v>
+      </c>
+      <c r="L5">
+        <v>7</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -16358,6 +16415,9 @@
       <c r="B4">
         <v>1</v>
       </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
       <c r="E4">
         <v>3</v>
       </c>
@@ -16385,7 +16445,7 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -16493,7 +16553,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -16542,7 +16602,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -17422,7 +17482,7 @@
 
 <file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -17432,9 +17492,10 @@
     <col min="5" max="5" width="4.7109375" customWidth="1"/>
     <col min="6" max="6" width="4.7109375" customWidth="1"/>
     <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -17451,21 +17512,24 @@
         <v>2020</v>
       </c>
       <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
         <v>2022</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -17476,7 +17540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -17498,8 +17562,11 @@
       <c r="G4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -17516,9 +17583,12 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
         <v>1</v>
       </c>
     </row>
@@ -17766,17 +17836,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
       <c r="F2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="J2">
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="L2">
+        <v>13</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -17786,41 +17877,86 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="H3">
+        <v>10</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="L3">
+        <v>23</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K5">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -17829,40 +17965,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17870,40 +18006,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>106</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -18759,7 +18895,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -18772,251 +18908,146 @@
     <col min="8" max="8" width="4.7109375" customWidth="1"/>
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="E1" s="1">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="G1" s="1">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
         <v>7</v>
       </c>
-      <c r="F3">
-        <v>15</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>8</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>25</v>
-      </c>
-      <c r="D6">
-        <v>17</v>
-      </c>
-      <c r="E6">
-        <v>18</v>
-      </c>
-      <c r="F6">
-        <v>16</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>20</v>
-      </c>
-      <c r="I6">
-        <v>15</v>
-      </c>
-      <c r="J6">
-        <v>18</v>
-      </c>
-      <c r="K6">
-        <v>31</v>
-      </c>
-      <c r="L6">
-        <v>33</v>
-      </c>
-      <c r="M6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>21</v>
-      </c>
-      <c r="C7">
-        <v>30</v>
-      </c>
-      <c r="D7">
-        <v>27</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>37</v>
-      </c>
-      <c r="G7">
-        <v>20</v>
-      </c>
-      <c r="H7">
-        <v>32</v>
-      </c>
-      <c r="I7">
-        <v>31</v>
-      </c>
       <c r="J7">
-        <v>31</v>
-      </c>
-      <c r="K7">
-        <v>48</v>
-      </c>
-      <c r="L7">
-        <v>46</v>
-      </c>
-      <c r="M7">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-ytd.xlsx
+++ b/output/cta-violent-crime-ytd.xlsx
@@ -9,36 +9,36 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Albany Park" sheetId="3" r:id="rId3"/>
-    <sheet name="Woodlawn" sheetId="4" r:id="rId4"/>
-    <sheet name="North Lawndale" sheetId="5" r:id="rId5"/>
-    <sheet name="South Shore" sheetId="6" r:id="rId6"/>
-    <sheet name="Old Town" sheetId="7" r:id="rId7"/>
-    <sheet name="Loop" sheetId="8" r:id="rId8"/>
-    <sheet name="O'Hare" sheetId="9" r:id="rId9"/>
-    <sheet name="Near South Side" sheetId="10" r:id="rId10"/>
-    <sheet name="Grand Crossing" sheetId="11" r:id="rId11"/>
-    <sheet name="Austin" sheetId="12" r:id="rId12"/>
-    <sheet name="Avondale" sheetId="13" r:id="rId13"/>
-    <sheet name="Rush &amp; Division" sheetId="14" r:id="rId14"/>
-    <sheet name="Oakland" sheetId="15" r:id="rId15"/>
-    <sheet name="Chatham" sheetId="16" r:id="rId16"/>
-    <sheet name="New City" sheetId="17" r:id="rId17"/>
-    <sheet name="Belmont Cragin" sheetId="18" r:id="rId18"/>
-    <sheet name="West Loop" sheetId="19" r:id="rId19"/>
-    <sheet name="Uptown" sheetId="20" r:id="rId20"/>
-    <sheet name="Lake View" sheetId="21" r:id="rId21"/>
-    <sheet name="Grand Boulevard" sheetId="22" r:id="rId22"/>
-    <sheet name="West Town" sheetId="23" r:id="rId23"/>
-    <sheet name="Englewood" sheetId="24" r:id="rId24"/>
-    <sheet name="Greektown" sheetId="25" r:id="rId25"/>
-    <sheet name="Edgewater" sheetId="26" r:id="rId26"/>
-    <sheet name="Little Italy, UIC" sheetId="27" r:id="rId27"/>
-    <sheet name="Gage Park" sheetId="28" r:id="rId28"/>
-    <sheet name="Humboldt Park" sheetId="29" r:id="rId29"/>
-    <sheet name="Lower West Side" sheetId="30" r:id="rId30"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="31" r:id="rId31"/>
-    <sheet name="Roseland" sheetId="32" r:id="rId32"/>
+    <sheet name="Austin" sheetId="3" r:id="rId3"/>
+    <sheet name="Roseland" sheetId="4" r:id="rId4"/>
+    <sheet name="Albany Park" sheetId="5" r:id="rId5"/>
+    <sheet name="Woodlawn" sheetId="6" r:id="rId6"/>
+    <sheet name="North Lawndale" sheetId="7" r:id="rId7"/>
+    <sheet name="South Shore" sheetId="8" r:id="rId8"/>
+    <sheet name="Old Town" sheetId="9" r:id="rId9"/>
+    <sheet name="Loop" sheetId="10" r:id="rId10"/>
+    <sheet name="O'Hare" sheetId="11" r:id="rId11"/>
+    <sheet name="Near South Side" sheetId="12" r:id="rId12"/>
+    <sheet name="Grand Crossing" sheetId="13" r:id="rId13"/>
+    <sheet name="Avondale" sheetId="14" r:id="rId14"/>
+    <sheet name="Rush &amp; Division" sheetId="15" r:id="rId15"/>
+    <sheet name="Oakland" sheetId="16" r:id="rId16"/>
+    <sheet name="Chatham" sheetId="17" r:id="rId17"/>
+    <sheet name="New City" sheetId="18" r:id="rId18"/>
+    <sheet name="Belmont Cragin" sheetId="19" r:id="rId19"/>
+    <sheet name="West Loop" sheetId="20" r:id="rId20"/>
+    <sheet name="Uptown" sheetId="21" r:id="rId21"/>
+    <sheet name="Lake View" sheetId="22" r:id="rId22"/>
+    <sheet name="Grand Boulevard" sheetId="23" r:id="rId23"/>
+    <sheet name="West Town" sheetId="24" r:id="rId24"/>
+    <sheet name="Englewood" sheetId="25" r:id="rId25"/>
+    <sheet name="Greektown" sheetId="26" r:id="rId26"/>
+    <sheet name="Edgewater" sheetId="27" r:id="rId27"/>
+    <sheet name="Little Italy, UIC" sheetId="28" r:id="rId28"/>
+    <sheet name="Gage Park" sheetId="29" r:id="rId29"/>
+    <sheet name="Humboldt Park" sheetId="30" r:id="rId30"/>
+    <sheet name="Lower West Side" sheetId="31" r:id="rId31"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="32" r:id="rId32"/>
     <sheet name="Norwood Park" sheetId="33" r:id="rId33"/>
     <sheet name="Garfield Park" sheetId="34" r:id="rId34"/>
     <sheet name="Wrigleyville" sheetId="35" r:id="rId35"/>
@@ -865,7 +865,7 @@
         <v>70</v>
       </c>
       <c r="E2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F2">
         <v>65</v>
@@ -880,7 +880,7 @@
         <v>89</v>
       </c>
       <c r="J2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K2">
         <v>105</v>
@@ -903,7 +903,7 @@
         <v>65</v>
       </c>
       <c r="D3">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E3">
         <v>100</v>
@@ -912,25 +912,25 @@
         <v>96</v>
       </c>
       <c r="G3">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H3">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I3">
         <v>151</v>
       </c>
       <c r="J3">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K3">
         <v>168</v>
       </c>
       <c r="L3">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M3">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -953,7 +953,7 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4">
         <v>11</v>
@@ -971,7 +971,7 @@
         <v>17</v>
       </c>
       <c r="M4">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1017,10 +1017,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C6">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D6">
         <v>311</v>
@@ -1035,19 +1035,19 @@
         <v>362</v>
       </c>
       <c r="H6">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="I6">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J6">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K6">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L6">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="M6">
         <v>194</v>
@@ -1058,40 +1058,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C7">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D7">
+        <v>487</v>
+      </c>
+      <c r="E7">
         <v>486</v>
-      </c>
-      <c r="E7">
-        <v>485</v>
       </c>
       <c r="F7">
         <v>563</v>
       </c>
       <c r="G7">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="H7">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="I7">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="J7">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K7">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="L7">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="M7">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -1164,17 +1164,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
       <c r="F2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="J2">
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="L2">
+        <v>13</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -1184,41 +1205,86 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="H3">
+        <v>11</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="L3">
+        <v>24</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K5">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -1227,40 +1293,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1268,40 +1334,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>106</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1310,6 +1376,168 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>5</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1374,98 +1602,53 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
       <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -1473,19 +1656,7 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -1494,40 +1665,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1535,40 +1706,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="J7">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1576,9 +1747,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -1642,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
         <v>5</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1683,60 +1854,54 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>5</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K3">
         <v>10</v>
       </c>
       <c r="L3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
       <c r="E4">
         <v>1</v>
       </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
       <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -1744,286 +1909,104 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>13</v>
-      </c>
-      <c r="C5">
-        <v>25</v>
-      </c>
-      <c r="D5">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>25</v>
-      </c>
-      <c r="F5">
-        <v>24</v>
-      </c>
-      <c r="G5">
-        <v>18</v>
-      </c>
-      <c r="H5">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>16</v>
-      </c>
-      <c r="J5">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>25</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>18</v>
+      </c>
+      <c r="F6">
+        <v>16</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>20</v>
+      </c>
+      <c r="I6">
+        <v>15</v>
+      </c>
+      <c r="J6">
+        <v>18</v>
+      </c>
+      <c r="K6">
+        <v>31</v>
+      </c>
+      <c r="L6">
+        <v>33</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
         <v>22</v>
       </c>
-      <c r="C6">
-        <v>34</v>
-      </c>
-      <c r="D6">
-        <v>23</v>
-      </c>
-      <c r="E6">
-        <v>34</v>
-      </c>
-      <c r="F6">
-        <v>35</v>
-      </c>
-      <c r="G6">
-        <v>24</v>
-      </c>
-      <c r="H6">
-        <v>44</v>
-      </c>
-      <c r="I6">
-        <v>22</v>
-      </c>
-      <c r="J6">
+      <c r="C7">
+        <v>30</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>37</v>
+      </c>
+      <c r="G7">
+        <v>21</v>
+      </c>
+      <c r="H7">
         <v>32</v>
       </c>
-      <c r="K6">
-        <v>34</v>
-      </c>
-      <c r="L6">
-        <v>22</v>
-      </c>
-      <c r="M6">
-        <v>36</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>7</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
+      <c r="I7">
+        <v>31</v>
+      </c>
+      <c r="J7">
+        <v>31</v>
+      </c>
+      <c r="K7">
+        <v>48</v>
+      </c>
+      <c r="L7">
+        <v>46</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2096,59 +2079,59 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
         <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -2157,40 +2140,34 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2198,40 +2175,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>3</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2240,6 +2217,214 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>13</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2327,7 +2512,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2414,7 +2599,7 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <v>5</v>
@@ -2545,7 +2730,7 @@
         <v>16</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K6">
         <v>24</v>
@@ -2562,7 +2747,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2737,7 +2922,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2862,234 +3047,6 @@
       </c>
       <c r="I6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>11</v>
-      </c>
-      <c r="I7">
-        <v>9</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>9</v>
-      </c>
-      <c r="M7">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3305,7 +3262,7 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7">
         <v>7</v>
@@ -3352,7 +3309,7 @@
         <v>23</v>
       </c>
       <c r="E8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8">
         <v>35</v>
@@ -3361,7 +3318,7 @@
         <v>24</v>
       </c>
       <c r="H8">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I8">
         <v>22</v>
@@ -3376,7 +3333,7 @@
         <v>22</v>
       </c>
       <c r="M8">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3671,7 +3628,7 @@
         <v>16</v>
       </c>
       <c r="J19">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K19">
         <v>24</v>
@@ -3799,7 +3756,7 @@
         <v>29</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23">
         <v>5</v>
@@ -3938,7 +3895,7 @@
         <v>39</v>
       </c>
       <c r="D28">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E28">
         <v>24</v>
@@ -3953,7 +3910,7 @@
         <v>37</v>
       </c>
       <c r="I28">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J28">
         <v>21</v>
@@ -4035,7 +3992,7 @@
         <v>3</v>
       </c>
       <c r="J30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30">
         <v>12</v>
@@ -4096,10 +4053,10 @@
         <v>31</v>
       </c>
       <c r="K32">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L32">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M32">
         <v>27</v>
@@ -4185,7 +4142,7 @@
         <v>37</v>
       </c>
       <c r="G36">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H36">
         <v>32</v>
@@ -4639,7 +4596,7 @@
         <v>14</v>
       </c>
       <c r="H50">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I50">
         <v>12</v>
@@ -4756,7 +4713,7 @@
         <v>64</v>
       </c>
       <c r="H53">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I53">
         <v>106</v>
@@ -4765,10 +4722,10 @@
         <v>89</v>
       </c>
       <c r="K53">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L53">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M53">
         <v>45</v>
@@ -5107,7 +5064,7 @@
         <v>11</v>
       </c>
       <c r="L65">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M65">
         <v>8</v>
@@ -5377,7 +5334,7 @@
         <v>15</v>
       </c>
       <c r="J74">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K74">
         <v>13</v>
@@ -5482,7 +5439,7 @@
         <v>13</v>
       </c>
       <c r="G77">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H77">
         <v>21</v>
@@ -5497,10 +5454,10 @@
         <v>21</v>
       </c>
       <c r="L77">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M77">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -5666,7 +5623,7 @@
         <v>11</v>
       </c>
       <c r="C82">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D82">
         <v>3</v>
@@ -5733,7 +5690,7 @@
         <v>1</v>
       </c>
       <c r="L84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M84">
         <v>1</v>
@@ -5803,7 +5760,7 @@
         <v>20</v>
       </c>
       <c r="H86">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I86">
         <v>8</v>
@@ -6214,40 +6171,40 @@
         <v>6</v>
       </c>
       <c r="B98">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C98">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D98">
+        <v>487</v>
+      </c>
+      <c r="E98">
         <v>486</v>
-      </c>
-      <c r="E98">
-        <v>485</v>
       </c>
       <c r="F98">
         <v>563</v>
       </c>
       <c r="G98">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="H98">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="I98">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="J98">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K98">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="L98">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="M98">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -6356,7 +6313,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -6423,28 +6380,19 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -6457,128 +6405,133 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L3">
         <v>3</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>13</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6">
         <v>7</v>
       </c>
-      <c r="C6">
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
         <v>10</v>
       </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>20</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
-      <c r="K6">
-        <v>14</v>
-      </c>
-      <c r="L6">
+      <c r="H7">
+        <v>11</v>
+      </c>
+      <c r="I7">
+        <v>9</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7">
         <v>10</v>
       </c>
-      <c r="M6">
-        <v>8</v>
+      <c r="L7">
+        <v>9</v>
+      </c>
+      <c r="M7">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -6651,140 +6604,125 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="B4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
       <c r="C5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>13</v>
+      </c>
+      <c r="H5">
         <v>7</v>
       </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>8</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
       <c r="I5">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>6</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -6792,40 +6730,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
         <v>20</v>
       </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>11</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
+        <v>13</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6">
         <v>12</v>
       </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>17</v>
-      </c>
-      <c r="I6">
-        <v>20</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
-      </c>
       <c r="K6">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L6">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -6834,6 +6772,253 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>16</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
+        <v>18</v>
+      </c>
+      <c r="L6">
+        <v>17</v>
+      </c>
+      <c r="M6">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7041,7 +7226,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7255,7 +7440,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7362,7 +7547,7 @@
         <v>4</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3">
         <v>6</v>
@@ -7449,7 +7634,7 @@
         <v>22</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -7475,7 +7660,7 @@
         <v>39</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>24</v>
@@ -7490,7 +7675,7 @@
         <v>37</v>
       </c>
       <c r="I7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J7">
         <v>21</v>
@@ -7510,7 +7695,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7645,220 +7830,6 @@
       </c>
       <c r="J6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>6</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>11</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -7932,12 +7903,15 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
-      <c r="H2">
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
@@ -7947,66 +7921,45 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
       <c r="M4">
         <v>1</v>
       </c>
@@ -8016,40 +7969,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -8057,40 +8010,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>8</v>
       </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>14</v>
-      </c>
-      <c r="F6">
-        <v>23</v>
-      </c>
       <c r="G6">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>11</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -8099,6 +8052,238 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>21</v>
+      </c>
+      <c r="G5">
+        <v>13</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>7</v>
+      </c>
+      <c r="K5">
+        <v>15</v>
+      </c>
+      <c r="L5">
+        <v>11</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>23</v>
+      </c>
+      <c r="G6">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>10</v>
+      </c>
+      <c r="K6">
+        <v>25</v>
+      </c>
+      <c r="L6">
+        <v>19</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8238,7 +8423,7 @@
         <v>2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -8276,7 +8461,7 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6">
         <v>12</v>
@@ -8293,7 +8478,260 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>9</v>
+      </c>
+      <c r="M3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>25</v>
+      </c>
+      <c r="D5">
+        <v>15</v>
+      </c>
+      <c r="E5">
+        <v>25</v>
+      </c>
+      <c r="F5">
+        <v>24</v>
+      </c>
+      <c r="G5">
+        <v>18</v>
+      </c>
+      <c r="H5">
+        <v>36</v>
+      </c>
+      <c r="I5">
+        <v>16</v>
+      </c>
+      <c r="J5">
+        <v>16</v>
+      </c>
+      <c r="K5">
+        <v>18</v>
+      </c>
+      <c r="L5">
+        <v>11</v>
+      </c>
+      <c r="M5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>34</v>
+      </c>
+      <c r="D6">
+        <v>23</v>
+      </c>
+      <c r="E6">
+        <v>35</v>
+      </c>
+      <c r="F6">
+        <v>35</v>
+      </c>
+      <c r="G6">
+        <v>24</v>
+      </c>
+      <c r="H6">
+        <v>45</v>
+      </c>
+      <c r="I6">
+        <v>22</v>
+      </c>
+      <c r="J6">
+        <v>32</v>
+      </c>
+      <c r="K6">
+        <v>34</v>
+      </c>
+      <c r="L6">
+        <v>22</v>
+      </c>
+      <c r="M6">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8513,192 +8951,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8889,7 +9142,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9096,261 +9349,6 @@
       </c>
       <c r="M6">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>5</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>5</v>
-      </c>
-      <c r="I3">
-        <v>7</v>
-      </c>
-      <c r="J3">
-        <v>8</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>14</v>
-      </c>
-      <c r="C6">
-        <v>12</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>13</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>12</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>22</v>
-      </c>
-      <c r="J6">
-        <v>15</v>
-      </c>
-      <c r="K6">
-        <v>14</v>
-      </c>
-      <c r="L6">
-        <v>14</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>20</v>
-      </c>
-      <c r="C7">
-        <v>19</v>
-      </c>
-      <c r="D7">
-        <v>11</v>
-      </c>
-      <c r="E7">
-        <v>21</v>
-      </c>
-      <c r="F7">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>17</v>
-      </c>
-      <c r="H7">
-        <v>21</v>
-      </c>
-      <c r="I7">
-        <v>35</v>
-      </c>
-      <c r="J7">
-        <v>25</v>
-      </c>
-      <c r="K7">
-        <v>21</v>
-      </c>
-      <c r="L7">
-        <v>20</v>
-      </c>
-      <c r="M7">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -9730,10 +9728,10 @@
         <v>21</v>
       </c>
       <c r="K6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M6">
         <v>12</v>
@@ -9771,10 +9769,10 @@
         <v>31</v>
       </c>
       <c r="K7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M7">
         <v>27</v>
@@ -10113,7 +10111,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -10154,7 +10152,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>7</v>
@@ -10857,7 +10855,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10923,16 +10921,37 @@
       <c r="B2">
         <v>2</v>
       </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
       </c>
       <c r="I2">
+        <v>5</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -10941,127 +10960,150 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
         <v>4</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>7</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>11</v>
+      </c>
+      <c r="E7">
+        <v>21</v>
+      </c>
+      <c r="F7">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>21</v>
+      </c>
+      <c r="I7">
+        <v>35</v>
+      </c>
+      <c r="J7">
+        <v>25</v>
+      </c>
+      <c r="K7">
+        <v>21</v>
+      </c>
+      <c r="L7">
+        <v>21</v>
+      </c>
+      <c r="M7">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -12284,7 +12326,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -12319,7 +12361,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -12858,7 +12900,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12872,11 +12914,9 @@
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12893,197 +12933,149 @@
         <v>2018</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G1" s="1">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>14</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
         <v>8</v>
       </c>
-      <c r="F6">
-        <v>24</v>
-      </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
       <c r="I6">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>11</v>
-      </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
-      <c r="M6">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -13361,7 +13353,7 @@
         <v>3</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <v>3</v>
@@ -13454,7 +13446,7 @@
         <v>15</v>
       </c>
       <c r="J6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6">
         <v>13</v>
@@ -14379,10 +14371,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -14445,26 +14437,17 @@
       <c r="B2">
         <v>2</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="F2">
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14475,116 +14458,124 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>8</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>7</v>
-      </c>
-      <c r="J4">
-        <v>9</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>13</v>
+      </c>
+      <c r="C6">
         <v>10</v>
       </c>
-      <c r="G5">
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
         <v>8</v>
       </c>
-      <c r="H5">
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
         <v>8</v>
       </c>
-      <c r="I5">
-        <v>11</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-      <c r="M5">
-        <v>8</v>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -16087,6 +16078,9 @@
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -16099,7 +16093,7 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -16112,10 +16106,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -16175,8 +16169,17 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -16185,16 +16188,22 @@
         <v>2</v>
       </c>
       <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16204,111 +16213,125 @@
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="D3">
+      <c r="C3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>9</v>
-      </c>
-      <c r="F4">
-        <v>14</v>
-      </c>
-      <c r="G4">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>6</v>
-      </c>
-      <c r="I4">
-        <v>14</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>13</v>
-      </c>
-      <c r="L4">
-        <v>4</v>
-      </c>
-      <c r="M4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F5">
+        <v>21</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>14</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>24</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
         <v>19</v>
       </c>
-      <c r="G5">
-        <v>12</v>
-      </c>
-      <c r="H5">
-        <v>9</v>
-      </c>
-      <c r="I5">
-        <v>16</v>
-      </c>
-      <c r="J5">
-        <v>7</v>
-      </c>
-      <c r="K5">
-        <v>17</v>
-      </c>
-      <c r="L5">
-        <v>7</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>11</v>
+      </c>
+      <c r="L6">
+        <v>13</v>
+      </c>
+      <c r="M6">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -17773,10 +17796,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -17837,40 +17860,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>9</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>10</v>
-      </c>
-      <c r="J2">
-        <v>15</v>
-      </c>
-      <c r="K2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17878,168 +17889,119 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>13</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
+        <v>11</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>22</v>
-      </c>
-      <c r="C6">
-        <v>27</v>
-      </c>
-      <c r="D6">
-        <v>33</v>
-      </c>
-      <c r="E6">
-        <v>50</v>
-      </c>
-      <c r="F6">
-        <v>41</v>
-      </c>
-      <c r="G6">
-        <v>45</v>
-      </c>
-      <c r="H6">
-        <v>46</v>
-      </c>
-      <c r="I6">
-        <v>67</v>
-      </c>
-      <c r="J6">
-        <v>46</v>
-      </c>
-      <c r="K6">
-        <v>38</v>
-      </c>
-      <c r="L6">
-        <v>35</v>
-      </c>
-      <c r="M6">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>36</v>
-      </c>
-      <c r="C7">
-        <v>42</v>
-      </c>
-      <c r="D7">
-        <v>59</v>
-      </c>
-      <c r="E7">
-        <v>61</v>
-      </c>
-      <c r="F7">
-        <v>55</v>
-      </c>
-      <c r="G7">
-        <v>64</v>
-      </c>
-      <c r="H7">
-        <v>64</v>
-      </c>
-      <c r="I7">
-        <v>106</v>
-      </c>
-      <c r="J7">
-        <v>89</v>
-      </c>
-      <c r="K7">
-        <v>73</v>
-      </c>
-      <c r="L7">
-        <v>76</v>
-      </c>
-      <c r="M7">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -18895,10 +18857,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -18908,146 +18870,190 @@
     <col min="8" max="8" width="4.7109375" customWidth="1"/>
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
         <v>2016</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
         <v>2017</v>
       </c>
-      <c r="D1" s="1">
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
         <v>2019</v>
       </c>
-      <c r="E1" s="1">
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
         <v>2021</v>
       </c>
-      <c r="F1" s="1">
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="G1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="H1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="I1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="J1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2">
-        <v>5</v>
-      </c>
       <c r="J2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
       <c r="E3">
         <v>1</v>
       </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
       <c r="H3">
         <v>2</v>
       </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
       <c r="J3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>9</v>
+      </c>
+      <c r="F4">
+        <v>14</v>
+      </c>
+      <c r="G4">
+        <v>9</v>
       </c>
       <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>6</v>
+      </c>
+      <c r="I4">
+        <v>14</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>13</v>
+      </c>
+      <c r="L4">
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>19</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J5">
         <v>7</v>
       </c>
-      <c r="J7">
-        <v>9</v>
+      <c r="K5">
+        <v>17</v>
+      </c>
+      <c r="L5">
+        <v>7</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-ytd.xlsx
+++ b/output/cta-violent-crime-ytd.xlsx
@@ -28,80 +28,80 @@
     <sheet name="Belmont Cragin" sheetId="19" r:id="rId19"/>
     <sheet name="West Loop" sheetId="20" r:id="rId20"/>
     <sheet name="Uptown" sheetId="21" r:id="rId21"/>
-    <sheet name="Lake View" sheetId="22" r:id="rId22"/>
-    <sheet name="Grand Boulevard" sheetId="23" r:id="rId23"/>
-    <sheet name="West Town" sheetId="24" r:id="rId24"/>
-    <sheet name="Englewood" sheetId="25" r:id="rId25"/>
-    <sheet name="Greektown" sheetId="26" r:id="rId26"/>
-    <sheet name="Edgewater" sheetId="27" r:id="rId27"/>
-    <sheet name="Little Italy, UIC" sheetId="28" r:id="rId28"/>
-    <sheet name="Gage Park" sheetId="29" r:id="rId29"/>
-    <sheet name="Humboldt Park" sheetId="30" r:id="rId30"/>
-    <sheet name="Lower West Side" sheetId="31" r:id="rId31"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="32" r:id="rId32"/>
-    <sheet name="Norwood Park" sheetId="33" r:id="rId33"/>
-    <sheet name="Garfield Park" sheetId="34" r:id="rId34"/>
-    <sheet name="Wrigleyville" sheetId="35" r:id="rId35"/>
-    <sheet name="Auburn Gresham" sheetId="36" r:id="rId36"/>
-    <sheet name="Rogers Park" sheetId="37" r:id="rId37"/>
-    <sheet name="Washington Park" sheetId="38" r:id="rId38"/>
-    <sheet name="Chicago Lawn" sheetId="39" r:id="rId39"/>
-    <sheet name="Kenwood" sheetId="40" r:id="rId40"/>
-    <sheet name="Calumet Heights" sheetId="41" r:id="rId41"/>
-    <sheet name="Hyde Park" sheetId="42" r:id="rId42"/>
-    <sheet name="Fuller Park" sheetId="43" r:id="rId43"/>
-    <sheet name="South Chicago" sheetId="44" r:id="rId44"/>
-    <sheet name="Armour Square" sheetId="45" r:id="rId45"/>
-    <sheet name="Douglas" sheetId="46" r:id="rId46"/>
-    <sheet name="United Center" sheetId="47" r:id="rId47"/>
-    <sheet name="Grant Park" sheetId="48" r:id="rId48"/>
-    <sheet name="Jefferson Park" sheetId="49" r:id="rId49"/>
-    <sheet name="Streeterville" sheetId="50" r:id="rId50"/>
-    <sheet name="Millenium Park" sheetId="51" r:id="rId51"/>
-    <sheet name="River North" sheetId="52" r:id="rId52"/>
-    <sheet name="Beverly" sheetId="53" r:id="rId53"/>
-    <sheet name="South Deering" sheetId="54" r:id="rId54"/>
-    <sheet name="West Elsdon" sheetId="55" r:id="rId55"/>
-    <sheet name="Pullman" sheetId="56" r:id="rId56"/>
-    <sheet name="West Pullman" sheetId="57" r:id="rId57"/>
-    <sheet name="Morgan Park" sheetId="58" r:id="rId58"/>
-    <sheet name="Wicker Park" sheetId="59" r:id="rId59"/>
-    <sheet name="Little Village" sheetId="60" r:id="rId60"/>
-    <sheet name="Irving Park" sheetId="61" r:id="rId61"/>
-    <sheet name="Jackson Park" sheetId="62" r:id="rId62"/>
-    <sheet name="Brighton Park" sheetId="63" r:id="rId63"/>
-    <sheet name="Bridgeport" sheetId="64" r:id="rId64"/>
-    <sheet name="Clearing" sheetId="65" r:id="rId65"/>
-    <sheet name="Mckinley Park" sheetId="66" r:id="rId66"/>
-    <sheet name="Chinatown" sheetId="67" r:id="rId67"/>
-    <sheet name="Bucktown" sheetId="68" r:id="rId68"/>
-    <sheet name="Ukrainian Village" sheetId="69" r:id="rId69"/>
-    <sheet name="Ashburn" sheetId="70" r:id="rId70"/>
-    <sheet name="Washington Heights" sheetId="71" r:id="rId71"/>
-    <sheet name="Printers Row" sheetId="72" r:id="rId72"/>
-    <sheet name="Logan Square" sheetId="73" r:id="rId73"/>
-    <sheet name="Lincoln Park" sheetId="74" r:id="rId74"/>
-    <sheet name="Lincoln Square" sheetId="75" r:id="rId75"/>
-    <sheet name="Archer Heights" sheetId="76" r:id="rId76"/>
-    <sheet name="Avalon Park" sheetId="77" r:id="rId77"/>
-    <sheet name="Burnside" sheetId="78" r:id="rId78"/>
-    <sheet name="East Side" sheetId="79" r:id="rId79"/>
-    <sheet name="Portage Park" sheetId="80" r:id="rId80"/>
-    <sheet name="Montclare" sheetId="81" r:id="rId81"/>
-    <sheet name="Hermosa" sheetId="82" r:id="rId82"/>
-    <sheet name="West Ridge" sheetId="83" r:id="rId83"/>
-    <sheet name="North Park" sheetId="84" r:id="rId84"/>
-    <sheet name="North Center" sheetId="85" r:id="rId85"/>
-    <sheet name="Magnificent Mile" sheetId="86" r:id="rId86"/>
-    <sheet name="Riverdale" sheetId="87" r:id="rId87"/>
-    <sheet name="Galewood" sheetId="88" r:id="rId88"/>
-    <sheet name="Gold Coast" sheetId="89" r:id="rId89"/>
-    <sheet name="Mount Greenwood" sheetId="90" r:id="rId90"/>
-    <sheet name="West Lawn" sheetId="91" r:id="rId91"/>
-    <sheet name="Boystown" sheetId="92" r:id="rId92"/>
-    <sheet name="East Village" sheetId="93" r:id="rId93"/>
-    <sheet name="Dunning" sheetId="94" r:id="rId94"/>
-    <sheet name="Hegewisch" sheetId="95" r:id="rId95"/>
+    <sheet name="Hegewisch" sheetId="22" r:id="rId22"/>
+    <sheet name="Lake View" sheetId="23" r:id="rId23"/>
+    <sheet name="Grand Boulevard" sheetId="24" r:id="rId24"/>
+    <sheet name="West Town" sheetId="25" r:id="rId25"/>
+    <sheet name="Englewood" sheetId="26" r:id="rId26"/>
+    <sheet name="Greektown" sheetId="27" r:id="rId27"/>
+    <sheet name="Edgewater" sheetId="28" r:id="rId28"/>
+    <sheet name="Little Italy, UIC" sheetId="29" r:id="rId29"/>
+    <sheet name="Gage Park" sheetId="30" r:id="rId30"/>
+    <sheet name="Humboldt Park" sheetId="31" r:id="rId31"/>
+    <sheet name="Lower West Side" sheetId="32" r:id="rId32"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="33" r:id="rId33"/>
+    <sheet name="Norwood Park" sheetId="34" r:id="rId34"/>
+    <sheet name="Garfield Park" sheetId="35" r:id="rId35"/>
+    <sheet name="Wrigleyville" sheetId="36" r:id="rId36"/>
+    <sheet name="Auburn Gresham" sheetId="37" r:id="rId37"/>
+    <sheet name="Rogers Park" sheetId="38" r:id="rId38"/>
+    <sheet name="Washington Park" sheetId="39" r:id="rId39"/>
+    <sheet name="Chicago Lawn" sheetId="40" r:id="rId40"/>
+    <sheet name="Kenwood" sheetId="41" r:id="rId41"/>
+    <sheet name="Calumet Heights" sheetId="42" r:id="rId42"/>
+    <sheet name="Hyde Park" sheetId="43" r:id="rId43"/>
+    <sheet name="Fuller Park" sheetId="44" r:id="rId44"/>
+    <sheet name="South Chicago" sheetId="45" r:id="rId45"/>
+    <sheet name="Armour Square" sheetId="46" r:id="rId46"/>
+    <sheet name="Douglas" sheetId="47" r:id="rId47"/>
+    <sheet name="United Center" sheetId="48" r:id="rId48"/>
+    <sheet name="Grant Park" sheetId="49" r:id="rId49"/>
+    <sheet name="Jefferson Park" sheetId="50" r:id="rId50"/>
+    <sheet name="Streeterville" sheetId="51" r:id="rId51"/>
+    <sheet name="Millenium Park" sheetId="52" r:id="rId52"/>
+    <sheet name="River North" sheetId="53" r:id="rId53"/>
+    <sheet name="Beverly" sheetId="54" r:id="rId54"/>
+    <sheet name="South Deering" sheetId="55" r:id="rId55"/>
+    <sheet name="West Elsdon" sheetId="56" r:id="rId56"/>
+    <sheet name="Pullman" sheetId="57" r:id="rId57"/>
+    <sheet name="West Pullman" sheetId="58" r:id="rId58"/>
+    <sheet name="Morgan Park" sheetId="59" r:id="rId59"/>
+    <sheet name="Wicker Park" sheetId="60" r:id="rId60"/>
+    <sheet name="Little Village" sheetId="61" r:id="rId61"/>
+    <sheet name="Irving Park" sheetId="62" r:id="rId62"/>
+    <sheet name="Jackson Park" sheetId="63" r:id="rId63"/>
+    <sheet name="Brighton Park" sheetId="64" r:id="rId64"/>
+    <sheet name="Bridgeport" sheetId="65" r:id="rId65"/>
+    <sheet name="Clearing" sheetId="66" r:id="rId66"/>
+    <sheet name="Mckinley Park" sheetId="67" r:id="rId67"/>
+    <sheet name="Chinatown" sheetId="68" r:id="rId68"/>
+    <sheet name="Bucktown" sheetId="69" r:id="rId69"/>
+    <sheet name="Ukrainian Village" sheetId="70" r:id="rId70"/>
+    <sheet name="Ashburn" sheetId="71" r:id="rId71"/>
+    <sheet name="Washington Heights" sheetId="72" r:id="rId72"/>
+    <sheet name="Printers Row" sheetId="73" r:id="rId73"/>
+    <sheet name="Logan Square" sheetId="74" r:id="rId74"/>
+    <sheet name="Lincoln Park" sheetId="75" r:id="rId75"/>
+    <sheet name="Lincoln Square" sheetId="76" r:id="rId76"/>
+    <sheet name="Archer Heights" sheetId="77" r:id="rId77"/>
+    <sheet name="Avalon Park" sheetId="78" r:id="rId78"/>
+    <sheet name="Burnside" sheetId="79" r:id="rId79"/>
+    <sheet name="East Side" sheetId="80" r:id="rId80"/>
+    <sheet name="Portage Park" sheetId="81" r:id="rId81"/>
+    <sheet name="Montclare" sheetId="82" r:id="rId82"/>
+    <sheet name="Hermosa" sheetId="83" r:id="rId83"/>
+    <sheet name="West Ridge" sheetId="84" r:id="rId84"/>
+    <sheet name="North Park" sheetId="85" r:id="rId85"/>
+    <sheet name="North Center" sheetId="86" r:id="rId86"/>
+    <sheet name="Magnificent Mile" sheetId="87" r:id="rId87"/>
+    <sheet name="Riverdale" sheetId="88" r:id="rId88"/>
+    <sheet name="Galewood" sheetId="89" r:id="rId89"/>
+    <sheet name="Gold Coast" sheetId="90" r:id="rId90"/>
+    <sheet name="Mount Greenwood" sheetId="91" r:id="rId91"/>
+    <sheet name="West Lawn" sheetId="92" r:id="rId92"/>
+    <sheet name="Boystown" sheetId="93" r:id="rId93"/>
+    <sheet name="East Village" sheetId="94" r:id="rId94"/>
+    <sheet name="Dunning" sheetId="95" r:id="rId95"/>
     <sheet name="Andersonville" sheetId="96" r:id="rId96"/>
     <sheet name="Garfield Ridge" sheetId="97" r:id="rId97"/>
   </sheets>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="104">
   <si>
     <t>crime_category</t>
   </si>
@@ -930,7 +930,7 @@
         <v>181</v>
       </c>
       <c r="M3">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>657</v>
       </c>
       <c r="M7">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -4222,6 +4222,9 @@
       <c r="G39">
         <v>1</v>
       </c>
+      <c r="M39">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="2" t="s">
@@ -6204,7 +6207,7 @@
         <v>657</v>
       </c>
       <c r="M98">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -6773,6 +6776,84 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7018,7 +7099,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7226,7 +7307,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7440,7 +7521,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7695,7 +7776,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7830,220 +7911,6 @@
       </c>
       <c r="J6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>6</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>11</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -8117,12 +7984,15 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
-      <c r="H2">
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
@@ -8132,66 +8002,45 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
       <c r="M4">
         <v>1</v>
       </c>
@@ -8201,40 +8050,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -8242,40 +8091,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>8</v>
       </c>
-      <c r="C6">
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
         <v>7</v>
       </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>14</v>
-      </c>
-      <c r="F6">
-        <v>23</v>
-      </c>
-      <c r="G6">
-        <v>14</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>25</v>
-      </c>
       <c r="L6">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -8285,7 +8134,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -8300,9 +8149,10 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8325,152 +8175,188 @@
         <v>2020</v>
       </c>
       <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="J1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="K1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="L1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>21</v>
+      </c>
+      <c r="G5">
+        <v>13</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
         <v>7</v>
       </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
       <c r="J5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>11</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>19</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -8733,6 +8619,201 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8951,7 +9032,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9142,7 +9223,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9356,7 +9437,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9528,7 +9609,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9776,196 +9857,6 @@
       </c>
       <c r="M7">
         <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -10039,59 +9930,44 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
       <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
       </c>
       <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="M3">
         <v>2</v>
       </c>
     </row>
@@ -10099,7 +9975,7 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
@@ -10107,41 +9983,29 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>13</v>
-      </c>
       <c r="C5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>1</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10149,40 +10013,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -10255,35 +10119,32 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>2</v>
+      <c r="H2">
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10291,36 +10152,27 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>6</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
         <v>2</v>
       </c>
     </row>
@@ -10328,20 +10180,8 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="C4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -10349,40 +10189,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G5">
         <v>6</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10390,40 +10230,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -10497,19 +10337,31 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
       <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -10520,19 +10372,22 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -10541,21 +10396,33 @@
         <v>2</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
       <c r="L4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -10563,40 +10430,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>7</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10604,40 +10471,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>15</v>
+      </c>
+      <c r="G6">
+        <v>12</v>
+      </c>
+      <c r="H6">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>18</v>
+      </c>
+      <c r="J6">
+        <v>13</v>
+      </c>
+      <c r="K6">
+        <v>19</v>
+      </c>
+      <c r="L6">
+        <v>17</v>
+      </c>
+      <c r="M6">
         <v>9</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -10710,68 +10577,65 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="J2">
         <v>2</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -10780,22 +10644,28 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -10805,6 +10675,9 @@
       </c>
       <c r="L5">
         <v>1</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10812,40 +10685,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
         <v>8</v>
       </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>9</v>
-      </c>
       <c r="H6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>2</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -11113,6 +10986,214 @@
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11227,7 +11308,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11390,7 +11471,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11555,7 +11636,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11772,7 +11853,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11978,7 +12059,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12201,7 +12282,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12402,7 +12483,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12625,7 +12706,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12689,208 +12770,6 @@
       </c>
       <c r="D5">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>7</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>8</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -13085,6 +12964,208 @@
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>8</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -13192,7 +13273,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13240,7 +13321,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13463,7 +13544,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13516,7 +13597,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13670,7 +13751,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13813,7 +13894,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13901,7 +13982,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14077,7 +14158,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14201,167 +14282,6 @@
       </c>
       <c r="J5">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -14606,25 +14526,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E1" s="1">
         <v>2019</v>
       </c>
       <c r="F1" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="G1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H1" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="I1" s="1">
         <v>2024</v>
@@ -14640,13 +14560,10 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="K2">
         <v>1</v>
       </c>
     </row>
@@ -14654,13 +14571,16 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
         <v>1</v>
       </c>
       <c r="K3">
@@ -14680,27 +14600,27 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
         <v>1</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -14709,31 +14629,31 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>2</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6">
         <v>4</v>
@@ -14745,6 +14665,167 @@
 </file>
 
 <file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14955,7 +15036,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15082,7 +15163,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15236,7 +15317,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15407,7 +15488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15545,7 +15626,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15695,7 +15776,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15917,7 +15998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16020,82 +16101,6 @@
         <v>2</v>
       </c>
       <c r="H5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
         <v>1</v>
       </c>
     </row>
@@ -16341,6 +16346,82 @@
 
 <file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -16494,7 +16575,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16660,7 +16741,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16831,223 +16912,6 @@
         <v>5</v>
       </c>
       <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>7</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
-      <c r="M6">
         <v>1</v>
       </c>
     </row>
@@ -17121,47 +16985,68 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
       <c r="J2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>1</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -17173,25 +17058,34 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -17202,37 +17096,37 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>3</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
         <v>7</v>
       </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
       <c r="L6">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -17244,6 +17138,193 @@
 </file>
 
 <file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17402,7 +17483,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17503,7 +17584,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17620,7 +17701,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17676,117 +17757,6 @@
       </c>
       <c r="D4">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -18011,6 +17981,117 @@
 
 <file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -18103,7 +18184,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18166,7 +18247,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18249,7 +18330,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18345,7 +18426,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18448,7 +18529,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18534,7 +18615,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18592,7 +18673,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18723,7 +18804,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18791,62 +18872,6 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
         <v>1</v>
       </c>
     </row>
@@ -19076,7 +19101,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C1" s="1">
         <v>2023</v>
@@ -19084,9 +19109,9 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="B2">
         <v>1</v>
       </c>
     </row>
@@ -19095,6 +19120,9 @@
         <v>5</v>
       </c>
       <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
         <v>1</v>
       </c>
     </row>
@@ -19103,7 +19131,7 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -19115,6 +19143,59 @@
 </file>
 
 <file path=xl/worksheets/sheet91.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19175,7 +19256,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet93.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19213,7 +19294,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet93.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet94.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19271,7 +19352,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet94.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet95.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19316,69 +19397,6 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet95.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
         <v>1</v>
       </c>
     </row>

--- a/output/cta-violent-crime-ytd.xlsx
+++ b/output/cta-violent-crime-ytd.xlsx
@@ -9,27 +9,27 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Austin" sheetId="3" r:id="rId3"/>
-    <sheet name="Roseland" sheetId="4" r:id="rId4"/>
-    <sheet name="Albany Park" sheetId="5" r:id="rId5"/>
-    <sheet name="Woodlawn" sheetId="6" r:id="rId6"/>
-    <sheet name="North Lawndale" sheetId="7" r:id="rId7"/>
-    <sheet name="South Shore" sheetId="8" r:id="rId8"/>
-    <sheet name="Old Town" sheetId="9" r:id="rId9"/>
-    <sheet name="Loop" sheetId="10" r:id="rId10"/>
-    <sheet name="O'Hare" sheetId="11" r:id="rId11"/>
-    <sheet name="Near South Side" sheetId="12" r:id="rId12"/>
-    <sheet name="Grand Crossing" sheetId="13" r:id="rId13"/>
-    <sheet name="Avondale" sheetId="14" r:id="rId14"/>
-    <sheet name="Rush &amp; Division" sheetId="15" r:id="rId15"/>
-    <sheet name="Oakland" sheetId="16" r:id="rId16"/>
-    <sheet name="Chatham" sheetId="17" r:id="rId17"/>
-    <sheet name="New City" sheetId="18" r:id="rId18"/>
-    <sheet name="Belmont Cragin" sheetId="19" r:id="rId19"/>
-    <sheet name="West Loop" sheetId="20" r:id="rId20"/>
-    <sheet name="Uptown" sheetId="21" r:id="rId21"/>
-    <sheet name="Hegewisch" sheetId="22" r:id="rId22"/>
-    <sheet name="Lake View" sheetId="23" r:id="rId23"/>
+    <sheet name="Lake View" sheetId="3" r:id="rId3"/>
+    <sheet name="Austin" sheetId="4" r:id="rId4"/>
+    <sheet name="Roseland" sheetId="5" r:id="rId5"/>
+    <sheet name="Albany Park" sheetId="6" r:id="rId6"/>
+    <sheet name="Woodlawn" sheetId="7" r:id="rId7"/>
+    <sheet name="North Lawndale" sheetId="8" r:id="rId8"/>
+    <sheet name="South Shore" sheetId="9" r:id="rId9"/>
+    <sheet name="Old Town" sheetId="10" r:id="rId10"/>
+    <sheet name="Loop" sheetId="11" r:id="rId11"/>
+    <sheet name="O'Hare" sheetId="12" r:id="rId12"/>
+    <sheet name="Near South Side" sheetId="13" r:id="rId13"/>
+    <sheet name="Grand Crossing" sheetId="14" r:id="rId14"/>
+    <sheet name="Avondale" sheetId="15" r:id="rId15"/>
+    <sheet name="Rush &amp; Division" sheetId="16" r:id="rId16"/>
+    <sheet name="Oakland" sheetId="17" r:id="rId17"/>
+    <sheet name="Chatham" sheetId="18" r:id="rId18"/>
+    <sheet name="New City" sheetId="19" r:id="rId19"/>
+    <sheet name="Belmont Cragin" sheetId="20" r:id="rId20"/>
+    <sheet name="West Loop" sheetId="21" r:id="rId21"/>
+    <sheet name="Uptown" sheetId="22" r:id="rId22"/>
+    <sheet name="Hegewisch" sheetId="23" r:id="rId23"/>
     <sheet name="Grand Boulevard" sheetId="24" r:id="rId24"/>
     <sheet name="West Town" sheetId="25" r:id="rId25"/>
     <sheet name="Englewood" sheetId="26" r:id="rId26"/>
@@ -98,12 +98,12 @@
     <sheet name="Galewood" sheetId="89" r:id="rId89"/>
     <sheet name="Gold Coast" sheetId="90" r:id="rId90"/>
     <sheet name="Mount Greenwood" sheetId="91" r:id="rId91"/>
-    <sheet name="West Lawn" sheetId="92" r:id="rId92"/>
-    <sheet name="Boystown" sheetId="93" r:id="rId93"/>
-    <sheet name="East Village" sheetId="94" r:id="rId94"/>
-    <sheet name="Dunning" sheetId="95" r:id="rId95"/>
-    <sheet name="Andersonville" sheetId="96" r:id="rId96"/>
-    <sheet name="Garfield Ridge" sheetId="97" r:id="rId97"/>
+    <sheet name="Garfield Ridge" sheetId="92" r:id="rId92"/>
+    <sheet name="West Lawn" sheetId="93" r:id="rId93"/>
+    <sheet name="Boystown" sheetId="94" r:id="rId94"/>
+    <sheet name="East Village" sheetId="95" r:id="rId95"/>
+    <sheet name="Dunning" sheetId="96" r:id="rId96"/>
+    <sheet name="Andersonville" sheetId="97" r:id="rId97"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -862,7 +862,7 @@
         <v>50</v>
       </c>
       <c r="D2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E2">
         <v>52</v>
@@ -874,16 +874,16 @@
         <v>66</v>
       </c>
       <c r="H2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J2">
         <v>88</v>
       </c>
       <c r="K2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L2">
         <v>105</v>
@@ -897,7 +897,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3">
         <v>65</v>
@@ -906,28 +906,28 @@
         <v>100</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F3">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G3">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H3">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I3">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K3">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L3">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M3">
         <v>153</v>
@@ -994,7 +994,7 @@
         <v>2</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5">
         <v>5</v>
@@ -1017,40 +1017,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C6">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D6">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E6">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F6">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G6">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H6">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I6">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J6">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K6">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="L6">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="M6">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1058,40 +1058,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C7">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D7">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E7">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F7">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="G7">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="H7">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="I7">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="J7">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K7">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="L7">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="M7">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -1100,6 +1100,212 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>9</v>
+      </c>
+      <c r="F4">
+        <v>14</v>
+      </c>
+      <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="I4">
+        <v>14</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>14</v>
+      </c>
+      <c r="L4">
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>19</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>9</v>
+      </c>
+      <c r="I5">
+        <v>16</v>
+      </c>
+      <c r="J5">
+        <v>7</v>
+      </c>
+      <c r="K5">
+        <v>18</v>
+      </c>
+      <c r="L5">
+        <v>7</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1183,7 +1389,7 @@
         <v>4</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2">
         <v>10</v>
@@ -1218,7 +1424,7 @@
         <v>9</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>14</v>
@@ -1278,6 +1484,9 @@
       <c r="G5">
         <v>1</v>
       </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
       <c r="J5">
         <v>2</v>
       </c>
@@ -1299,13 +1508,13 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6">
         <v>50</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G6">
         <v>45</v>
@@ -1314,7 +1523,7 @@
         <v>46</v>
       </c>
       <c r="I6">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J6">
         <v>46</v>
@@ -1323,7 +1532,7 @@
         <v>39</v>
       </c>
       <c r="L6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M6">
         <v>21</v>
@@ -1340,22 +1549,22 @@
         <v>42</v>
       </c>
       <c r="D7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7">
         <v>61</v>
       </c>
       <c r="F7">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>64</v>
       </c>
       <c r="H7">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J7">
         <v>89</v>
@@ -1364,7 +1573,7 @@
         <v>74</v>
       </c>
       <c r="L7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M7">
         <v>45</v>
@@ -1375,7 +1584,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1530,216 +1739,6 @@
       </c>
       <c r="J7">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>12</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>3</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1812,98 +1811,53 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
       <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>6</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -1911,19 +1865,7 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -1932,40 +1874,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1973,40 +1915,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="J7">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2016,7 +1958,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -2080,135 +2022,200 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
       <c r="E3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="K3">
+        <v>11</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K4">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
       <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>23</v>
+      </c>
+      <c r="C7">
+        <v>30</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>37</v>
+      </c>
+      <c r="G7">
+        <v>21</v>
+      </c>
+      <c r="H7">
+        <v>32</v>
+      </c>
+      <c r="I7">
+        <v>31</v>
+      </c>
+      <c r="J7">
+        <v>31</v>
+      </c>
+      <c r="K7">
+        <v>49</v>
+      </c>
+      <c r="L7">
+        <v>47</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2281,59 +2288,59 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
         <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -2342,40 +2349,34 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2383,40 +2384,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>3</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2425,6 +2426,214 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>13</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2512,7 +2721,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2747,7 +2956,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2915,138 +3124,6 @@
       </c>
       <c r="L5">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3175,7 +3252,7 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -3192,7 +3269,7 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>7</v>
@@ -3274,7 +3351,7 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7">
         <v>6</v>
@@ -3309,28 +3386,28 @@
         <v>23</v>
       </c>
       <c r="E8">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F8">
         <v>35</v>
       </c>
       <c r="G8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H8">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I8">
         <v>22</v>
       </c>
       <c r="J8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M8">
         <v>37</v>
@@ -3538,7 +3615,7 @@
         <v>4</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16">
         <v>2</v>
@@ -3578,7 +3655,7 @@
         <v>3</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -3875,7 +3952,7 @@
         <v>9</v>
       </c>
       <c r="K27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>7</v>
@@ -3889,7 +3966,7 @@
         <v>34</v>
       </c>
       <c r="B28">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C28">
         <v>39</v>
@@ -3898,19 +3975,19 @@
         <v>36</v>
       </c>
       <c r="E28">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F28">
         <v>39</v>
       </c>
       <c r="G28">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H28">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I28">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J28">
         <v>21</v>
@@ -4069,6 +4146,9 @@
       <c r="D33">
         <v>1</v>
       </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="2" t="s">
@@ -4127,7 +4207,7 @@
         <v>42</v>
       </c>
       <c r="B36">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C36">
         <v>30</v>
@@ -4154,10 +4234,10 @@
         <v>31</v>
       </c>
       <c r="K36">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L36">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M36">
         <v>27</v>
@@ -4254,7 +4334,7 @@
         <v>5</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -4269,13 +4349,13 @@
         <v>5</v>
       </c>
       <c r="H41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I41">
         <v>6</v>
       </c>
       <c r="J41">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K41">
         <v>11</v>
@@ -4497,7 +4577,7 @@
         <v>17</v>
       </c>
       <c r="M47">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -4590,7 +4670,7 @@
         <v>10</v>
       </c>
       <c r="E50">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F50">
         <v>23</v>
@@ -4643,7 +4723,7 @@
         <v>1</v>
       </c>
       <c r="K51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L51">
         <v>2</v>
@@ -4681,7 +4761,7 @@
         <v>4</v>
       </c>
       <c r="J52">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K52">
         <v>7</v>
@@ -4704,22 +4784,22 @@
         <v>42</v>
       </c>
       <c r="D53">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E53">
         <v>61</v>
       </c>
       <c r="F53">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G53">
         <v>64</v>
       </c>
       <c r="H53">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I53">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J53">
         <v>89</v>
@@ -4728,7 +4808,7 @@
         <v>74</v>
       </c>
       <c r="L53">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M53">
         <v>45</v>
@@ -5049,7 +5129,7 @@
         <v>8</v>
       </c>
       <c r="F65">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G65">
         <v>16</v>
@@ -5064,7 +5144,7 @@
         <v>5</v>
       </c>
       <c r="K65">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L65">
         <v>13</v>
@@ -5194,7 +5274,7 @@
         <v>1</v>
       </c>
       <c r="C70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D70">
         <v>7</v>
@@ -5218,7 +5298,7 @@
         <v>7</v>
       </c>
       <c r="K70">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L70">
         <v>7</v>
@@ -5240,6 +5320,9 @@
       <c r="E71">
         <v>1</v>
       </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
       <c r="J71">
         <v>3</v>
       </c>
@@ -5258,7 +5341,7 @@
         <v>3</v>
       </c>
       <c r="D72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -5430,7 +5513,7 @@
         <v>20</v>
       </c>
       <c r="C77">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D77">
         <v>11</v>
@@ -5448,7 +5531,7 @@
         <v>21</v>
       </c>
       <c r="I77">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J77">
         <v>25</v>
@@ -5457,7 +5540,7 @@
         <v>21</v>
       </c>
       <c r="L77">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M77">
         <v>12</v>
@@ -5536,7 +5619,7 @@
         <v>4</v>
       </c>
       <c r="K79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L79">
         <v>9</v>
@@ -5556,10 +5639,10 @@
         <v>7</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F80">
         <v>4</v>
@@ -5792,7 +5875,7 @@
         <v>9</v>
       </c>
       <c r="D87">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E87">
         <v>6</v>
@@ -5941,7 +6024,7 @@
         <v>3</v>
       </c>
       <c r="K91">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L91">
         <v>9</v>
@@ -5976,7 +6059,7 @@
         <v>2</v>
       </c>
       <c r="I92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J92">
         <v>4</v>
@@ -6016,7 +6099,7 @@
         <v>100</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C94">
         <v>4</v>
@@ -6160,7 +6243,7 @@
         <v>3</v>
       </c>
       <c r="K97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L97">
         <v>1</v>
@@ -6174,40 +6257,40 @@
         <v>6</v>
       </c>
       <c r="B98">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C98">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D98">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E98">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F98">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="G98">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="H98">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="I98">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="J98">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K98">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="L98">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="M98">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -6316,6 +6399,138 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6430,7 +6645,7 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3">
         <v>3</v>
@@ -6528,7 +6743,7 @@
         <v>3</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L7">
         <v>9</v>
@@ -6542,7 +6757,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6774,7 +6989,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6845,253 +7060,6 @@
       </c>
       <c r="E5">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>6</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>8</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>16</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>20</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>11</v>
-      </c>
-      <c r="F6">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>17</v>
-      </c>
-      <c r="I6">
-        <v>20</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
-      </c>
-      <c r="K6">
-        <v>18</v>
-      </c>
-      <c r="L6">
-        <v>17</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -7439,7 +7407,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -7480,7 +7448,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -7622,7 +7590,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -7631,7 +7599,7 @@
         <v>14</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
         <v>6</v>
@@ -7640,10 +7608,10 @@
         <v>4</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -7709,7 +7677,7 @@
         <v>28</v>
       </c>
       <c r="G6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H6">
         <v>22</v>
@@ -7735,7 +7703,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>39</v>
@@ -7744,19 +7712,19 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F7">
         <v>39</v>
       </c>
       <c r="G7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J7">
         <v>21</v>
@@ -8077,7 +8045,7 @@
         <v>5</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>4</v>
@@ -8118,7 +8086,7 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -8291,7 +8259,7 @@
         <v>8</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5">
         <v>21</v>
@@ -8332,7 +8300,7 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6">
         <v>23</v>
@@ -8429,41 +8397,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
       <c r="C2">
         <v>4</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8471,59 +8436,59 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>4</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
+        <v>6</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
         <v>7</v>
       </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>9</v>
-      </c>
       <c r="M3">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
       </c>
       <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
         <v>2</v>
       </c>
       <c r="M4">
@@ -8534,41 +8499,38 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>13</v>
-      </c>
       <c r="C5">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="G5">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H5">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>16</v>
       </c>
       <c r="J5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -8576,40 +8538,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H6">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="I6">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J6">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="L6">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="M6">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -8919,13 +8881,13 @@
         <v>2</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3">
         <v>2</v>
@@ -8953,7 +8915,7 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -8994,7 +8956,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -9009,13 +8971,13 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>6</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K6">
         <v>11</v>
@@ -9332,6 +9294,9 @@
       <c r="J3">
         <v>1</v>
       </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
       <c r="L3">
         <v>5</v>
       </c>
@@ -9423,7 +9388,7 @@
         <v>4</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -10001,6 +9966,9 @@
       <c r="J5">
         <v>1</v>
       </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
       <c r="L5">
         <v>1</v>
       </c>
@@ -10040,7 +10008,7 @@
         <v>3</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -10164,7 +10132,7 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -10245,7 +10213,7 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -10728,7 +10696,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10792,40 +10760,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>2</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10836,147 +10804,142 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
         <v>7</v>
       </c>
-      <c r="J3">
-        <v>8</v>
-      </c>
       <c r="K3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="I4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>25</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="E5">
+        <v>26</v>
+      </c>
+      <c r="F5">
+        <v>24</v>
+      </c>
+      <c r="G5">
+        <v>19</v>
+      </c>
+      <c r="H5">
+        <v>37</v>
+      </c>
+      <c r="I5">
+        <v>16</v>
+      </c>
+      <c r="J5">
+        <v>17</v>
+      </c>
+      <c r="K5">
+        <v>19</v>
+      </c>
+      <c r="L5">
+        <v>11</v>
+      </c>
+      <c r="M5">
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H6">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="I6">
         <v>22</v>
       </c>
       <c r="J6">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="K6">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="L6">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="M6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>20</v>
-      </c>
-      <c r="C7">
-        <v>19</v>
-      </c>
-      <c r="D7">
-        <v>11</v>
-      </c>
-      <c r="E7">
-        <v>21</v>
-      </c>
-      <c r="F7">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>18</v>
-      </c>
-      <c r="H7">
-        <v>21</v>
-      </c>
-      <c r="I7">
-        <v>35</v>
-      </c>
-      <c r="J7">
-        <v>25</v>
-      </c>
-      <c r="K7">
-        <v>21</v>
-      </c>
-      <c r="L7">
-        <v>21</v>
-      </c>
-      <c r="M7">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -11389,6 +11352,9 @@
       <c r="E3">
         <v>1</v>
       </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
       <c r="L3">
         <v>1</v>
       </c>
@@ -11445,7 +11411,7 @@
         <v>3</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -11951,7 +11917,7 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -11986,7 +11952,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -12024,10 +11990,10 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -12206,7 +12172,7 @@
         <v>3</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -12247,7 +12213,7 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>7</v>
@@ -12779,7 +12745,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12793,9 +12759,11 @@
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12812,149 +12780,220 @@
         <v>2018</v>
       </c>
       <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
         <v>2020</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="H1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="I1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="J1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="K1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>4</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>14</v>
+      </c>
+      <c r="L6">
+        <v>16</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>11</v>
+      </c>
+      <c r="E7">
+        <v>21</v>
+      </c>
+      <c r="F7">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>21</v>
+      </c>
+      <c r="I7">
+        <v>36</v>
+      </c>
+      <c r="J7">
+        <v>25</v>
+      </c>
+      <c r="K7">
+        <v>21</v>
+      </c>
+      <c r="L7">
+        <v>22</v>
+      </c>
+      <c r="M7">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -14099,6 +14138,9 @@
       <c r="H4">
         <v>2</v>
       </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
       <c r="J4">
         <v>1</v>
       </c>
@@ -14138,7 +14180,7 @@
         <v>2</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -14291,7 +14333,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -14305,11 +14347,9 @@
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14326,114 +14366,102 @@
         <v>2018</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G1" s="1">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="E2">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
       <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -14444,58 +14472,43 @@
       <c r="I5">
         <v>4</v>
       </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
       <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
         <v>8</v>
       </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
       <c r="I6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -14730,6 +14743,9 @@
       <c r="H2">
         <v>1</v>
       </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
@@ -14811,7 +14827,7 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6">
         <v>2</v>
@@ -16061,7 +16077,7 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -16095,7 +16111,7 @@
         <v>4</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -16175,40 +16191,19 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16216,43 +16211,43 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>2</v>
+      <c r="D3">
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>4</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
       <c r="H4">
         <v>1</v>
       </c>
@@ -16262,40 +16257,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -16303,40 +16298,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>8</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -16639,6 +16634,9 @@
       <c r="B2">
         <v>1</v>
       </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
       <c r="E2">
         <v>1</v>
       </c>
@@ -16709,7 +16707,7 @@
         <v>9</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>6</v>
@@ -16847,7 +16845,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -16885,7 +16883,7 @@
         <v>3</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -17027,7 +17025,7 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -17120,7 +17118,7 @@
         <v>4</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>7</v>
@@ -17527,6 +17525,9 @@
       <c r="D2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
@@ -17573,7 +17574,7 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -17766,10 +17767,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -17830,28 +17831,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17859,34 +17872,34 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
       <c r="H3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M3">
         <v>3</v>
@@ -17894,83 +17907,91 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>9</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>7</v>
-      </c>
-      <c r="J4">
-        <v>9</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>13</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E5">
         <v>5</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G5">
+        <v>11</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>14</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
         <v>8</v>
       </c>
-      <c r="H5">
-        <v>8</v>
-      </c>
-      <c r="I5">
-        <v>11</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-      <c r="M5">
+      <c r="F6">
+        <v>25</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>19</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>12</v>
+      </c>
+      <c r="L6">
+        <v>13</v>
+      </c>
+      <c r="M6">
         <v>8</v>
       </c>
     </row>
@@ -18092,7 +18113,7 @@
 
 <file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -18101,9 +18122,10 @@
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
     <col min="5" max="5" width="4.7109375" customWidth="1"/>
     <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -18117,35 +18139,41 @@
         <v>2018</v>
       </c>
       <c r="E1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="F1" s="1">
         <v>2023</v>
       </c>
-      <c r="F1" s="1">
+      <c r="G1" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
       <c r="F3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -18155,11 +18183,11 @@
       <c r="C4">
         <v>2</v>
       </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -18173,9 +18201,12 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
     </row>
@@ -18945,26 +18976,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>2</v>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="I2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18972,72 +19006,78 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
       <c r="C4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4">
         <v>9</v>
       </c>
-      <c r="F4">
-        <v>14</v>
-      </c>
-      <c r="G4">
-        <v>9</v>
-      </c>
-      <c r="H4">
-        <v>6</v>
-      </c>
-      <c r="I4">
-        <v>14</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
       <c r="K4">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -19045,40 +19085,40 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
         <v>10</v>
       </c>
-      <c r="F5">
-        <v>19</v>
-      </c>
       <c r="G5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -19197,6 +19237,54 @@
 
 <file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet93.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -19256,7 +19344,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet93.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet94.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19294,7 +19382,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet94.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet95.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19352,7 +19440,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet95.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet96.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19405,7 +19493,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet96.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet97.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19441,42 +19529,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet97.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/output/cta-violent-crime-ytd.xlsx
+++ b/output/cta-violent-crime-ytd.xlsx
@@ -9,65 +9,65 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Lake View" sheetId="3" r:id="rId3"/>
-    <sheet name="Austin" sheetId="4" r:id="rId4"/>
-    <sheet name="Roseland" sheetId="5" r:id="rId5"/>
-    <sheet name="Albany Park" sheetId="6" r:id="rId6"/>
-    <sheet name="Woodlawn" sheetId="7" r:id="rId7"/>
-    <sheet name="North Lawndale" sheetId="8" r:id="rId8"/>
-    <sheet name="South Shore" sheetId="9" r:id="rId9"/>
-    <sheet name="Old Town" sheetId="10" r:id="rId10"/>
-    <sheet name="Loop" sheetId="11" r:id="rId11"/>
-    <sheet name="O'Hare" sheetId="12" r:id="rId12"/>
-    <sheet name="Near South Side" sheetId="13" r:id="rId13"/>
-    <sheet name="Grand Crossing" sheetId="14" r:id="rId14"/>
-    <sheet name="Avondale" sheetId="15" r:id="rId15"/>
-    <sheet name="Rush &amp; Division" sheetId="16" r:id="rId16"/>
-    <sheet name="Oakland" sheetId="17" r:id="rId17"/>
-    <sheet name="Chatham" sheetId="18" r:id="rId18"/>
-    <sheet name="New City" sheetId="19" r:id="rId19"/>
-    <sheet name="Belmont Cragin" sheetId="20" r:id="rId20"/>
-    <sheet name="West Loop" sheetId="21" r:id="rId21"/>
-    <sheet name="Uptown" sheetId="22" r:id="rId22"/>
-    <sheet name="Hegewisch" sheetId="23" r:id="rId23"/>
-    <sheet name="Grand Boulevard" sheetId="24" r:id="rId24"/>
-    <sheet name="West Town" sheetId="25" r:id="rId25"/>
-    <sheet name="Englewood" sheetId="26" r:id="rId26"/>
-    <sheet name="Greektown" sheetId="27" r:id="rId27"/>
-    <sheet name="Edgewater" sheetId="28" r:id="rId28"/>
-    <sheet name="Little Italy, UIC" sheetId="29" r:id="rId29"/>
-    <sheet name="Gage Park" sheetId="30" r:id="rId30"/>
-    <sheet name="Humboldt Park" sheetId="31" r:id="rId31"/>
-    <sheet name="Lower West Side" sheetId="32" r:id="rId32"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="33" r:id="rId33"/>
-    <sheet name="Norwood Park" sheetId="34" r:id="rId34"/>
-    <sheet name="Garfield Park" sheetId="35" r:id="rId35"/>
-    <sheet name="Wrigleyville" sheetId="36" r:id="rId36"/>
-    <sheet name="Auburn Gresham" sheetId="37" r:id="rId37"/>
-    <sheet name="Rogers Park" sheetId="38" r:id="rId38"/>
-    <sheet name="Washington Park" sheetId="39" r:id="rId39"/>
-    <sheet name="Chicago Lawn" sheetId="40" r:id="rId40"/>
-    <sheet name="Kenwood" sheetId="41" r:id="rId41"/>
-    <sheet name="Calumet Heights" sheetId="42" r:id="rId42"/>
-    <sheet name="Hyde Park" sheetId="43" r:id="rId43"/>
-    <sheet name="Fuller Park" sheetId="44" r:id="rId44"/>
-    <sheet name="South Chicago" sheetId="45" r:id="rId45"/>
-    <sheet name="Armour Square" sheetId="46" r:id="rId46"/>
-    <sheet name="Douglas" sheetId="47" r:id="rId47"/>
-    <sheet name="United Center" sheetId="48" r:id="rId48"/>
-    <sheet name="Grant Park" sheetId="49" r:id="rId49"/>
-    <sheet name="Jefferson Park" sheetId="50" r:id="rId50"/>
-    <sheet name="Streeterville" sheetId="51" r:id="rId51"/>
-    <sheet name="Millenium Park" sheetId="52" r:id="rId52"/>
-    <sheet name="River North" sheetId="53" r:id="rId53"/>
-    <sheet name="Beverly" sheetId="54" r:id="rId54"/>
-    <sheet name="South Deering" sheetId="55" r:id="rId55"/>
-    <sheet name="West Elsdon" sheetId="56" r:id="rId56"/>
-    <sheet name="Pullman" sheetId="57" r:id="rId57"/>
-    <sheet name="West Pullman" sheetId="58" r:id="rId58"/>
-    <sheet name="Morgan Park" sheetId="59" r:id="rId59"/>
-    <sheet name="Wicker Park" sheetId="60" r:id="rId60"/>
-    <sheet name="Little Village" sheetId="61" r:id="rId61"/>
+    <sheet name="North Lawndale" sheetId="3" r:id="rId3"/>
+    <sheet name="Little Village" sheetId="4" r:id="rId4"/>
+    <sheet name="Lake View" sheetId="5" r:id="rId5"/>
+    <sheet name="Austin" sheetId="6" r:id="rId6"/>
+    <sheet name="Roseland" sheetId="7" r:id="rId7"/>
+    <sheet name="Albany Park" sheetId="8" r:id="rId8"/>
+    <sheet name="Woodlawn" sheetId="9" r:id="rId9"/>
+    <sheet name="South Shore" sheetId="10" r:id="rId10"/>
+    <sheet name="Old Town" sheetId="11" r:id="rId11"/>
+    <sheet name="Loop" sheetId="12" r:id="rId12"/>
+    <sheet name="O'Hare" sheetId="13" r:id="rId13"/>
+    <sheet name="Near South Side" sheetId="14" r:id="rId14"/>
+    <sheet name="Grand Crossing" sheetId="15" r:id="rId15"/>
+    <sheet name="Avondale" sheetId="16" r:id="rId16"/>
+    <sheet name="Rush &amp; Division" sheetId="17" r:id="rId17"/>
+    <sheet name="Oakland" sheetId="18" r:id="rId18"/>
+    <sheet name="Chatham" sheetId="19" r:id="rId19"/>
+    <sheet name="New City" sheetId="20" r:id="rId20"/>
+    <sheet name="Belmont Cragin" sheetId="21" r:id="rId21"/>
+    <sheet name="West Loop" sheetId="22" r:id="rId22"/>
+    <sheet name="Uptown" sheetId="23" r:id="rId23"/>
+    <sheet name="Hegewisch" sheetId="24" r:id="rId24"/>
+    <sheet name="Grand Boulevard" sheetId="25" r:id="rId25"/>
+    <sheet name="West Town" sheetId="26" r:id="rId26"/>
+    <sheet name="Englewood" sheetId="27" r:id="rId27"/>
+    <sheet name="Greektown" sheetId="28" r:id="rId28"/>
+    <sheet name="Edgewater" sheetId="29" r:id="rId29"/>
+    <sheet name="Little Italy, UIC" sheetId="30" r:id="rId30"/>
+    <sheet name="Gage Park" sheetId="31" r:id="rId31"/>
+    <sheet name="Humboldt Park" sheetId="32" r:id="rId32"/>
+    <sheet name="Lower West Side" sheetId="33" r:id="rId33"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="34" r:id="rId34"/>
+    <sheet name="Norwood Park" sheetId="35" r:id="rId35"/>
+    <sheet name="Garfield Park" sheetId="36" r:id="rId36"/>
+    <sheet name="Wrigleyville" sheetId="37" r:id="rId37"/>
+    <sheet name="Auburn Gresham" sheetId="38" r:id="rId38"/>
+    <sheet name="Rogers Park" sheetId="39" r:id="rId39"/>
+    <sheet name="Washington Park" sheetId="40" r:id="rId40"/>
+    <sheet name="Chicago Lawn" sheetId="41" r:id="rId41"/>
+    <sheet name="Kenwood" sheetId="42" r:id="rId42"/>
+    <sheet name="Calumet Heights" sheetId="43" r:id="rId43"/>
+    <sheet name="Hyde Park" sheetId="44" r:id="rId44"/>
+    <sheet name="Fuller Park" sheetId="45" r:id="rId45"/>
+    <sheet name="South Chicago" sheetId="46" r:id="rId46"/>
+    <sheet name="Armour Square" sheetId="47" r:id="rId47"/>
+    <sheet name="Douglas" sheetId="48" r:id="rId48"/>
+    <sheet name="United Center" sheetId="49" r:id="rId49"/>
+    <sheet name="Grant Park" sheetId="50" r:id="rId50"/>
+    <sheet name="Jefferson Park" sheetId="51" r:id="rId51"/>
+    <sheet name="Streeterville" sheetId="52" r:id="rId52"/>
+    <sheet name="Millenium Park" sheetId="53" r:id="rId53"/>
+    <sheet name="River North" sheetId="54" r:id="rId54"/>
+    <sheet name="Beverly" sheetId="55" r:id="rId55"/>
+    <sheet name="South Deering" sheetId="56" r:id="rId56"/>
+    <sheet name="West Elsdon" sheetId="57" r:id="rId57"/>
+    <sheet name="Pullman" sheetId="58" r:id="rId58"/>
+    <sheet name="West Pullman" sheetId="59" r:id="rId59"/>
+    <sheet name="Morgan Park" sheetId="60" r:id="rId60"/>
+    <sheet name="Wicker Park" sheetId="61" r:id="rId61"/>
     <sheet name="Irving Park" sheetId="62" r:id="rId62"/>
     <sheet name="Jackson Park" sheetId="63" r:id="rId63"/>
     <sheet name="Brighton Park" sheetId="64" r:id="rId64"/>
@@ -868,7 +868,7 @@
         <v>52</v>
       </c>
       <c r="F2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>66</v>
@@ -883,13 +883,13 @@
         <v>88</v>
       </c>
       <c r="K2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L2">
         <v>105</v>
       </c>
       <c r="M2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -903,34 +903,34 @@
         <v>65</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E3">
         <v>102</v>
       </c>
       <c r="F3">
+        <v>99</v>
+      </c>
+      <c r="G3">
         <v>98</v>
-      </c>
-      <c r="G3">
-        <v>97</v>
       </c>
       <c r="H3">
         <v>103</v>
       </c>
       <c r="I3">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J3">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L3">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M3">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1020,34 +1020,34 @@
         <v>285</v>
       </c>
       <c r="C6">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D6">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E6">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F6">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="G6">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H6">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="I6">
         <v>393</v>
       </c>
       <c r="J6">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="K6">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L6">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M6">
         <v>195</v>
@@ -1061,37 +1061,37 @@
         <v>388</v>
       </c>
       <c r="C7">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D7">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E7">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="F7">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="G7">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="H7">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="I7">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="J7">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="K7">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="L7">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="M7">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
@@ -1164,26 +1164,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>2</v>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="I2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1191,72 +1194,78 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
       <c r="C4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4">
         <v>9</v>
       </c>
-      <c r="F4">
-        <v>14</v>
-      </c>
-      <c r="G4">
-        <v>9</v>
-      </c>
-      <c r="H4">
-        <v>6</v>
-      </c>
-      <c r="I4">
-        <v>14</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
       <c r="K4">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1264,40 +1273,40 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
         <v>10</v>
       </c>
-      <c r="F5">
-        <v>19</v>
-      </c>
       <c r="G5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1306,6 +1315,212 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>14</v>
+      </c>
+      <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="I4">
+        <v>14</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>14</v>
+      </c>
+      <c r="L4">
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>19</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>9</v>
+      </c>
+      <c r="I5">
+        <v>16</v>
+      </c>
+      <c r="J5">
+        <v>8</v>
+      </c>
+      <c r="K5">
+        <v>18</v>
+      </c>
+      <c r="L5">
+        <v>7</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1398,7 +1613,7 @@
         <v>15</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2">
         <v>13</v>
@@ -1511,16 +1726,16 @@
         <v>34</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G6">
         <v>45</v>
       </c>
       <c r="H6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I6">
         <v>68</v>
@@ -1552,16 +1767,16 @@
         <v>60</v>
       </c>
       <c r="E7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G7">
         <v>64</v>
       </c>
       <c r="H7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I7">
         <v>107</v>
@@ -1570,7 +1785,7 @@
         <v>89</v>
       </c>
       <c r="K7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L7">
         <v>78</v>
@@ -1584,7 +1799,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1739,216 +1954,6 @@
       </c>
       <c r="J7">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>12</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>3</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2021,98 +2026,53 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
       <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>6</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>11</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -2120,19 +2080,7 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -2141,40 +2089,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2182,40 +2130,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="J7">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2225,7 +2173,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -2289,135 +2237,200 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
       <c r="E3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="K3">
+        <v>11</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K4">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
       <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>23</v>
+      </c>
+      <c r="C7">
+        <v>30</v>
+      </c>
+      <c r="D7">
+        <v>28</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>37</v>
+      </c>
+      <c r="G7">
+        <v>21</v>
+      </c>
+      <c r="H7">
+        <v>32</v>
+      </c>
+      <c r="I7">
+        <v>31</v>
+      </c>
+      <c r="J7">
+        <v>31</v>
+      </c>
+      <c r="K7">
+        <v>49</v>
+      </c>
+      <c r="L7">
+        <v>48</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2490,59 +2503,59 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
         <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -2551,40 +2564,34 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2592,40 +2599,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>3</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2634,6 +2641,214 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>13</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2721,7 +2936,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2796,7 +3011,7 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -2927,7 +3142,7 @@
         <v>12</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6">
         <v>18</v>
@@ -2949,181 +3164,6 @@
       </c>
       <c r="M6">
         <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3360,7 +3400,7 @@
         <v>8</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>7</v>
@@ -3383,10 +3423,10 @@
         <v>34</v>
       </c>
       <c r="D8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F8">
         <v>35</v>
@@ -3395,7 +3435,7 @@
         <v>25</v>
       </c>
       <c r="H8">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I8">
         <v>22</v>
@@ -3693,7 +3733,7 @@
         <v>12</v>
       </c>
       <c r="F19">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G19">
         <v>18</v>
@@ -3978,7 +4018,7 @@
         <v>25</v>
       </c>
       <c r="F28">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G28">
         <v>34</v>
@@ -3993,7 +4033,7 @@
         <v>21</v>
       </c>
       <c r="K28">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L28">
         <v>52</v>
@@ -4063,7 +4103,7 @@
         <v>1</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I30">
         <v>3</v>
@@ -4106,7 +4146,7 @@
         <v>11</v>
       </c>
       <c r="C32">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D32">
         <v>42</v>
@@ -4213,7 +4253,7 @@
         <v>30</v>
       </c>
       <c r="D36">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E36">
         <v>30</v>
@@ -4237,7 +4277,7 @@
         <v>49</v>
       </c>
       <c r="L36">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M36">
         <v>27</v>
@@ -4355,7 +4395,7 @@
         <v>6</v>
       </c>
       <c r="J41">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K41">
         <v>11</v>
@@ -4437,7 +4477,7 @@
         <v>4</v>
       </c>
       <c r="L43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M43">
         <v>3</v>
@@ -4556,7 +4596,7 @@
         <v>11</v>
       </c>
       <c r="F47">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G47">
         <v>16</v>
@@ -4729,7 +4769,7 @@
         <v>2</v>
       </c>
       <c r="M51">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -4787,16 +4827,16 @@
         <v>60</v>
       </c>
       <c r="E53">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F53">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G53">
         <v>64</v>
       </c>
       <c r="H53">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I53">
         <v>107</v>
@@ -4805,7 +4845,7 @@
         <v>89</v>
       </c>
       <c r="K53">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L53">
         <v>78</v>
@@ -4952,7 +4992,7 @@
         <v>1</v>
       </c>
       <c r="J59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K59">
         <v>2</v>
@@ -5068,7 +5108,7 @@
         <v>4</v>
       </c>
       <c r="E63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F63">
         <v>4</v>
@@ -5141,7 +5181,7 @@
         <v>19</v>
       </c>
       <c r="J65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K65">
         <v>12</v>
@@ -5150,7 +5190,7 @@
         <v>13</v>
       </c>
       <c r="M65">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -5280,7 +5320,7 @@
         <v>7</v>
       </c>
       <c r="E70">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F70">
         <v>19</v>
@@ -5295,7 +5335,7 @@
         <v>16</v>
       </c>
       <c r="J70">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K70">
         <v>18</v>
@@ -5362,7 +5402,7 @@
         <v>3</v>
       </c>
       <c r="K72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L72">
         <v>5</v>
@@ -5484,7 +5524,7 @@
         <v>15</v>
       </c>
       <c r="G76">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H76">
         <v>14</v>
@@ -5636,7 +5676,7 @@
         <v>13</v>
       </c>
       <c r="C80">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D80">
         <v>3</v>
@@ -6196,7 +6236,7 @@
         <v>6</v>
       </c>
       <c r="I96">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J96">
         <v>8</v>
@@ -6260,37 +6300,37 @@
         <v>388</v>
       </c>
       <c r="C98">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D98">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E98">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="F98">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="G98">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="H98">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="I98">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="J98">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="K98">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="L98">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="M98">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
@@ -6399,6 +6439,181 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6529,7 +6744,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6757,7 +6972,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6989,7 +7204,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7067,7 +7282,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7275,7 +7490,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7489,7 +7704,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7617,7 +7832,7 @@
         <v>5</v>
       </c>
       <c r="K3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L3">
         <v>14</v>
@@ -7674,7 +7889,7 @@
         <v>17</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G6">
         <v>25</v>
@@ -7689,7 +7904,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L6">
         <v>33</v>
@@ -7715,7 +7930,7 @@
         <v>25</v>
       </c>
       <c r="F7">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7">
         <v>34</v>
@@ -7730,7 +7945,7 @@
         <v>21</v>
       </c>
       <c r="K7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L7">
         <v>52</v>
@@ -7744,7 +7959,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7879,220 +8094,6 @@
       </c>
       <c r="J6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>6</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>7</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>11</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
-      </c>
-      <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -8166,12 +8167,15 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
-      <c r="H2">
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
@@ -8181,66 +8185,45 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
       <c r="M4">
         <v>1</v>
       </c>
@@ -8250,40 +8233,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
         <v>7</v>
       </c>
-      <c r="J5">
-        <v>7</v>
-      </c>
-      <c r="K5">
-        <v>15</v>
-      </c>
       <c r="L5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -8291,40 +8274,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>8</v>
       </c>
-      <c r="C6">
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
         <v>7</v>
       </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>15</v>
-      </c>
-      <c r="F6">
-        <v>23</v>
-      </c>
-      <c r="G6">
-        <v>14</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>25</v>
-      </c>
-      <c r="L6">
-        <v>19</v>
-      </c>
       <c r="M6">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -8397,38 +8380,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L2">
         <v>3</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8436,92 +8422,77 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>3</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
       <c r="H4">
         <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
       <c r="C5">
+        <v>13</v>
+      </c>
+      <c r="D5">
+        <v>16</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>21</v>
+      </c>
+      <c r="G5">
         <v>11</v>
       </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>8</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
       <c r="H5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <v>6</v>
@@ -8538,40 +8509,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="G6">
         <v>16</v>
       </c>
       <c r="H6">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>12</v>
+      </c>
+      <c r="L6">
+        <v>13</v>
+      </c>
+      <c r="M6">
         <v>9</v>
-      </c>
-      <c r="K6">
-        <v>18</v>
-      </c>
-      <c r="L6">
-        <v>17</v>
-      </c>
-      <c r="M6">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -8580,6 +8551,238 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>13</v>
+      </c>
+      <c r="F5">
+        <v>21</v>
+      </c>
+      <c r="G5">
+        <v>13</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>7</v>
+      </c>
+      <c r="K5">
+        <v>15</v>
+      </c>
+      <c r="L5">
+        <v>11</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>15</v>
+      </c>
+      <c r="F6">
+        <v>23</v>
+      </c>
+      <c r="G6">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>10</v>
+      </c>
+      <c r="K6">
+        <v>25</v>
+      </c>
+      <c r="L6">
+        <v>19</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8713,7 +8916,7 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -8751,7 +8954,7 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -8774,7 +8977,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8887,7 +9090,7 @@
         <v>2</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3">
         <v>2</v>
@@ -8977,7 +9180,7 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K6">
         <v>11</v>
@@ -8994,7 +9197,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9185,7 +9388,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9402,7 +9605,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9574,7 +9777,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9750,7 +9953,7 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>30</v>
@@ -9791,7 +9994,7 @@
         <v>11</v>
       </c>
       <c r="C7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7">
         <v>42</v>
@@ -9822,199 +10025,6 @@
       </c>
       <c r="M7">
         <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -10088,59 +10098,44 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
       <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
       </c>
       <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="M3">
         <v>2</v>
       </c>
     </row>
@@ -10148,7 +10143,7 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
@@ -10156,41 +10151,32 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>13</v>
-      </c>
       <c r="C5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>1</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10198,40 +10184,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -10304,35 +10290,32 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>2</v>
+      <c r="H2">
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10340,36 +10323,27 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>6</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
         <v>2</v>
       </c>
     </row>
@@ -10377,20 +10351,8 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="C4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -10398,40 +10360,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G5">
         <v>6</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10439,40 +10401,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -10546,19 +10508,31 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
       <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -10569,19 +10543,22 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -10590,21 +10567,33 @@
         <v>2</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
       <c r="L4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -10612,40 +10601,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>7</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10653,40 +10642,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>15</v>
+      </c>
+      <c r="G6">
+        <v>13</v>
+      </c>
+      <c r="H6">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>18</v>
+      </c>
+      <c r="J6">
+        <v>13</v>
+      </c>
+      <c r="K6">
+        <v>19</v>
+      </c>
+      <c r="L6">
+        <v>17</v>
+      </c>
+      <c r="M6">
         <v>9</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -10696,7 +10685,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10710,11 +10699,9 @@
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10728,218 +10715,131 @@
         <v>2017</v>
       </c>
       <c r="E1" s="1">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G1" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>6</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
       <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>10</v>
-      </c>
-      <c r="M3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>13</v>
-      </c>
-      <c r="C5">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>19</v>
-      </c>
-      <c r="H5">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>19</v>
-      </c>
-      <c r="L5">
-        <v>11</v>
-      </c>
-      <c r="M5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>35</v>
-      </c>
-      <c r="L6">
-        <v>23</v>
-      </c>
-      <c r="M6">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -11012,68 +10912,65 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="J2">
         <v>2</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -11082,22 +10979,28 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -11107,6 +11010,9 @@
       </c>
       <c r="L5">
         <v>1</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -11114,40 +11020,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
         <v>8</v>
       </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>9</v>
-      </c>
       <c r="H6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>2</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -11156,6 +11062,214 @@
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11271,7 +11385,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11437,7 +11551,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11602,7 +11716,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11819,7 +11933,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11949,7 +12063,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -11987,7 +12101,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -12025,7 +12139,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12248,7 +12362,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12449,7 +12563,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12672,336 +12786,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>6</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>5</v>
-      </c>
-      <c r="I3">
-        <v>7</v>
-      </c>
-      <c r="J3">
-        <v>8</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>14</v>
-      </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>13</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>12</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>22</v>
-      </c>
-      <c r="J6">
-        <v>15</v>
-      </c>
-      <c r="K6">
-        <v>14</v>
-      </c>
-      <c r="L6">
-        <v>16</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>20</v>
-      </c>
-      <c r="C7">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>11</v>
-      </c>
-      <c r="E7">
-        <v>21</v>
-      </c>
-      <c r="F7">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>18</v>
-      </c>
-      <c r="H7">
-        <v>21</v>
-      </c>
-      <c r="I7">
-        <v>36</v>
-      </c>
-      <c r="J7">
-        <v>25</v>
-      </c>
-      <c r="K7">
-        <v>21</v>
-      </c>
-      <c r="L7">
-        <v>22</v>
-      </c>
-      <c r="M7">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13066,92 +12851,137 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L2">
         <v>3</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
       <c r="I4">
         <v>1</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
       <c r="C5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>3</v>
@@ -13162,40 +12992,111 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="L6">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -13204,163 +13105,6 @@
 </file>
 
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13425,74 +13169,53 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
       <c r="D3">
         <v>3</v>
       </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
@@ -13501,40 +13224,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -13542,40 +13265,197 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -13584,6 +13464,229 @@
 </file>
 
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
+      </c>
+      <c r="H5">
+        <v>9</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>12</v>
+      </c>
+      <c r="K5">
+        <v>8</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>13</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>15</v>
+      </c>
+      <c r="J6">
+        <v>20</v>
+      </c>
+      <c r="K6">
+        <v>13</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13636,7 +13739,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13790,7 +13893,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13933,7 +14036,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14021,7 +14124,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14200,7 +14303,260 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>10</v>
+      </c>
+      <c r="M3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>25</v>
+      </c>
+      <c r="D5">
+        <v>16</v>
+      </c>
+      <c r="E5">
+        <v>27</v>
+      </c>
+      <c r="F5">
+        <v>24</v>
+      </c>
+      <c r="G5">
+        <v>19</v>
+      </c>
+      <c r="H5">
+        <v>39</v>
+      </c>
+      <c r="I5">
+        <v>16</v>
+      </c>
+      <c r="J5">
+        <v>17</v>
+      </c>
+      <c r="K5">
+        <v>19</v>
+      </c>
+      <c r="L5">
+        <v>11</v>
+      </c>
+      <c r="M5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>34</v>
+      </c>
+      <c r="D6">
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <v>37</v>
+      </c>
+      <c r="F6">
+        <v>35</v>
+      </c>
+      <c r="G6">
+        <v>25</v>
+      </c>
+      <c r="H6">
+        <v>48</v>
+      </c>
+      <c r="I6">
+        <v>22</v>
+      </c>
+      <c r="J6">
+        <v>33</v>
+      </c>
+      <c r="K6">
+        <v>35</v>
+      </c>
+      <c r="L6">
+        <v>23</v>
+      </c>
+      <c r="M6">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14285,7 +14641,7 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -14317,359 +14673,13 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
       <c r="J5">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -14700,25 +14710,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E1" s="1">
         <v>2019</v>
       </c>
       <c r="F1" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="G1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H1" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="I1" s="1">
         <v>2024</v>
@@ -14734,16 +14744,10 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="K2">
         <v>1</v>
       </c>
     </row>
@@ -14751,13 +14755,16 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
         <v>1</v>
       </c>
       <c r="K3">
@@ -14777,27 +14784,27 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
         <v>1</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -14806,31 +14813,31 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6">
         <v>4</v>
@@ -14954,7 +14961,7 @@
         <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -15041,7 +15048,7 @@
         <v>4</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -16127,7 +16134,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -16193,16 +16200,37 @@
       <c r="B2">
         <v>2</v>
       </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
       </c>
       <c r="I2">
+        <v>6</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -16211,127 +16239,150 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
         <v>4</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
+        <v>14</v>
+      </c>
+      <c r="C6">
         <v>13</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
       </c>
       <c r="D6">
         <v>7</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>11</v>
+      </c>
+      <c r="E7">
+        <v>21</v>
+      </c>
+      <c r="F7">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>21</v>
+      </c>
+      <c r="I7">
+        <v>36</v>
+      </c>
+      <c r="J7">
+        <v>25</v>
+      </c>
+      <c r="K7">
+        <v>21</v>
+      </c>
+      <c r="L7">
+        <v>22</v>
+      </c>
+      <c r="M7">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -16863,7 +16914,7 @@
         <v>2</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>2</v>
@@ -16904,7 +16955,7 @@
         <v>3</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -17767,7 +17818,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -17781,11 +17832,9 @@
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -17802,197 +17851,149 @@
         <v>2018</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G1" s="1">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
       <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>14</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
         <v>8</v>
       </c>
-      <c r="F6">
-        <v>25</v>
-      </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
       <c r="I6">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>12</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -18913,10 +18914,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -18979,26 +18980,17 @@
       <c r="B2">
         <v>2</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="F2">
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19009,116 +19001,124 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>9</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>7</v>
-      </c>
-      <c r="J4">
-        <v>9</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
         <v>11</v>
       </c>
-      <c r="C5">
-        <v>13</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>10</v>
-      </c>
-      <c r="G5">
+      <c r="J6">
         <v>8</v>
       </c>
-      <c r="H5">
-        <v>8</v>
-      </c>
-      <c r="I5">
-        <v>11</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-      <c r="M5">
-        <v>8</v>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-ytd.xlsx
+++ b/output/cta-violent-crime-ytd.xlsx
@@ -9,33 +9,33 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Riverdale" sheetId="3" r:id="rId3"/>
-    <sheet name="Fuller Park" sheetId="4" r:id="rId4"/>
-    <sheet name="North Lawndale" sheetId="5" r:id="rId5"/>
-    <sheet name="Little Village" sheetId="6" r:id="rId6"/>
-    <sheet name="Lake View" sheetId="7" r:id="rId7"/>
-    <sheet name="Austin" sheetId="8" r:id="rId8"/>
-    <sheet name="Roseland" sheetId="9" r:id="rId9"/>
-    <sheet name="Albany Park" sheetId="10" r:id="rId10"/>
-    <sheet name="Woodlawn" sheetId="11" r:id="rId11"/>
-    <sheet name="South Shore" sheetId="12" r:id="rId12"/>
-    <sheet name="Old Town" sheetId="13" r:id="rId13"/>
-    <sheet name="Loop" sheetId="14" r:id="rId14"/>
-    <sheet name="O'Hare" sheetId="15" r:id="rId15"/>
-    <sheet name="Near South Side" sheetId="16" r:id="rId16"/>
-    <sheet name="Grand Crossing" sheetId="17" r:id="rId17"/>
-    <sheet name="Avondale" sheetId="18" r:id="rId18"/>
-    <sheet name="Rush &amp; Division" sheetId="19" r:id="rId19"/>
-    <sheet name="Oakland" sheetId="20" r:id="rId20"/>
-    <sheet name="Chatham" sheetId="21" r:id="rId21"/>
-    <sheet name="New City" sheetId="22" r:id="rId22"/>
-    <sheet name="Belmont Cragin" sheetId="23" r:id="rId23"/>
-    <sheet name="West Loop" sheetId="24" r:id="rId24"/>
-    <sheet name="Uptown" sheetId="25" r:id="rId25"/>
-    <sheet name="Hegewisch" sheetId="26" r:id="rId26"/>
-    <sheet name="Grand Boulevard" sheetId="27" r:id="rId27"/>
-    <sheet name="West Town" sheetId="28" r:id="rId28"/>
-    <sheet name="Englewood" sheetId="29" r:id="rId29"/>
+    <sheet name="Englewood" sheetId="3" r:id="rId3"/>
+    <sheet name="Uptown" sheetId="4" r:id="rId4"/>
+    <sheet name="Riverdale" sheetId="5" r:id="rId5"/>
+    <sheet name="Fuller Park" sheetId="6" r:id="rId6"/>
+    <sheet name="North Lawndale" sheetId="7" r:id="rId7"/>
+    <sheet name="Little Village" sheetId="8" r:id="rId8"/>
+    <sheet name="Lake View" sheetId="9" r:id="rId9"/>
+    <sheet name="Austin" sheetId="10" r:id="rId10"/>
+    <sheet name="Roseland" sheetId="11" r:id="rId11"/>
+    <sheet name="Albany Park" sheetId="12" r:id="rId12"/>
+    <sheet name="Woodlawn" sheetId="13" r:id="rId13"/>
+    <sheet name="South Shore" sheetId="14" r:id="rId14"/>
+    <sheet name="Old Town" sheetId="15" r:id="rId15"/>
+    <sheet name="Loop" sheetId="16" r:id="rId16"/>
+    <sheet name="O'Hare" sheetId="17" r:id="rId17"/>
+    <sheet name="Near South Side" sheetId="18" r:id="rId18"/>
+    <sheet name="Grand Crossing" sheetId="19" r:id="rId19"/>
+    <sheet name="Avondale" sheetId="20" r:id="rId20"/>
+    <sheet name="Rush &amp; Division" sheetId="21" r:id="rId21"/>
+    <sheet name="Oakland" sheetId="22" r:id="rId22"/>
+    <sheet name="Chatham" sheetId="23" r:id="rId23"/>
+    <sheet name="New City" sheetId="24" r:id="rId24"/>
+    <sheet name="Belmont Cragin" sheetId="25" r:id="rId25"/>
+    <sheet name="West Loop" sheetId="26" r:id="rId26"/>
+    <sheet name="Hegewisch" sheetId="27" r:id="rId27"/>
+    <sheet name="Grand Boulevard" sheetId="28" r:id="rId28"/>
+    <sheet name="West Town" sheetId="29" r:id="rId29"/>
     <sheet name="Greektown" sheetId="30" r:id="rId30"/>
     <sheet name="Edgewater" sheetId="31" r:id="rId31"/>
     <sheet name="Little Italy, UIC" sheetId="32" r:id="rId32"/>
@@ -868,7 +868,7 @@
         <v>52</v>
       </c>
       <c r="F2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>66</v>
@@ -883,13 +883,13 @@
         <v>88</v>
       </c>
       <c r="K2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L2">
         <v>105</v>
       </c>
       <c r="M2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -912,22 +912,22 @@
         <v>99</v>
       </c>
       <c r="G3">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H3">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J3">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K3">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="M3">
         <v>155</v>
@@ -1017,40 +1017,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C6">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D6">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E6">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F6">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G6">
         <v>367</v>
       </c>
       <c r="H6">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I6">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J6">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K6">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L6">
         <v>354</v>
       </c>
       <c r="M6">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1058,40 +1058,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C7">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D7">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E7">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F7">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="G7">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H7">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="I7">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="J7">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="K7">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="L7">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="M7">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -1100,191 +1100,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1350,19 +1165,40 @@
         <v>1</v>
       </c>
       <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
         <v>2</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
       <c r="I2">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1370,45 +1206,63 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>11</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1416,40 +1270,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1457,40 +1311,298 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>34</v>
+      </c>
+      <c r="D6">
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <v>38</v>
+      </c>
+      <c r="F6">
+        <v>35</v>
+      </c>
+      <c r="G6">
+        <v>25</v>
+      </c>
+      <c r="H6">
+        <v>48</v>
+      </c>
+      <c r="I6">
+        <v>22</v>
+      </c>
+      <c r="J6">
+        <v>34</v>
+      </c>
+      <c r="K6">
+        <v>36</v>
+      </c>
+      <c r="L6">
+        <v>24</v>
+      </c>
+      <c r="M6">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>6</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <v>7</v>
+      </c>
+      <c r="J3">
+        <v>8</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>14</v>
+      </c>
+      <c r="C6">
         <v>13</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
       </c>
       <c r="D6">
         <v>7</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I6">
+        <v>22</v>
+      </c>
+      <c r="J6">
+        <v>15</v>
+      </c>
+      <c r="K6">
+        <v>14</v>
+      </c>
+      <c r="L6">
+        <v>16</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
         <v>11</v>
       </c>
-      <c r="J6">
-        <v>8</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
+      <c r="E7">
+        <v>21</v>
+      </c>
+      <c r="F7">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>21</v>
+      </c>
+      <c r="I7">
+        <v>36</v>
+      </c>
+      <c r="J7">
+        <v>25</v>
+      </c>
+      <c r="K7">
+        <v>21</v>
+      </c>
+      <c r="L7">
+        <v>22</v>
+      </c>
+      <c r="M7">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1499,6 +1611,405 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1713,7 +2224,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1829,7 +2340,7 @@
         <v>4</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <v>2</v>
@@ -1864,7 +2375,7 @@
         <v>3</v>
       </c>
       <c r="K4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L4">
         <v>4</v>
@@ -1905,457 +2416,13 @@
         <v>8</v>
       </c>
       <c r="K5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L5">
         <v>7</v>
       </c>
       <c r="M5">
         <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>9</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>8</v>
-      </c>
-      <c r="I2">
-        <v>10</v>
-      </c>
-      <c r="J2">
-        <v>15</v>
-      </c>
-      <c r="K2">
-        <v>12</v>
-      </c>
-      <c r="L2">
-        <v>13</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>11</v>
-      </c>
-      <c r="D3">
-        <v>16</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>14</v>
-      </c>
-      <c r="H3">
-        <v>11</v>
-      </c>
-      <c r="I3">
-        <v>25</v>
-      </c>
-      <c r="J3">
-        <v>24</v>
-      </c>
-      <c r="K3">
-        <v>23</v>
-      </c>
-      <c r="L3">
-        <v>24</v>
-      </c>
-      <c r="M3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>4</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>4</v>
-      </c>
-      <c r="M4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>22</v>
-      </c>
-      <c r="C6">
-        <v>27</v>
-      </c>
-      <c r="D6">
-        <v>34</v>
-      </c>
-      <c r="E6">
-        <v>51</v>
-      </c>
-      <c r="F6">
-        <v>43</v>
-      </c>
-      <c r="G6">
-        <v>46</v>
-      </c>
-      <c r="H6">
-        <v>47</v>
-      </c>
-      <c r="I6">
-        <v>68</v>
-      </c>
-      <c r="J6">
-        <v>47</v>
-      </c>
-      <c r="K6">
-        <v>40</v>
-      </c>
-      <c r="L6">
-        <v>36</v>
-      </c>
-      <c r="M6">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>36</v>
-      </c>
-      <c r="C7">
-        <v>42</v>
-      </c>
-      <c r="D7">
-        <v>60</v>
-      </c>
-      <c r="E7">
-        <v>62</v>
-      </c>
-      <c r="F7">
-        <v>58</v>
-      </c>
-      <c r="G7">
-        <v>65</v>
-      </c>
-      <c r="H7">
-        <v>68</v>
-      </c>
-      <c r="I7">
-        <v>107</v>
-      </c>
-      <c r="J7">
-        <v>90</v>
-      </c>
-      <c r="K7">
-        <v>77</v>
-      </c>
-      <c r="L7">
-        <v>78</v>
-      </c>
-      <c r="M7">
-        <v>45</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>5</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2428,17 +2495,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
       <c r="F2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="J2">
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>12</v>
+      </c>
+      <c r="L2">
+        <v>13</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -2448,41 +2536,89 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="H3">
+        <v>11</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="L3">
+        <v>24</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K5">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -2491,40 +2627,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2532,40 +2668,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -2574,6 +2710,171 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>5</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2638,98 +2939,53 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
       <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>6</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>12</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -2737,19 +2993,7 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -2758,40 +3002,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2799,40 +3043,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="J7">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2840,9 +3084,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -2906,343 +3150,200 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
       <c r="E3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K4">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
       <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="M6">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>12</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>14</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
         <v>13</v>
       </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>23</v>
+      </c>
+      <c r="C7">
+        <v>30</v>
+      </c>
+      <c r="D7">
+        <v>28</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>37</v>
+      </c>
+      <c r="G7">
+        <v>21</v>
+      </c>
+      <c r="H7">
+        <v>32</v>
+      </c>
+      <c r="I7">
+        <v>31</v>
+      </c>
+      <c r="J7">
+        <v>31</v>
+      </c>
+      <c r="K7">
+        <v>50</v>
+      </c>
+      <c r="L7">
+        <v>48</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -3403,7 +3504,7 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J5">
         <v>18</v>
@@ -3435,10 +3536,10 @@
         <v>5</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
         <v>4</v>
@@ -3505,7 +3606,7 @@
         <v>24</v>
       </c>
       <c r="E8">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F8">
         <v>35</v>
@@ -3523,10 +3624,10 @@
         <v>34</v>
       </c>
       <c r="K8">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M8">
         <v>37</v>
@@ -3812,7 +3913,7 @@
         <v>12</v>
       </c>
       <c r="F19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G19">
         <v>18</v>
@@ -3841,7 +3942,7 @@
         <v>26</v>
       </c>
       <c r="B20">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -4115,10 +4216,10 @@
         <v>46</v>
       </c>
       <c r="L28">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M28">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -4185,7 +4286,7 @@
         <v>3</v>
       </c>
       <c r="I30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30">
         <v>4</v>
@@ -4842,7 +4943,7 @@
         <v>1</v>
       </c>
       <c r="K51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L51">
         <v>2</v>
@@ -4903,7 +5004,7 @@
         <v>42</v>
       </c>
       <c r="D53">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E53">
         <v>62</v>
@@ -4915,13 +5016,13 @@
         <v>65</v>
       </c>
       <c r="H53">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I53">
         <v>107</v>
       </c>
       <c r="J53">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K53">
         <v>77</v>
@@ -5056,7 +5157,7 @@
         <v>1</v>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E59">
         <v>1</v>
@@ -5417,7 +5518,7 @@
         <v>8</v>
       </c>
       <c r="K70">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L70">
         <v>7</v>
@@ -5533,7 +5634,7 @@
         <v>13</v>
       </c>
       <c r="H74">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I74">
         <v>15</v>
@@ -5591,7 +5692,7 @@
         <v>82</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C76">
         <v>12</v>
@@ -5744,7 +5845,7 @@
         <v>4</v>
       </c>
       <c r="L79">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M79">
         <v>3</v>
@@ -5909,7 +6010,7 @@
         <v>91</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C85">
         <v>12</v>
@@ -5983,7 +6084,7 @@
         <v>10</v>
       </c>
       <c r="M86">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -6152,7 +6253,7 @@
         <v>11</v>
       </c>
       <c r="L91">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M91">
         <v>9</v>
@@ -6277,7 +6378,7 @@
         <v>2</v>
       </c>
       <c r="H95">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I95">
         <v>4</v>
@@ -6303,7 +6404,7 @@
         <v>13</v>
       </c>
       <c r="C96">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D96">
         <v>7</v>
@@ -6315,7 +6416,7 @@
         <v>5</v>
       </c>
       <c r="G96">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H96">
         <v>6</v>
@@ -6324,7 +6425,7 @@
         <v>11</v>
       </c>
       <c r="J96">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K96">
         <v>7</v>
@@ -6353,7 +6454,7 @@
         <v>1</v>
       </c>
       <c r="F97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G97">
         <v>4</v>
@@ -6382,40 +6483,40 @@
         <v>6</v>
       </c>
       <c r="B98">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C98">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D98">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E98">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F98">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="G98">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H98">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="I98">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="J98">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="K98">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="L98">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="M98">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -6524,6 +6625,416 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>13</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6610,7 +7121,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6775,7 +7286,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>12</v>
@@ -6816,7 +7327,7 @@
         <v>12</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6">
         <v>18</v>
@@ -6845,7 +7356,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7020,7 +7531,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7152,7 +7663,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7271,7 +7782,7 @@
         <v>5</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -7369,7 +7880,7 @@
         <v>11</v>
       </c>
       <c r="L7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>9</v>
@@ -7380,7 +7891,293 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>10</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7448,35 +8245,29 @@
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
       <c r="D2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7489,39 +8280,27 @@
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
@@ -7530,40 +8309,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -7571,40 +8350,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>8</v>
       </c>
       <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
         <v>12</v>
       </c>
-      <c r="K6">
-        <v>14</v>
-      </c>
-      <c r="L6">
+      <c r="M6">
         <v>10</v>
-      </c>
-      <c r="M6">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -7612,507 +8391,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>8</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>10</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>6</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>11</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
-      <c r="M6">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8243,7 +8522,7 @@
         <v>15</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M3">
         <v>5</v>
@@ -8318,7 +8597,7 @@
         <v>33</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8356,151 +8635,10 @@
         <v>46</v>
       </c>
       <c r="L7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M7">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -9233,7 +9371,7 @@
         <v>3</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -9271,7 +9409,7 @@
         <v>3</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>4</v>
@@ -9815,7 +9953,7 @@
         <v>1</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -9908,7 +10046,7 @@
         <v>4</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -10418,7 +10556,7 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -10510,7 +10648,7 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -10544,7 +10682,7 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -10604,43 +10742,58 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
       <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>2</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -10649,23 +10802,23 @@
         <v>2</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
@@ -10674,40 +10827,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>3</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G5">
+        <v>13</v>
+      </c>
+      <c r="H5">
         <v>7</v>
       </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
       <c r="I5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J5">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10715,40 +10868,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
         <v>8</v>
       </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
+      <c r="G6">
+        <v>20</v>
+      </c>
+      <c r="H6">
+        <v>13</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>14</v>
+      </c>
+      <c r="L6">
+        <v>10</v>
+      </c>
+      <c r="M6">
         <v>9</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>11</v>
-      </c>
-      <c r="K6">
-        <v>15</v>
-      </c>
-      <c r="L6">
-        <v>25</v>
-      </c>
-      <c r="M6">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -11132,7 +11285,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -11173,7 +11326,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>12</v>
@@ -11563,7 +11716,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -11595,7 +11748,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -12401,6 +12554,9 @@
       <c r="H3">
         <v>1</v>
       </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
       <c r="J3">
         <v>1</v>
       </c>
@@ -12492,7 +12648,7 @@
         <v>6</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J6">
         <v>18</v>
@@ -12715,10 +12871,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -12729,11 +12885,9 @@
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12756,191 +12910,99 @@
         <v>2020</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
       <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>12</v>
-      </c>
-      <c r="C6">
-        <v>15</v>
-      </c>
-      <c r="D6">
-        <v>17</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>25</v>
-      </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>19</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>12</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -13089,7 +13151,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -13130,7 +13192,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>12</v>
@@ -13708,7 +13770,7 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>3</v>
@@ -13801,7 +13863,7 @@
         <v>13</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I6">
         <v>15</v>
@@ -14264,10 +14326,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -14278,9 +14340,11 @@
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14294,36 +14358,39 @@
         <v>2017</v>
       </c>
       <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
         <v>2019</v>
       </c>
-      <c r="F1" s="1">
+      <c r="G1" s="1">
         <v>2020</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
         <v>2021</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="J1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="K1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
+      <c r="D2">
+        <v>2</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -14331,94 +14398,142 @@
       <c r="I2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
       <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>11</v>
+      </c>
+      <c r="L5">
+        <v>20</v>
+      </c>
+      <c r="M5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>15</v>
+      </c>
+      <c r="L6">
+        <v>25</v>
+      </c>
+      <c r="M6">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -14684,7 +14799,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -14707,7 +14822,7 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -14842,7 +14957,7 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -14874,7 +14989,7 @@
         <v>2</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -16138,38 +16253,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L2">
         <v>3</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16177,92 +16295,77 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>3</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
       <c r="H4">
         <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
       <c r="C5">
+        <v>13</v>
+      </c>
+      <c r="D5">
+        <v>16</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>21</v>
+      </c>
+      <c r="G5">
         <v>11</v>
       </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>8</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
       <c r="H5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <v>6</v>
@@ -16279,40 +16382,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G6">
         <v>16</v>
       </c>
       <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
         <v>19</v>
       </c>
-      <c r="I6">
-        <v>20</v>
-      </c>
       <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>12</v>
+      </c>
+      <c r="L6">
+        <v>13</v>
+      </c>
+      <c r="M6">
         <v>9</v>
-      </c>
-      <c r="K6">
-        <v>18</v>
-      </c>
-      <c r="L6">
-        <v>17</v>
-      </c>
-      <c r="M6">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -16589,6 +16692,9 @@
       <c r="E3">
         <v>1</v>
       </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
       <c r="G3">
         <v>1</v>
       </c>
@@ -16616,7 +16722,7 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -16642,10 +16748,10 @@
         <v>5</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -17796,7 +17902,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -17810,11 +17916,9 @@
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -17828,218 +17932,131 @@
         <v>2017</v>
       </c>
       <c r="E1" s="1">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G1" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>6</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
       <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>10</v>
-      </c>
-      <c r="M3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>13</v>
-      </c>
-      <c r="C5">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>19</v>
-      </c>
-      <c r="H5">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>19</v>
-      </c>
-      <c r="L5">
-        <v>11</v>
-      </c>
-      <c r="M5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>35</v>
-      </c>
-      <c r="L6">
-        <v>23</v>
-      </c>
-      <c r="M6">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -18892,7 +18909,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -18955,11 +18972,8 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -18971,25 +18985,25 @@
         <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18997,37 +19011,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>5</v>
       </c>
       <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
         <v>7</v>
-      </c>
-      <c r="J3">
-        <v>8</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
       </c>
       <c r="M3">
         <v>4</v>
@@ -19040,107 +19054,99 @@
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
-      <c r="J4">
-        <v>1</v>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>11</v>
+      </c>
+      <c r="I5">
+        <v>16</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
         <v>13</v>
       </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>19</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
+        <v>18</v>
+      </c>
+      <c r="L6">
+        <v>17</v>
+      </c>
+      <c r="M6">
         <v>13</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>12</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>22</v>
-      </c>
-      <c r="J6">
-        <v>15</v>
-      </c>
-      <c r="K6">
-        <v>14</v>
-      </c>
-      <c r="L6">
-        <v>16</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>20</v>
-      </c>
-      <c r="C7">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>11</v>
-      </c>
-      <c r="E7">
-        <v>21</v>
-      </c>
-      <c r="F7">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>18</v>
-      </c>
-      <c r="H7">
-        <v>21</v>
-      </c>
-      <c r="I7">
-        <v>36</v>
-      </c>
-      <c r="J7">
-        <v>25</v>
-      </c>
-      <c r="K7">
-        <v>21</v>
-      </c>
-      <c r="L7">
-        <v>22</v>
-      </c>
-      <c r="M7">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-ytd.xlsx
+++ b/output/cta-violent-crime-ytd.xlsx
@@ -971,7 +971,7 @@
         <v>17</v>
       </c>
       <c r="M4">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>669</v>
       </c>
       <c r="M7">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -2602,7 +2602,7 @@
         <v>4</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2704,7 +2704,7 @@
         <v>78</v>
       </c>
       <c r="M7">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -5034,7 +5034,7 @@
         <v>78</v>
       </c>
       <c r="M53">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -6519,7 +6519,7 @@
         <v>669</v>
       </c>
       <c r="M98">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-ytd.xlsx
+++ b/output/cta-violent-crime-ytd.xlsx
@@ -9,42 +9,42 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="North Lawndale" sheetId="3" r:id="rId3"/>
-    <sheet name="Englewood" sheetId="4" r:id="rId4"/>
-    <sheet name="Uptown" sheetId="5" r:id="rId5"/>
-    <sheet name="Riverdale" sheetId="6" r:id="rId6"/>
-    <sheet name="Fuller Park" sheetId="7" r:id="rId7"/>
-    <sheet name="Little Village" sheetId="8" r:id="rId8"/>
-    <sheet name="Lake View" sheetId="9" r:id="rId9"/>
-    <sheet name="Austin" sheetId="10" r:id="rId10"/>
-    <sheet name="Roseland" sheetId="11" r:id="rId11"/>
-    <sheet name="Albany Park" sheetId="12" r:id="rId12"/>
-    <sheet name="Woodlawn" sheetId="13" r:id="rId13"/>
-    <sheet name="South Shore" sheetId="14" r:id="rId14"/>
-    <sheet name="Old Town" sheetId="15" r:id="rId15"/>
-    <sheet name="Loop" sheetId="16" r:id="rId16"/>
-    <sheet name="O'Hare" sheetId="17" r:id="rId17"/>
-    <sheet name="Near South Side" sheetId="18" r:id="rId18"/>
-    <sheet name="Grand Crossing" sheetId="19" r:id="rId19"/>
-    <sheet name="Avondale" sheetId="20" r:id="rId20"/>
-    <sheet name="Rush &amp; Division" sheetId="21" r:id="rId21"/>
-    <sheet name="Oakland" sheetId="22" r:id="rId22"/>
-    <sheet name="Chatham" sheetId="23" r:id="rId23"/>
-    <sheet name="New City" sheetId="24" r:id="rId24"/>
-    <sheet name="Belmont Cragin" sheetId="25" r:id="rId25"/>
-    <sheet name="West Loop" sheetId="26" r:id="rId26"/>
-    <sheet name="Hegewisch" sheetId="27" r:id="rId27"/>
-    <sheet name="Grand Boulevard" sheetId="28" r:id="rId28"/>
-    <sheet name="West Town" sheetId="29" r:id="rId29"/>
-    <sheet name="Greektown" sheetId="30" r:id="rId30"/>
-    <sheet name="Edgewater" sheetId="31" r:id="rId31"/>
-    <sheet name="Little Italy, UIC" sheetId="32" r:id="rId32"/>
-    <sheet name="Gage Park" sheetId="33" r:id="rId33"/>
-    <sheet name="Humboldt Park" sheetId="34" r:id="rId34"/>
-    <sheet name="Lower West Side" sheetId="35" r:id="rId35"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="36" r:id="rId36"/>
-    <sheet name="Norwood Park" sheetId="37" r:id="rId37"/>
-    <sheet name="Garfield Park" sheetId="38" r:id="rId38"/>
+    <sheet name="Garfield Park" sheetId="3" r:id="rId3"/>
+    <sheet name="North Lawndale" sheetId="4" r:id="rId4"/>
+    <sheet name="Englewood" sheetId="5" r:id="rId5"/>
+    <sheet name="Uptown" sheetId="6" r:id="rId6"/>
+    <sheet name="Riverdale" sheetId="7" r:id="rId7"/>
+    <sheet name="Fuller Park" sheetId="8" r:id="rId8"/>
+    <sheet name="Little Village" sheetId="9" r:id="rId9"/>
+    <sheet name="Lake View" sheetId="10" r:id="rId10"/>
+    <sheet name="Austin" sheetId="11" r:id="rId11"/>
+    <sheet name="Roseland" sheetId="12" r:id="rId12"/>
+    <sheet name="Albany Park" sheetId="13" r:id="rId13"/>
+    <sheet name="Woodlawn" sheetId="14" r:id="rId14"/>
+    <sheet name="South Shore" sheetId="15" r:id="rId15"/>
+    <sheet name="Old Town" sheetId="16" r:id="rId16"/>
+    <sheet name="Loop" sheetId="17" r:id="rId17"/>
+    <sheet name="O'Hare" sheetId="18" r:id="rId18"/>
+    <sheet name="Near South Side" sheetId="19" r:id="rId19"/>
+    <sheet name="Grand Crossing" sheetId="20" r:id="rId20"/>
+    <sheet name="Avondale" sheetId="21" r:id="rId21"/>
+    <sheet name="Rush &amp; Division" sheetId="22" r:id="rId22"/>
+    <sheet name="Oakland" sheetId="23" r:id="rId23"/>
+    <sheet name="Chatham" sheetId="24" r:id="rId24"/>
+    <sheet name="New City" sheetId="25" r:id="rId25"/>
+    <sheet name="Belmont Cragin" sheetId="26" r:id="rId26"/>
+    <sheet name="West Loop" sheetId="27" r:id="rId27"/>
+    <sheet name="Hegewisch" sheetId="28" r:id="rId28"/>
+    <sheet name="Grand Boulevard" sheetId="29" r:id="rId29"/>
+    <sheet name="West Town" sheetId="30" r:id="rId30"/>
+    <sheet name="Greektown" sheetId="31" r:id="rId31"/>
+    <sheet name="Edgewater" sheetId="32" r:id="rId32"/>
+    <sheet name="Little Italy, UIC" sheetId="33" r:id="rId33"/>
+    <sheet name="Gage Park" sheetId="34" r:id="rId34"/>
+    <sheet name="Humboldt Park" sheetId="35" r:id="rId35"/>
+    <sheet name="Lower West Side" sheetId="36" r:id="rId36"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="37" r:id="rId37"/>
+    <sheet name="Norwood Park" sheetId="38" r:id="rId38"/>
     <sheet name="Wrigleyville" sheetId="39" r:id="rId39"/>
     <sheet name="Auburn Gresham" sheetId="40" r:id="rId40"/>
     <sheet name="Rogers Park" sheetId="41" r:id="rId41"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="104">
   <si>
     <t>crime_category</t>
   </si>
@@ -856,25 +856,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F2">
+        <v>68</v>
+      </c>
+      <c r="G2">
         <v>67</v>
       </c>
-      <c r="G2">
-        <v>66</v>
-      </c>
       <c r="H2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I2">
         <v>91</v>
@@ -886,7 +886,7 @@
         <v>111</v>
       </c>
       <c r="L2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M2">
         <v>89</v>
@@ -897,40 +897,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D3">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E3">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F3">
         <v>99</v>
       </c>
       <c r="G3">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H3">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I3">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J3">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K3">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L3">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="M3">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -965,10 +965,10 @@
         <v>16</v>
       </c>
       <c r="K4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M4">
         <v>23</v>
@@ -1017,37 +1017,37 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C6">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D6">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E6">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F6">
         <v>404</v>
       </c>
       <c r="G6">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="H6">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="I6">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="J6">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="K6">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="L6">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M6">
         <v>198</v>
@@ -1058,40 +1058,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C7">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="D7">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="E7">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="F7">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="G7">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="H7">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="I7">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="J7">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="K7">
-        <v>700</v>
+        <v>711</v>
       </c>
       <c r="L7">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="M7">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -1164,41 +1164,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
       <c r="C2">
         <v>4</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1206,59 +1203,59 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
       </c>
       <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
         <v>2</v>
       </c>
       <c r="M4">
@@ -1269,41 +1266,38 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>14</v>
-      </c>
       <c r="C5">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="G5">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="I5">
         <v>16</v>
       </c>
       <c r="J5">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1311,40 +1305,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H6">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I6">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J6">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="L6">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="M6">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1353,6 +1347,259 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>8</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>11</v>
+      </c>
+      <c r="M3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>14</v>
+      </c>
+      <c r="C5">
+        <v>25</v>
+      </c>
+      <c r="D5">
+        <v>16</v>
+      </c>
+      <c r="E5">
+        <v>28</v>
+      </c>
+      <c r="F5">
+        <v>24</v>
+      </c>
+      <c r="G5">
+        <v>19</v>
+      </c>
+      <c r="H5">
+        <v>40</v>
+      </c>
+      <c r="I5">
+        <v>17</v>
+      </c>
+      <c r="J5">
+        <v>17</v>
+      </c>
+      <c r="K5">
+        <v>20</v>
+      </c>
+      <c r="L5">
+        <v>12</v>
+      </c>
+      <c r="M5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>23</v>
+      </c>
+      <c r="C6">
+        <v>34</v>
+      </c>
+      <c r="D6">
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <v>38</v>
+      </c>
+      <c r="F6">
+        <v>36</v>
+      </c>
+      <c r="G6">
+        <v>25</v>
+      </c>
+      <c r="H6">
+        <v>49</v>
+      </c>
+      <c r="I6">
+        <v>23</v>
+      </c>
+      <c r="J6">
+        <v>34</v>
+      </c>
+      <c r="K6">
+        <v>37</v>
+      </c>
+      <c r="L6">
+        <v>25</v>
+      </c>
+      <c r="M6">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1424,7 +1671,7 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -1459,7 +1706,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -1549,7 +1796,7 @@
         <v>12</v>
       </c>
       <c r="I6">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J6">
         <v>15</v>
@@ -1569,13 +1816,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7">
         <v>20</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7">
         <v>21</v>
@@ -1590,7 +1837,7 @@
         <v>21</v>
       </c>
       <c r="I7">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J7">
         <v>25</v>
@@ -1610,7 +1857,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1696,6 +1943,9 @@
       <c r="B3">
         <v>1</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
       <c r="F3">
         <v>1</v>
       </c>
@@ -1763,7 +2013,7 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -1795,7 +2045,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1861,7 +2111,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1902,7 +2152,7 @@
         <v>5</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3">
         <v>4</v>
@@ -1968,7 +2218,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6">
         <v>11</v>
@@ -1992,7 +2242,7 @@
         <v>11</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>7</v>
@@ -2002,221 +2252,6 @@
       </c>
       <c r="M6">
         <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>9</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>7</v>
-      </c>
-      <c r="J4">
-        <v>9</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>13</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>8</v>
-      </c>
-      <c r="H5">
-        <v>8</v>
-      </c>
-      <c r="I5">
-        <v>11</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-      <c r="M5">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2289,26 +2324,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>2</v>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="I2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2316,34 +2354,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2351,40 +2392,40 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4">
         <v>7</v>
       </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4">
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4">
         <v>10</v>
       </c>
-      <c r="F4">
-        <v>15</v>
-      </c>
-      <c r="G4">
-        <v>9</v>
-      </c>
-      <c r="H4">
-        <v>6</v>
-      </c>
-      <c r="I4">
-        <v>14</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
       <c r="K4">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2392,40 +2433,40 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>8</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
         <v>11</v>
       </c>
-      <c r="F5">
-        <v>20</v>
-      </c>
-      <c r="G5">
-        <v>12</v>
-      </c>
-      <c r="H5">
-        <v>9</v>
-      </c>
-      <c r="I5">
-        <v>16</v>
-      </c>
       <c r="J5">
+        <v>11</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
+      </c>
+      <c r="M5">
         <v>8</v>
-      </c>
-      <c r="K5">
-        <v>20</v>
-      </c>
-      <c r="L5">
-        <v>7</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2434,6 +2475,215 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>15</v>
+      </c>
+      <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="I4">
+        <v>14</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>15</v>
+      </c>
+      <c r="L4">
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>20</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>9</v>
+      </c>
+      <c r="I5">
+        <v>16</v>
+      </c>
+      <c r="J5">
+        <v>9</v>
+      </c>
+      <c r="K5">
+        <v>20</v>
+      </c>
+      <c r="L5">
+        <v>7</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2645,7 +2895,7 @@
         <v>44</v>
       </c>
       <c r="G6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H6">
         <v>49</v>
@@ -2657,7 +2907,7 @@
         <v>47</v>
       </c>
       <c r="K6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L6">
         <v>36</v>
@@ -2686,7 +2936,7 @@
         <v>59</v>
       </c>
       <c r="G7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H7">
         <v>70</v>
@@ -2698,7 +2948,7 @@
         <v>91</v>
       </c>
       <c r="K7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L7">
         <v>78</v>
@@ -2712,7 +2962,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2797,6 +3047,9 @@
       <c r="E3">
         <v>1</v>
       </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
       <c r="G3">
         <v>1</v>
       </c>
@@ -2857,7 +3110,7 @@
         <v>2</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -2870,216 +3123,6 @@
       </c>
       <c r="J7">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>12</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>3</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3152,98 +3195,53 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
       <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>6</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>12</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -3251,19 +3249,7 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -3272,40 +3258,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3313,40 +3299,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="J7">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3423,7 +3409,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -3510,10 +3496,10 @@
         <v>14</v>
       </c>
       <c r="J5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L5">
         <v>20</v>
@@ -3559,7 +3545,7 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>10</v>
@@ -3612,25 +3598,25 @@
         <v>38</v>
       </c>
       <c r="F8">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G8">
         <v>25</v>
       </c>
       <c r="H8">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J8">
         <v>34</v>
       </c>
       <c r="K8">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M8">
         <v>37</v>
@@ -3685,16 +3671,16 @@
         <v>4</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10">
         <v>4</v>
       </c>
       <c r="J10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L10">
         <v>3</v>
@@ -3780,7 +3766,7 @@
         <v>2</v>
       </c>
       <c r="K14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>2</v>
@@ -3910,7 +3896,7 @@
         <v>8</v>
       </c>
       <c r="D19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19">
         <v>12</v>
@@ -3931,7 +3917,7 @@
         <v>17</v>
       </c>
       <c r="K19">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L19">
         <v>19</v>
@@ -3951,7 +3937,7 @@
         <v>1</v>
       </c>
       <c r="D20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -3960,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="G20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H20">
         <v>6</v>
       </c>
       <c r="I20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J20">
         <v>5</v>
@@ -3995,7 +3981,7 @@
         <v>2</v>
       </c>
       <c r="E21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F21">
         <v>10</v>
@@ -4039,7 +4025,7 @@
         <v>2</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22">
         <v>2</v>
@@ -4074,7 +4060,7 @@
         <v>2</v>
       </c>
       <c r="H23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>6</v>
@@ -4151,7 +4137,7 @@
         <v>1</v>
       </c>
       <c r="C27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27">
         <v>7</v>
@@ -4195,16 +4181,16 @@
         <v>39</v>
       </c>
       <c r="D28">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E28">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F28">
         <v>41</v>
       </c>
       <c r="G28">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H28">
         <v>38</v>
@@ -4216,10 +4202,10 @@
         <v>21</v>
       </c>
       <c r="K28">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L28">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M28">
         <v>27</v>
@@ -4257,7 +4243,7 @@
         <v>11</v>
       </c>
       <c r="K29">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L29">
         <v>25</v>
@@ -4298,7 +4284,7 @@
         <v>12</v>
       </c>
       <c r="L30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M30">
         <v>4</v>
@@ -4329,13 +4315,13 @@
         <v>11</v>
       </c>
       <c r="C32">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D32">
         <v>42</v>
       </c>
       <c r="E32">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F32">
         <v>52</v>
@@ -4344,7 +4330,7 @@
         <v>43</v>
       </c>
       <c r="H32">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I32">
         <v>37</v>
@@ -4359,7 +4345,7 @@
         <v>35</v>
       </c>
       <c r="M32">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -4369,6 +4355,9 @@
       <c r="D33">
         <v>1</v>
       </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
       <c r="I33">
         <v>1</v>
       </c>
@@ -4392,7 +4381,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D35">
         <v>6</v>
@@ -4439,7 +4428,7 @@
         <v>28</v>
       </c>
       <c r="E36">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F36">
         <v>37</v>
@@ -4451,7 +4440,7 @@
         <v>32</v>
       </c>
       <c r="I36">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J36">
         <v>32</v>
@@ -4460,7 +4449,7 @@
         <v>50</v>
       </c>
       <c r="L36">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M36">
         <v>27</v>
@@ -4569,7 +4558,7 @@
         <v>3</v>
       </c>
       <c r="G41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H41">
         <v>6</v>
@@ -4630,7 +4619,7 @@
         <v>49</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43">
         <v>4</v>
@@ -4648,7 +4637,7 @@
         <v>4</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I43">
         <v>5</v>
@@ -4724,7 +4713,7 @@
         <v>4</v>
       </c>
       <c r="J45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K45">
         <v>4</v>
@@ -4782,7 +4771,7 @@
         <v>13</v>
       </c>
       <c r="G47">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H47">
         <v>20</v>
@@ -4823,7 +4812,7 @@
         <v>3</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48">
         <v>4</v>
@@ -4851,6 +4840,9 @@
       <c r="B49">
         <v>1</v>
       </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
       <c r="D49">
         <v>2</v>
       </c>
@@ -4876,7 +4868,7 @@
         <v>1</v>
       </c>
       <c r="L49">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -4905,7 +4897,7 @@
         <v>12</v>
       </c>
       <c r="I50">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J50">
         <v>10</v>
@@ -4984,7 +4976,7 @@
         <v>5</v>
       </c>
       <c r="J52">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K52">
         <v>7</v>
@@ -5016,7 +5008,7 @@
         <v>59</v>
       </c>
       <c r="G53">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H53">
         <v>70</v>
@@ -5028,7 +5020,7 @@
         <v>91</v>
       </c>
       <c r="K53">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L53">
         <v>78</v>
@@ -5121,7 +5113,7 @@
         <v>5</v>
       </c>
       <c r="L56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M56">
         <v>1</v>
@@ -5169,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I59">
         <v>1</v>
@@ -5227,7 +5219,7 @@
         <v>1</v>
       </c>
       <c r="K61">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L61">
         <v>6</v>
@@ -5247,7 +5239,7 @@
         <v>3</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62">
         <v>5</v>
@@ -5322,6 +5314,9 @@
       <c r="B64">
         <v>1</v>
       </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
       <c r="F64">
         <v>3</v>
       </c>
@@ -5370,7 +5365,7 @@
         <v>13</v>
       </c>
       <c r="L65">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M65">
         <v>10</v>
@@ -5454,7 +5449,7 @@
         <v>2</v>
       </c>
       <c r="I68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J68">
         <v>2</v>
@@ -5518,7 +5513,7 @@
         <v>16</v>
       </c>
       <c r="J70">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K70">
         <v>20</v>
@@ -5628,7 +5623,7 @@
         <v>10</v>
       </c>
       <c r="E74">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F74">
         <v>10</v>
@@ -5640,16 +5635,16 @@
         <v>12</v>
       </c>
       <c r="I74">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J74">
         <v>20</v>
       </c>
       <c r="K74">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L74">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M74">
         <v>8</v>
@@ -5666,7 +5661,7 @@
         <v>1</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75">
         <v>3</v>
@@ -5704,7 +5699,7 @@
         <v>10</v>
       </c>
       <c r="E76">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F76">
         <v>15</v>
@@ -5736,13 +5731,13 @@
         <v>83</v>
       </c>
       <c r="B77">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C77">
         <v>20</v>
       </c>
       <c r="D77">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E77">
         <v>21</v>
@@ -5757,7 +5752,7 @@
         <v>21</v>
       </c>
       <c r="I77">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J77">
         <v>25</v>
@@ -5839,7 +5834,7 @@
         <v>8</v>
       </c>
       <c r="I79">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J79">
         <v>4</v>
@@ -5874,7 +5869,7 @@
         <v>4</v>
       </c>
       <c r="G80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H80">
         <v>4</v>
@@ -5938,7 +5933,7 @@
         <v>13</v>
       </c>
       <c r="D82">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E82">
         <v>5</v>
@@ -5956,7 +5951,7 @@
         <v>11</v>
       </c>
       <c r="J82">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K82">
         <v>5</v>
@@ -6002,7 +5997,7 @@
         <v>1</v>
       </c>
       <c r="L84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M84">
         <v>1</v>
@@ -6078,13 +6073,13 @@
         <v>8</v>
       </c>
       <c r="J86">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K86">
         <v>15</v>
       </c>
       <c r="L86">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M86">
         <v>9</v>
@@ -6229,7 +6224,7 @@
         <v>6</v>
       </c>
       <c r="C91">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D91">
         <v>6</v>
@@ -6404,7 +6399,7 @@
         <v>102</v>
       </c>
       <c r="B96">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C96">
         <v>11</v>
@@ -6428,7 +6423,7 @@
         <v>11</v>
       </c>
       <c r="J96">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K96">
         <v>7</v>
@@ -6486,40 +6481,40 @@
         <v>6</v>
       </c>
       <c r="B98">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C98">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="D98">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="E98">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="F98">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="G98">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="H98">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="I98">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="J98">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="K98">
-        <v>700</v>
+        <v>711</v>
       </c>
       <c r="L98">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="M98">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -6628,7 +6623,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -6692,135 +6687,200 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
       <c r="E3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K4">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
       <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>23</v>
+      </c>
+      <c r="C7">
+        <v>30</v>
+      </c>
+      <c r="D7">
+        <v>28</v>
+      </c>
+      <c r="E7">
+        <v>31</v>
+      </c>
+      <c r="F7">
+        <v>37</v>
+      </c>
+      <c r="G7">
+        <v>21</v>
+      </c>
+      <c r="H7">
+        <v>32</v>
+      </c>
+      <c r="I7">
+        <v>32</v>
+      </c>
+      <c r="J7">
+        <v>32</v>
+      </c>
+      <c r="K7">
+        <v>50</v>
+      </c>
+      <c r="L7">
+        <v>49</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -6893,59 +6953,59 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
         <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -6954,40 +7014,37 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -6995,40 +7052,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
         <v>8</v>
       </c>
-      <c r="G6">
-        <v>14</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>13</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
       <c r="K6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>3</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -7037,6 +7094,214 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>13</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7124,7 +7389,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7231,7 +7496,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -7252,7 +7517,7 @@
         <v>2</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L3">
         <v>5</v>
@@ -7324,7 +7589,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -7345,7 +7610,7 @@
         <v>17</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L6">
         <v>19</v>
@@ -7359,7 +7624,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7534,7 +7799,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7666,7 +7931,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7735,7 +8000,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -7856,7 +8121,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -7894,7 +8159,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7972,7 +8237,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8104,7 +8369,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -8142,7 +8407,7 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6">
         <v>6</v>
@@ -8180,7 +8445,262 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>7</v>
+      </c>
+      <c r="J3">
+        <v>9</v>
+      </c>
+      <c r="K3">
+        <v>14</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>26</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>33</v>
+      </c>
+      <c r="F6">
+        <v>44</v>
+      </c>
+      <c r="G6">
+        <v>35</v>
+      </c>
+      <c r="H6">
+        <v>32</v>
+      </c>
+      <c r="I6">
+        <v>24</v>
+      </c>
+      <c r="J6">
+        <v>22</v>
+      </c>
+      <c r="K6">
+        <v>21</v>
+      </c>
+      <c r="L6">
+        <v>25</v>
+      </c>
+      <c r="M6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>42</v>
+      </c>
+      <c r="E7">
+        <v>42</v>
+      </c>
+      <c r="F7">
+        <v>52</v>
+      </c>
+      <c r="G7">
+        <v>43</v>
+      </c>
+      <c r="H7">
+        <v>41</v>
+      </c>
+      <c r="I7">
+        <v>37</v>
+      </c>
+      <c r="J7">
+        <v>32</v>
+      </c>
+      <c r="K7">
+        <v>39</v>
+      </c>
+      <c r="L7">
+        <v>35</v>
+      </c>
+      <c r="M7">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8394,242 +8914,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>13</v>
-      </c>
-      <c r="D5">
-        <v>16</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>21</v>
-      </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>14</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>7</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>12</v>
-      </c>
-      <c r="C6">
-        <v>15</v>
-      </c>
-      <c r="D6">
-        <v>17</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>25</v>
-      </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>19</v>
-      </c>
-      <c r="J6">
-        <v>7</v>
-      </c>
-      <c r="K6">
-        <v>13</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8764,220 +9049,6 @@
       </c>
       <c r="J6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>12</v>
-      </c>
-      <c r="I5">
-        <v>6</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>7</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -9051,12 +9122,15 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
-      <c r="H2">
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
@@ -9066,66 +9140,45 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
       <c r="M4">
         <v>1</v>
       </c>
@@ -9135,40 +9188,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>5</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
         <v>7</v>
       </c>
-      <c r="J5">
-        <v>7</v>
-      </c>
-      <c r="K5">
-        <v>15</v>
-      </c>
       <c r="L5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -9176,40 +9229,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>8</v>
       </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>15</v>
-      </c>
-      <c r="F6">
-        <v>23</v>
-      </c>
       <c r="G6">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>12</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>10</v>
       </c>
       <c r="K6">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -9218,6 +9271,238 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>13</v>
+      </c>
+      <c r="F5">
+        <v>21</v>
+      </c>
+      <c r="G5">
+        <v>13</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>7</v>
+      </c>
+      <c r="K5">
+        <v>15</v>
+      </c>
+      <c r="L5">
+        <v>11</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>15</v>
+      </c>
+      <c r="F6">
+        <v>23</v>
+      </c>
+      <c r="G6">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>13</v>
+      </c>
+      <c r="J6">
+        <v>10</v>
+      </c>
+      <c r="K6">
+        <v>25</v>
+      </c>
+      <c r="L6">
+        <v>19</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9317,7 +9602,7 @@
         <v>2</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -9401,7 +9686,7 @@
         <v>12</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L6">
         <v>4</v>
@@ -9412,7 +9697,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9568,7 +9853,7 @@
         <v>2</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -9609,7 +9894,7 @@
         <v>3</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -9635,7 +9920,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9826,7 +10111,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9930,7 +10215,7 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -10023,7 +10308,7 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -10043,7 +10328,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10208,261 +10493,6 @@
       </c>
       <c r="K7">
         <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>6</v>
-      </c>
-      <c r="F2">
-        <v>4</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>7</v>
-      </c>
-      <c r="J3">
-        <v>9</v>
-      </c>
-      <c r="K3">
-        <v>14</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
-      <c r="M3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>25</v>
-      </c>
-      <c r="D6">
-        <v>30</v>
-      </c>
-      <c r="E6">
-        <v>31</v>
-      </c>
-      <c r="F6">
-        <v>44</v>
-      </c>
-      <c r="G6">
-        <v>35</v>
-      </c>
-      <c r="H6">
-        <v>31</v>
-      </c>
-      <c r="I6">
-        <v>24</v>
-      </c>
-      <c r="J6">
-        <v>22</v>
-      </c>
-      <c r="K6">
-        <v>21</v>
-      </c>
-      <c r="L6">
-        <v>25</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>28</v>
-      </c>
-      <c r="D7">
-        <v>42</v>
-      </c>
-      <c r="E7">
-        <v>40</v>
-      </c>
-      <c r="F7">
-        <v>52</v>
-      </c>
-      <c r="G7">
-        <v>43</v>
-      </c>
-      <c r="H7">
-        <v>40</v>
-      </c>
-      <c r="I7">
-        <v>37</v>
-      </c>
-      <c r="J7">
-        <v>32</v>
-      </c>
-      <c r="K7">
-        <v>39</v>
-      </c>
-      <c r="L7">
-        <v>35</v>
-      </c>
-      <c r="M7">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -10665,7 +10695,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10728,35 +10758,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10764,40 +10800,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10807,110 +10840,87 @@
       <c r="H4">
         <v>1</v>
       </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>13</v>
+      </c>
+      <c r="D5">
+        <v>16</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>21</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>7</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H6">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>13</v>
+      </c>
+      <c r="L6">
+        <v>14</v>
+      </c>
+      <c r="M6">
         <v>10</v>
-      </c>
-      <c r="K6">
-        <v>28</v>
-      </c>
-      <c r="L6">
-        <v>33</v>
-      </c>
-      <c r="M6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>29</v>
-      </c>
-      <c r="C7">
-        <v>39</v>
-      </c>
-      <c r="D7">
-        <v>36</v>
-      </c>
-      <c r="E7">
-        <v>25</v>
-      </c>
-      <c r="F7">
-        <v>41</v>
-      </c>
-      <c r="G7">
-        <v>34</v>
-      </c>
-      <c r="H7">
-        <v>38</v>
-      </c>
-      <c r="I7">
-        <v>38</v>
-      </c>
-      <c r="J7">
-        <v>21</v>
-      </c>
-      <c r="K7">
-        <v>46</v>
-      </c>
-      <c r="L7">
-        <v>53</v>
-      </c>
-      <c r="M7">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -11053,7 +11063,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -11094,7 +11104,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -11207,7 +11217,7 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -11344,7 +11354,7 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6">
         <v>15</v>
@@ -11659,7 +11669,7 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -11697,7 +11707,7 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>3</v>
@@ -11728,7 +11738,7 @@
         <v>11</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -11763,7 +11773,7 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -11772,13 +11782,13 @@
         <v>4</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6">
         <v>6</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6">
         <v>5</v>
@@ -12348,6 +12358,9 @@
       <c r="F3">
         <v>1</v>
       </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
       <c r="H3">
         <v>1</v>
       </c>
@@ -12425,7 +12438,7 @@
         <v>4</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -12619,10 +12632,10 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>14</v>
@@ -12660,10 +12673,10 @@
         <v>14</v>
       </c>
       <c r="J6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L6">
         <v>20</v>
@@ -12748,6 +12761,9 @@
       <c r="D2">
         <v>1</v>
       </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
       <c r="I2">
         <v>1</v>
       </c>
@@ -12855,7 +12871,7 @@
         <v>2</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -12880,7 +12896,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12943,73 +12959,73 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
       <c r="D2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
       <c r="G2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G3">
         <v>5</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J3">
         <v>5</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="M3">
         <v>5</v>
@@ -13019,90 +13035,113 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>7</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-    